--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -105,6 +105,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -481,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -615,12 +621,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="15" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
@@ -630,66 +636,66 @@
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D2" s="13" t="n">
+      <c r="D2" s="15" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E2" s="13" t="n">
+      <c r="E2" s="15" t="n">
         <v>402.51</v>
       </c>
-      <c r="F2" s="13" t="n">
+      <c r="F2" s="15" t="n">
         <v>408.58</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="15" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H2" s="13" t="n">
+      <c r="H2" s="15" t="n">
         <v>407.11</v>
       </c>
-      <c r="I2" s="13" t="n">
+      <c r="I2" s="15" t="n">
         <v>398.12</v>
       </c>
-      <c r="J2" s="13" t="n">
+      <c r="J2" s="15" t="n">
         <v>1.09</v>
       </c>
-      <c r="K2" s="13" t="n">
+      <c r="K2" s="15" t="n">
         <v>94827</v>
       </c>
-      <c r="L2" s="13" t="n">
+      <c r="L2" s="15" t="n">
         <v>94827</v>
       </c>
-      <c r="M2" s="13" t="n">
+      <c r="M2" s="15" t="n">
         <v>96773</v>
       </c>
-      <c r="N2" s="13" t="n"/>
-      <c r="O2" s="13" t="n">
+      <c r="N2" s="15" t="n"/>
+      <c r="O2" s="15" t="n">
         <v>3794</v>
       </c>
-      <c r="P2" s="13" t="n">
+      <c r="P2" s="15" t="n">
         <v>3794</v>
       </c>
-      <c r="Q2" s="13" t="n">
+      <c r="Q2" s="15" t="n">
         <v>14999</v>
       </c>
-      <c r="R2" s="13" t="n"/>
-      <c r="S2" s="13" t="n">
+      <c r="R2" s="15" t="n"/>
+      <c r="S2" s="15" t="n">
         <v>14719</v>
       </c>
-      <c r="T2" s="13" t="n">
+      <c r="T2" s="15" t="n">
         <v>44059</v>
       </c>
-      <c r="U2" s="13" t="inlineStr">
+      <c r="U2" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -699,66 +705,66 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="16" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="16" t="n">
         <v>177.19</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="16" t="n">
         <v>184.89</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="16" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="16" t="n">
         <v>182.58</v>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I3" s="16" t="n">
         <v>176.38</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J3" s="16" t="n">
         <v>4.91</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="16" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L3" s="14" t="n">
+      <c r="L3" s="16" t="n">
         <v>215938</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="M3" s="16" t="n">
         <v>60922</v>
       </c>
-      <c r="N3" s="14" t="n"/>
-      <c r="O3" s="14" t="n">
+      <c r="N3" s="16" t="n"/>
+      <c r="O3" s="16" t="n">
         <v>120067</v>
       </c>
-      <c r="P3" s="14" t="n">
+      <c r="P3" s="16" t="n">
         <v>120067</v>
       </c>
-      <c r="Q3" s="14" t="n">
+      <c r="Q3" s="16" t="n">
         <v>29760</v>
       </c>
-      <c r="R3" s="14" t="n"/>
-      <c r="S3" s="14" t="n">
+      <c r="R3" s="16" t="n"/>
+      <c r="S3" s="16" t="n">
         <v>11412</v>
       </c>
-      <c r="T3" s="14" t="n">
+      <c r="T3" s="16" t="n">
         <v>62556</v>
       </c>
-      <c r="U3" s="14" t="inlineStr">
+      <c r="U3" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -768,74 +774,74 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D4" s="13" t="n">
+      <c r="D4" s="15" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E4" s="13" t="n">
+      <c r="E4" s="15" t="n">
         <v>392.74</v>
       </c>
-      <c r="F4" s="13" t="n">
+      <c r="F4" s="15" t="n">
         <v>401.72</v>
       </c>
-      <c r="G4" s="13" t="n">
+      <c r="G4" s="15" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="H4" s="15" t="n">
         <v>396.8</v>
       </c>
-      <c r="I4" s="13" t="n">
+      <c r="I4" s="15" t="n">
         <v>390</v>
       </c>
-      <c r="J4" s="13" t="n">
+      <c r="J4" s="15" t="n">
         <v>15.98</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="K4" s="15" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L4" s="13" t="n">
+      <c r="L4" s="15" t="n">
         <v>281724</v>
       </c>
-      <c r="M4" s="13" t="n">
+      <c r="M4" s="15" t="n">
         <v>211915</v>
       </c>
-      <c r="N4" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" s="13" t="n">
+      <c r="N4" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="15" t="n">
         <v>119262</v>
       </c>
-      <c r="P4" s="13" t="n">
+      <c r="P4" s="15" t="n">
         <v>101832</v>
       </c>
-      <c r="Q4" s="13" t="n">
+      <c r="Q4" s="15" t="n">
         <v>72361</v>
       </c>
-      <c r="R4" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" s="13" t="n">
+      <c r="R4" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="15" t="n">
         <v>123278</v>
       </c>
-      <c r="T4" s="13" t="n">
+      <c r="T4" s="15" t="n">
         <v>89462</v>
       </c>
-      <c r="U4" s="13" t="inlineStr">
+      <c r="U4" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
@@ -845,92 +851,92 @@
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="16" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="16" t="n">
         <v>38.7</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="16" t="n">
         <v>38.67</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="16" t="n">
         <v>0.08</v>
       </c>
-      <c r="H5" s="14" t="n">
+      <c r="H5" s="16" t="n">
         <v>38.8</v>
       </c>
-      <c r="I5" s="14" t="n">
+      <c r="I5" s="16" t="n">
         <v>38.5</v>
       </c>
-      <c r="J5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T5" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U5" s="14" t="inlineStr">
+      <c r="J5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T5" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U5" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -940,92 +946,92 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="15" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="15" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="15" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="15" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="15" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" s="13" t="n">
+      <c r="I6" s="15" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="U6" s="13" t="inlineStr">
+      <c r="J6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="T6" s="15" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="U6" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -1035,66 +1041,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="16" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="16" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="16" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="16" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="16" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" s="14" t="n">
+      <c r="I7" s="16" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" s="14" t="n">
+      <c r="J7" s="16" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" s="14" t="n">
+      <c r="K7" s="16" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" s="14" t="n">
+      <c r="L7" s="16" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" s="14" t="n">
+      <c r="M7" s="16" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" s="14" t="n"/>
-      <c r="O7" s="14" t="n">
+      <c r="N7" s="16" t="n"/>
+      <c r="O7" s="16" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" s="14" t="n">
+      <c r="P7" s="16" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" s="14" t="n">
+      <c r="Q7" s="16" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" s="14" t="n"/>
-      <c r="S7" s="14" t="n">
+      <c r="R7" s="16" t="n"/>
+      <c r="S7" s="16" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" s="14" t="n">
+      <c r="T7" s="16" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" s="14" t="inlineStr">
+      <c r="U7" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>TD.TO</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank</t>
         </is>
@@ -1104,66 +1110,66 @@
           <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="15" t="n">
         <v>223066.26</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="15" t="n">
         <v>132.88</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="15" t="n">
         <v>135.14</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="15" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="15" t="n">
         <v>136.49</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="15" t="n">
         <v>132.48</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="15" t="n">
         <v>11.56</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="15" t="n">
         <v>65980</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="15" t="n">
         <v>61281</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="M8" s="15" t="n">
         <v>51524</v>
       </c>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n">
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n">
         <v>21208</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="15" t="n">
         <v>20538</v>
       </c>
-      <c r="Q8" s="13" t="n">
+      <c r="Q8" s="15" t="n">
         <v>10634</v>
       </c>
-      <c r="R8" s="13" t="n"/>
-      <c r="S8" s="13" t="n">
+      <c r="R8" s="15" t="n"/>
+      <c r="S8" s="15" t="n">
         <v>528488.99</v>
       </c>
-      <c r="T8" s="13" t="n">
+      <c r="T8" s="15" t="n">
         <v>654255</v>
       </c>
-      <c r="U8" s="13" t="inlineStr">
+      <c r="U8" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc.</t>
         </is>
@@ -1173,66 +1179,66 @@
           <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="16" t="n">
         <v>328113.98</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="16" t="n">
         <v>137.19</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="16" t="n">
         <v>135.94</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="16" t="n">
         <v>0.92</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="16" t="n">
         <v>138.1</v>
       </c>
-      <c r="I9" s="14" t="n">
+      <c r="I9" s="16" t="n">
         <v>133.99</v>
       </c>
-      <c r="J9" s="14" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.63</v>
       </c>
-      <c r="K9" s="14" t="n">
+      <c r="K9" s="16" t="n">
         <v>4475.45</v>
       </c>
-      <c r="L9" s="14" t="n">
+      <c r="L9" s="16" t="n">
         <v>4475.45</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="16" t="n">
         <v>2225.01</v>
       </c>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n">
+      <c r="N9" s="16" t="n"/>
+      <c r="O9" s="16" t="n">
         <v>1625.03</v>
       </c>
-      <c r="P9" s="14" t="n">
+      <c r="P9" s="16" t="n">
         <v>1625.03</v>
       </c>
-      <c r="Q9" s="14" t="n">
+      <c r="Q9" s="16" t="n">
         <v>209.82</v>
       </c>
-      <c r="R9" s="14" t="n"/>
-      <c r="S9" s="14" t="n">
+      <c r="R9" s="16" t="n"/>
+      <c r="S9" s="16" t="n">
         <v>229.34</v>
       </c>
-      <c r="T9" s="14" t="n">
+      <c r="T9" s="16" t="n">
         <v>7177.04</v>
       </c>
-      <c r="U9" s="14" t="inlineStr">
+      <c r="U9" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
@@ -1242,66 +1248,66 @@
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="15" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="15" t="n">
         <v>200.21</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="15" t="n">
         <v>203.68</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="15" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="15" t="n">
         <v>201.88</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="15" t="n">
         <v>197.74</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="15" t="n">
         <v>2.6</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="15" t="n">
         <v>34639</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="15" t="n">
         <v>34639</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="15" t="n">
         <v>22680</v>
       </c>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n">
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="n">
         <v>4269</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="15" t="n">
         <v>4335</v>
       </c>
-      <c r="Q10" s="13" t="n">
+      <c r="Q10" s="15" t="n">
         <v>854</v>
       </c>
-      <c r="R10" s="13" t="n"/>
-      <c r="S10" s="13" t="n">
+      <c r="R10" s="15" t="n"/>
+      <c r="S10" s="15" t="n">
         <v>4006</v>
       </c>
-      <c r="T10" s="13" t="n">
+      <c r="T10" s="15" t="n">
         <v>10552</v>
       </c>
-      <c r="U10" s="13" t="inlineStr">
+      <c r="U10" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -1311,62 +1317,62 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="16" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="16" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="16" t="n">
         <v>84.607</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="16" t="n">
         <v>13.75</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="16" t="n">
         <v>96.75</v>
       </c>
-      <c r="I11" s="14" t="n">
+      <c r="I11" s="16" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="16" t="n">
         <v>2.53</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="16" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L11" s="14" t="n">
+      <c r="L11" s="16" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M11" s="14" t="n">
+      <c r="M11" s="16" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="n">
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="16" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="16" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R11" s="14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="14" t="n">
+      <c r="R11" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="16" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T11" s="14" t="n">
+      <c r="T11" s="16" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U11" s="14" t="inlineStr">
+      <c r="U11" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
@@ -1446,6 +1452,160 @@
       <c r="U12" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
+        <v>22648.69</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I13" s="16" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>3583.03</v>
+      </c>
+      <c r="L13" s="16" t="n">
+        <v>3613.35</v>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>2108.22</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="P13" s="16" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="Q13" s="16" t="n">
+        <v>-300.74</v>
+      </c>
+      <c r="R13" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S13" s="16" t="n">
+        <v>1939.17</v>
+      </c>
+      <c r="T13" s="16" t="n">
+        <v>5001.41</v>
+      </c>
+      <c r="U13" s="16" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>2254333.28</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>210</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>207.92</v>
+      </c>
+      <c r="G14" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>210.33</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>205.2</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>716923.99</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <v>716924</v>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>574785</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="n">
+        <v>77670</v>
+      </c>
+      <c r="P14" s="17" t="n">
+        <v>77670</v>
+      </c>
+      <c r="Q14" s="17" t="n">
+        <v>30425</v>
+      </c>
+      <c r="R14" s="17" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="17" t="n">
+        <v>178547</v>
+      </c>
+      <c r="T14" s="17" t="n">
+        <v>123029</v>
+      </c>
+      <c r="U14" s="17" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,729 +745,798 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANK.TO</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
+          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>882.9299999999999</v>
+        <v>1511612.87</v>
       </c>
       <c r="E5" t="n">
-        <v>9.77</v>
+        <v>318.82</v>
       </c>
       <c r="F5" t="n">
-        <v>9.91</v>
+        <v>319.55</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.41</v>
+        <v>-0.23</v>
       </c>
       <c r="H5" t="n">
-        <v>9.91</v>
+        <v>320.04</v>
       </c>
       <c r="I5" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>307.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>63887</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63887</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35819</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>23126</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23126</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14082</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>40457</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11105</v>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-01 15:59:09</t>
+          <t>2026-03-02 21:41:28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BANK.TO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3771360.87</v>
+        <v>882.9299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>311.76</v>
+        <v>9.77</v>
       </c>
       <c r="F6" t="n">
-        <v>307.38</v>
+        <v>9.91</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>-1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>312.37</v>
+        <v>9.91</v>
       </c>
       <c r="I6" t="n">
-        <v>303.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="K6" t="n">
-        <v>402836</v>
-      </c>
-      <c r="L6" t="n">
-        <v>402836</v>
-      </c>
-      <c r="M6" t="n">
-        <v>307394</v>
-      </c>
+        <v>9.74</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
-        <v>132170</v>
-      </c>
-      <c r="P6" t="n">
-        <v>132170</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>73795</v>
-      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
-        <v>66996</v>
-      </c>
-      <c r="T6" t="n">
-        <v>126843</v>
-      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:06</t>
+          <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68288.39</v>
+        <v>3771360.87</v>
       </c>
       <c r="E7" t="n">
-        <v>75.84999999999999</v>
+        <v>311.76</v>
       </c>
       <c r="F7" t="n">
-        <v>79.45</v>
+        <v>307.38</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.53</v>
+        <v>1.42</v>
       </c>
       <c r="H7" t="n">
-        <v>77.79000000000001</v>
+        <v>312.37</v>
       </c>
       <c r="I7" t="n">
-        <v>74.81999999999999</v>
+        <v>303.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.05</v>
+        <v>10.82</v>
       </c>
       <c r="K7" t="n">
-        <v>4473</v>
+        <v>402836</v>
       </c>
       <c r="L7" t="n">
-        <v>4473</v>
+        <v>402836</v>
       </c>
       <c r="M7" t="n">
-        <v>1865</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>307394</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1883</v>
+        <v>132170</v>
       </c>
       <c r="P7" t="n">
-        <v>1883</v>
+        <v>132170</v>
       </c>
       <c r="Q7" t="n">
-        <v>-541</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>73795</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12449</v>
+        <v>66996</v>
       </c>
       <c r="T7" t="n">
-        <v>12646</v>
+        <v>126843</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:07</t>
+          <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2918992.05</v>
+        <v>68288.39</v>
       </c>
       <c r="E8" t="n">
-        <v>392.74</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>401.72</v>
+        <v>79.45</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.24</v>
+        <v>-4.53</v>
       </c>
       <c r="H8" t="n">
-        <v>396.8</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>390</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>15.98</v>
+        <v>2.05</v>
       </c>
       <c r="K8" t="n">
-        <v>305453.01</v>
+        <v>4473</v>
       </c>
       <c r="L8" t="n">
-        <v>281724</v>
+        <v>4473</v>
       </c>
       <c r="M8" t="n">
-        <v>211915</v>
+        <v>1865</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>119262</v>
+        <v>1883</v>
       </c>
       <c r="P8" t="n">
-        <v>101832</v>
+        <v>1883</v>
       </c>
       <c r="Q8" t="n">
-        <v>72361</v>
+        <v>-541</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>123278</v>
+        <v>12449</v>
       </c>
       <c r="T8" t="n">
-        <v>89462</v>
+        <v>12646</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>408239.44</v>
+        <v>2918992.05</v>
       </c>
       <c r="E9" t="n">
-        <v>96.23999999999999</v>
+        <v>392.74</v>
       </c>
       <c r="F9" t="n">
-        <v>84.607</v>
+        <v>401.72</v>
       </c>
       <c r="G9" t="n">
-        <v>13.75</v>
+        <v>-2.24</v>
       </c>
       <c r="H9" t="n">
-        <v>96.75</v>
+        <v>396.8</v>
       </c>
       <c r="I9" t="n">
-        <v>90.59999999999999</v>
+        <v>390</v>
       </c>
       <c r="J9" t="n">
-        <v>2.53</v>
+        <v>15.98</v>
       </c>
       <c r="K9" t="n">
-        <v>45183.04</v>
+        <v>305453.01</v>
       </c>
       <c r="L9" t="n">
-        <v>45183.04</v>
+        <v>281724</v>
       </c>
       <c r="M9" t="n">
-        <v>33723.3</v>
+        <v>211915</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>10981.2</v>
+        <v>119262</v>
       </c>
       <c r="P9" t="n">
-        <v>10981.2</v>
+        <v>101832</v>
       </c>
       <c r="Q9" t="n">
-        <v>5407.99</v>
+        <v>72361</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>16975.84</v>
+        <v>123278</v>
       </c>
       <c r="T9" t="n">
-        <v>9062.360000000001</v>
+        <v>89462</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4306603.08</v>
+        <v>408239.44</v>
       </c>
       <c r="E10" t="n">
-        <v>177.19</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>184.89</v>
+        <v>84.607</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.16</v>
+        <v>13.75</v>
       </c>
       <c r="H10" t="n">
-        <v>182.58</v>
+        <v>96.75</v>
       </c>
       <c r="I10" t="n">
-        <v>176.38</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>4.91</v>
+        <v>2.53</v>
       </c>
       <c r="K10" t="n">
-        <v>215938.01</v>
+        <v>45183.04</v>
       </c>
       <c r="L10" t="n">
-        <v>215938</v>
+        <v>45183.04</v>
       </c>
       <c r="M10" t="n">
-        <v>60922</v>
+        <v>33723.3</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>120067</v>
+        <v>10981.2</v>
       </c>
       <c r="P10" t="n">
-        <v>120067</v>
+        <v>10981.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>29760</v>
+        <v>5407.99</v>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11412</v>
+        <v>16975.84</v>
       </c>
       <c r="T10" t="n">
-        <v>62556</v>
+        <v>9062.360000000001</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>328113.98</v>
+        <v>4306603.08</v>
       </c>
       <c r="E11" t="n">
-        <v>137.19</v>
+        <v>177.19</v>
       </c>
       <c r="F11" t="n">
-        <v>135.94</v>
+        <v>184.89</v>
       </c>
       <c r="G11" t="n">
-        <v>0.92</v>
+        <v>-4.16</v>
       </c>
       <c r="H11" t="n">
-        <v>138.1</v>
+        <v>182.58</v>
       </c>
       <c r="I11" t="n">
-        <v>133.99</v>
+        <v>176.38</v>
       </c>
       <c r="J11" t="n">
-        <v>0.63</v>
+        <v>4.91</v>
       </c>
       <c r="K11" t="n">
-        <v>4475.45</v>
+        <v>215938.01</v>
       </c>
       <c r="L11" t="n">
-        <v>4475.45</v>
+        <v>215938</v>
       </c>
       <c r="M11" t="n">
-        <v>2225.01</v>
+        <v>60922</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>1625.03</v>
+        <v>120067</v>
       </c>
       <c r="P11" t="n">
-        <v>1625.03</v>
+        <v>120067</v>
       </c>
       <c r="Q11" t="n">
-        <v>209.82</v>
+        <v>29760</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>229.34</v>
+        <v>11412</v>
       </c>
       <c r="T11" t="n">
-        <v>7177.04</v>
+        <v>62556</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22648.69</v>
+        <v>328113.98</v>
       </c>
       <c r="E12" t="n">
-        <v>17.76</v>
+        <v>137.19</v>
       </c>
       <c r="F12" t="n">
-        <v>19.1</v>
+        <v>135.94</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.02</v>
+        <v>0.92</v>
       </c>
       <c r="H12" t="n">
-        <v>18.21</v>
+        <v>138.1</v>
       </c>
       <c r="I12" t="n">
-        <v>17.31</v>
+        <v>133.99</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39</v>
+        <v>0.63</v>
       </c>
       <c r="K12" t="n">
-        <v>3583.03</v>
+        <v>4475.45</v>
       </c>
       <c r="L12" t="n">
-        <v>3613.35</v>
+        <v>4475.45</v>
       </c>
       <c r="M12" t="n">
-        <v>2108.22</v>
+        <v>2225.01</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>481.32</v>
+        <v>1625.03</v>
       </c>
       <c r="P12" t="n">
-        <v>481.32</v>
+        <v>1625.03</v>
       </c>
       <c r="Q12" t="n">
-        <v>-300.74</v>
+        <v>209.82</v>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1939.17</v>
+        <v>229.34</v>
       </c>
       <c r="T12" t="n">
-        <v>5001.41</v>
+        <v>7177.04</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TD.TO</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>223066.26</v>
+        <v>22648.69</v>
       </c>
       <c r="E13" t="n">
-        <v>132.88</v>
+        <v>17.76</v>
       </c>
       <c r="F13" t="n">
-        <v>135.14</v>
+        <v>19.1</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.67</v>
+        <v>-7.02</v>
       </c>
       <c r="H13" t="n">
-        <v>136.49</v>
+        <v>18.21</v>
       </c>
       <c r="I13" t="n">
-        <v>132.48</v>
+        <v>17.31</v>
       </c>
       <c r="J13" t="n">
-        <v>11.56</v>
+        <v>0.39</v>
       </c>
       <c r="K13" t="n">
-        <v>65980</v>
+        <v>3583.03</v>
       </c>
       <c r="L13" t="n">
-        <v>61281</v>
+        <v>3613.35</v>
       </c>
       <c r="M13" t="n">
-        <v>51524</v>
+        <v>2108.22</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>21208</v>
+        <v>481.32</v>
       </c>
       <c r="P13" t="n">
-        <v>20538</v>
+        <v>481.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>10634</v>
+        <v>-300.74</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>528488.99</v>
+        <v>1939.17</v>
       </c>
       <c r="T13" t="n">
-        <v>654255</v>
+        <v>5001.41</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>TD.TO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1510391.41</v>
+        <v>223066.26</v>
       </c>
       <c r="E14" t="n">
-        <v>402.51</v>
+        <v>132.88</v>
       </c>
       <c r="F14" t="n">
-        <v>408.58</v>
+        <v>135.14</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.49</v>
+        <v>-1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>407.11</v>
+        <v>136.49</v>
       </c>
       <c r="I14" t="n">
-        <v>398.12</v>
+        <v>132.48</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>11.56</v>
       </c>
       <c r="K14" t="n">
-        <v>94827</v>
+        <v>65980</v>
       </c>
       <c r="L14" t="n">
-        <v>94827</v>
+        <v>61281</v>
       </c>
       <c r="M14" t="n">
-        <v>96773</v>
+        <v>51524</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>3794</v>
+        <v>21208</v>
       </c>
       <c r="P14" t="n">
-        <v>3794</v>
+        <v>20538</v>
       </c>
       <c r="Q14" t="n">
-        <v>14999</v>
+        <v>10634</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>14719</v>
+        <v>528488.99</v>
       </c>
       <c r="T14" t="n">
-        <v>44059</v>
+        <v>654255</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H15" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I15" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M15" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T15" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>38.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>38.67</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>0.08</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>38.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>38.5</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,12 +29,18 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +61,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -581,7 +593,6 @@
       <c r="M2" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>117777</v>
       </c>
@@ -591,7 +602,6 @@
       <c r="Q2" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>90509</v>
       </c>
@@ -650,7 +660,6 @@
       <c r="M3" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>4269</v>
       </c>
@@ -660,7 +669,6 @@
       <c r="Q3" t="n">
         <v>854</v>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>4006</v>
       </c>
@@ -719,7 +727,6 @@
       <c r="M4" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>77670</v>
       </c>
@@ -729,7 +736,6 @@
       <c r="Q4" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>178547</v>
       </c>
@@ -745,800 +751,770 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>BANK.TO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1511612.87</v>
+        <v>882.9299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>318.82</v>
+        <v>9.77</v>
       </c>
       <c r="F5" t="n">
-        <v>319.55</v>
+        <v>9.91</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.23</v>
+        <v>-1.41</v>
       </c>
       <c r="H5" t="n">
-        <v>320.04</v>
+        <v>9.91</v>
       </c>
       <c r="I5" t="n">
-        <v>307.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K5" t="n">
-        <v>63887</v>
-      </c>
-      <c r="L5" t="n">
-        <v>63887</v>
-      </c>
-      <c r="M5" t="n">
-        <v>35819</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" t="n">
-        <v>23126</v>
-      </c>
-      <c r="P5" t="n">
-        <v>23126</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14082</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>40457</v>
-      </c>
-      <c r="T5" t="n">
-        <v>11105</v>
+        <v>9.74</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-02 21:41:28</t>
+          <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BANK.TO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>882.9299999999999</v>
+        <v>3771360.87</v>
       </c>
       <c r="E6" t="n">
-        <v>9.77</v>
+        <v>311.76</v>
       </c>
       <c r="F6" t="n">
-        <v>9.91</v>
+        <v>307.38</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H6" t="n">
-        <v>9.91</v>
+        <v>312.37</v>
       </c>
       <c r="I6" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+        <v>303.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="K6" t="n">
+        <v>402836</v>
+      </c>
+      <c r="L6" t="n">
+        <v>402836</v>
+      </c>
+      <c r="M6" t="n">
+        <v>307394</v>
+      </c>
+      <c r="O6" t="n">
+        <v>132170</v>
+      </c>
+      <c r="P6" t="n">
+        <v>132170</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>73795</v>
+      </c>
+      <c r="S6" t="n">
+        <v>66996</v>
+      </c>
+      <c r="T6" t="n">
+        <v>126843</v>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-01 15:59:09</t>
+          <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
+          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3771360.87</v>
+        <v>68288.39</v>
       </c>
       <c r="E7" t="n">
-        <v>311.76</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>307.38</v>
+        <v>79.45</v>
       </c>
       <c r="G7" t="n">
-        <v>1.42</v>
+        <v>-4.53</v>
       </c>
       <c r="H7" t="n">
-        <v>312.37</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>303.8</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>10.82</v>
+        <v>2.05</v>
       </c>
       <c r="K7" t="n">
-        <v>402836</v>
+        <v>4473</v>
       </c>
       <c r="L7" t="n">
-        <v>402836</v>
+        <v>4473</v>
       </c>
       <c r="M7" t="n">
-        <v>307394</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>1865</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O7" t="n">
-        <v>132170</v>
+        <v>1883</v>
       </c>
       <c r="P7" t="n">
-        <v>132170</v>
+        <v>1883</v>
       </c>
       <c r="Q7" t="n">
-        <v>73795</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
+        <v>-541</v>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="S7" t="n">
-        <v>66996</v>
+        <v>12449</v>
       </c>
       <c r="T7" t="n">
-        <v>126843</v>
+        <v>12646</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:06</t>
+          <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>68288.39</v>
+        <v>2918992.05</v>
       </c>
       <c r="E8" t="n">
-        <v>75.84999999999999</v>
+        <v>392.74</v>
       </c>
       <c r="F8" t="n">
-        <v>79.45</v>
+        <v>401.72</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.53</v>
+        <v>-2.24</v>
       </c>
       <c r="H8" t="n">
-        <v>77.79000000000001</v>
+        <v>396.8</v>
       </c>
       <c r="I8" t="n">
-        <v>74.81999999999999</v>
+        <v>390</v>
       </c>
       <c r="J8" t="n">
-        <v>2.05</v>
+        <v>15.98</v>
       </c>
       <c r="K8" t="n">
-        <v>4473</v>
+        <v>305453.01</v>
       </c>
       <c r="L8" t="n">
-        <v>4473</v>
+        <v>281724</v>
       </c>
       <c r="M8" t="n">
-        <v>1865</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>211915</v>
+      </c>
       <c r="O8" t="n">
-        <v>1883</v>
+        <v>119262</v>
       </c>
       <c r="P8" t="n">
-        <v>1883</v>
+        <v>101832</v>
       </c>
       <c r="Q8" t="n">
-        <v>-541</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+        <v>72361</v>
+      </c>
       <c r="S8" t="n">
-        <v>12449</v>
+        <v>123278</v>
       </c>
       <c r="T8" t="n">
-        <v>12646</v>
+        <v>89462</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:07</t>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2918992.05</v>
+        <v>408239.44</v>
       </c>
       <c r="E9" t="n">
-        <v>392.74</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>401.72</v>
+        <v>84.607</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.24</v>
+        <v>13.75</v>
       </c>
       <c r="H9" t="n">
-        <v>396.8</v>
+        <v>96.75</v>
       </c>
       <c r="I9" t="n">
-        <v>390</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>15.98</v>
+        <v>2.53</v>
       </c>
       <c r="K9" t="n">
-        <v>305453.01</v>
+        <v>45183.04</v>
       </c>
       <c r="L9" t="n">
-        <v>281724</v>
+        <v>45183.04</v>
       </c>
       <c r="M9" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
+        <v>33723.3</v>
+      </c>
       <c r="O9" t="n">
-        <v>119262</v>
+        <v>10981.2</v>
       </c>
       <c r="P9" t="n">
-        <v>101832</v>
+        <v>10981.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+        <v>5407.99</v>
+      </c>
       <c r="S9" t="n">
-        <v>123278</v>
+        <v>16975.84</v>
       </c>
       <c r="T9" t="n">
-        <v>89462</v>
+        <v>9062.360000000001</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>408239.44</v>
+        <v>4306603.08</v>
       </c>
       <c r="E10" t="n">
-        <v>96.23999999999999</v>
+        <v>177.19</v>
       </c>
       <c r="F10" t="n">
-        <v>84.607</v>
+        <v>184.89</v>
       </c>
       <c r="G10" t="n">
-        <v>13.75</v>
+        <v>-4.16</v>
       </c>
       <c r="H10" t="n">
-        <v>96.75</v>
+        <v>182.58</v>
       </c>
       <c r="I10" t="n">
-        <v>90.59999999999999</v>
+        <v>176.38</v>
       </c>
       <c r="J10" t="n">
-        <v>2.53</v>
+        <v>4.91</v>
       </c>
       <c r="K10" t="n">
-        <v>45183.04</v>
+        <v>215938.01</v>
       </c>
       <c r="L10" t="n">
-        <v>45183.04</v>
+        <v>215938</v>
       </c>
       <c r="M10" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>60922</v>
+      </c>
       <c r="O10" t="n">
-        <v>10981.2</v>
+        <v>120067</v>
       </c>
       <c r="P10" t="n">
-        <v>10981.2</v>
+        <v>120067</v>
       </c>
       <c r="Q10" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+        <v>29760</v>
+      </c>
       <c r="S10" t="n">
-        <v>16975.84</v>
+        <v>11412</v>
       </c>
       <c r="T10" t="n">
-        <v>9062.360000000001</v>
+        <v>62556</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4306603.08</v>
+        <v>328113.98</v>
       </c>
       <c r="E11" t="n">
-        <v>177.19</v>
+        <v>137.19</v>
       </c>
       <c r="F11" t="n">
-        <v>184.89</v>
+        <v>135.94</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.16</v>
+        <v>0.92</v>
       </c>
       <c r="H11" t="n">
-        <v>182.58</v>
+        <v>138.1</v>
       </c>
       <c r="I11" t="n">
-        <v>176.38</v>
+        <v>133.99</v>
       </c>
       <c r="J11" t="n">
-        <v>4.91</v>
+        <v>0.63</v>
       </c>
       <c r="K11" t="n">
-        <v>215938.01</v>
+        <v>4475.45</v>
       </c>
       <c r="L11" t="n">
-        <v>215938</v>
+        <v>4475.45</v>
       </c>
       <c r="M11" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
+        <v>2225.01</v>
+      </c>
       <c r="O11" t="n">
-        <v>120067</v>
+        <v>1625.03</v>
       </c>
       <c r="P11" t="n">
-        <v>120067</v>
+        <v>1625.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+        <v>209.82</v>
+      </c>
       <c r="S11" t="n">
-        <v>11412</v>
+        <v>229.34</v>
       </c>
       <c r="T11" t="n">
-        <v>62556</v>
+        <v>7177.04</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>328113.98</v>
+        <v>22648.69</v>
       </c>
       <c r="E12" t="n">
-        <v>137.19</v>
+        <v>17.76</v>
       </c>
       <c r="F12" t="n">
-        <v>135.94</v>
+        <v>19.1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.92</v>
+        <v>-7.02</v>
       </c>
       <c r="H12" t="n">
-        <v>138.1</v>
+        <v>18.21</v>
       </c>
       <c r="I12" t="n">
-        <v>133.99</v>
+        <v>17.31</v>
       </c>
       <c r="J12" t="n">
-        <v>0.63</v>
+        <v>0.39</v>
       </c>
       <c r="K12" t="n">
-        <v>4475.45</v>
+        <v>3583.03</v>
       </c>
       <c r="L12" t="n">
-        <v>4475.45</v>
+        <v>3613.35</v>
       </c>
       <c r="M12" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>2108.22</v>
+      </c>
       <c r="O12" t="n">
-        <v>1625.03</v>
+        <v>481.32</v>
       </c>
       <c r="P12" t="n">
-        <v>1625.03</v>
+        <v>481.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>-300.74</v>
+      </c>
       <c r="S12" t="n">
-        <v>229.34</v>
+        <v>1939.17</v>
       </c>
       <c r="T12" t="n">
-        <v>7177.04</v>
+        <v>5001.41</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>TD.TO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>22648.69</v>
+        <v>223066.26</v>
       </c>
       <c r="E13" t="n">
-        <v>17.76</v>
+        <v>132.88</v>
       </c>
       <c r="F13" t="n">
-        <v>19.1</v>
+        <v>135.14</v>
       </c>
       <c r="G13" t="n">
-        <v>-7.02</v>
+        <v>-1.67</v>
       </c>
       <c r="H13" t="n">
-        <v>18.21</v>
+        <v>136.49</v>
       </c>
       <c r="I13" t="n">
-        <v>17.31</v>
+        <v>132.48</v>
       </c>
       <c r="J13" t="n">
-        <v>0.39</v>
+        <v>11.56</v>
       </c>
       <c r="K13" t="n">
-        <v>3583.03</v>
+        <v>65980</v>
       </c>
       <c r="L13" t="n">
-        <v>3613.35</v>
+        <v>61281</v>
       </c>
       <c r="M13" t="n">
-        <v>2108.22</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
+        <v>51524</v>
+      </c>
       <c r="O13" t="n">
-        <v>481.32</v>
+        <v>21208</v>
       </c>
       <c r="P13" t="n">
-        <v>481.32</v>
+        <v>20538</v>
       </c>
       <c r="Q13" t="n">
-        <v>-300.74</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
+        <v>10634</v>
+      </c>
       <c r="S13" t="n">
-        <v>1939.17</v>
+        <v>528488.99</v>
       </c>
       <c r="T13" t="n">
-        <v>5001.41</v>
+        <v>654255</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TD.TO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>223066.26</v>
+        <v>1510391.41</v>
       </c>
       <c r="E14" t="n">
-        <v>132.88</v>
+        <v>402.51</v>
       </c>
       <c r="F14" t="n">
-        <v>135.14</v>
+        <v>408.58</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.67</v>
+        <v>-1.49</v>
       </c>
       <c r="H14" t="n">
-        <v>136.49</v>
+        <v>407.11</v>
       </c>
       <c r="I14" t="n">
-        <v>132.48</v>
+        <v>398.12</v>
       </c>
       <c r="J14" t="n">
-        <v>11.56</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>65980</v>
+        <v>94827</v>
       </c>
       <c r="L14" t="n">
-        <v>61281</v>
+        <v>94827</v>
       </c>
       <c r="M14" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>96773</v>
+      </c>
       <c r="O14" t="n">
-        <v>21208</v>
+        <v>3794</v>
       </c>
       <c r="P14" t="n">
-        <v>20538</v>
+        <v>3794</v>
       </c>
       <c r="Q14" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
+        <v>14999</v>
+      </c>
       <c r="S14" t="n">
-        <v>528488.99</v>
+        <v>14719</v>
       </c>
       <c r="T14" t="n">
-        <v>654255</v>
+        <v>44059</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>XDIV.TO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1510391.41</v>
+        <v>3940.24</v>
       </c>
       <c r="E15" t="n">
-        <v>402.51</v>
+        <v>38.7</v>
       </c>
       <c r="F15" t="n">
-        <v>408.58</v>
+        <v>38.67</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.49</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>407.11</v>
+        <v>38.8</v>
       </c>
       <c r="I15" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M15" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T15" t="n">
-        <v>44059</v>
+        <v>38.5</v>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E16" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H16" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1511612.87</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>63887</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>63887</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>35819</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>23126</v>
+      </c>
+      <c r="P16" s="2" t="n">
+        <v>23126</v>
+      </c>
+      <c r="Q16" s="2" t="n">
+        <v>14082</v>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="n">
+        <v>40457</v>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>11105</v>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,7 +29,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +40,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
         <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,7 +67,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -70,6 +76,12 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -437,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,6 +1527,83 @@
       <c r="U16" s="2" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>K.TO</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corporation</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="n">
+        <v>60705.06</v>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="J17" s="4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K17" s="4" t="n">
+        <v>7051.1</v>
+      </c>
+      <c r="L17" s="4" t="n">
+        <v>7051.1</v>
+      </c>
+      <c r="M17" s="4" t="n">
+        <v>4239.7</v>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="n">
+        <v>2390.1</v>
+      </c>
+      <c r="P17" s="4" t="n">
+        <v>2390.1</v>
+      </c>
+      <c r="Q17" s="4" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="n">
+        <v>758.5</v>
+      </c>
+      <c r="T17" s="4" t="n">
+        <v>1761.7</v>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,24 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,22 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U17"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -605,6 +581,7 @@
       <c r="M2" t="n">
         <v>383285</v>
       </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>117777</v>
       </c>
@@ -614,6 +591,7 @@
       <c r="Q2" t="n">
         <v>96995</v>
       </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>90509</v>
       </c>
@@ -672,6 +650,7 @@
       <c r="M3" t="n">
         <v>22680</v>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>4269</v>
       </c>
@@ -681,6 +660,7 @@
       <c r="Q3" t="n">
         <v>854</v>
       </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>4006</v>
       </c>
@@ -739,6 +719,7 @@
       <c r="M4" t="n">
         <v>574785</v>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
         <v>77670</v>
       </c>
@@ -748,6 +729,7 @@
       <c r="Q4" t="n">
         <v>30425</v>
       </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
         <v>178547</v>
       </c>
@@ -763,847 +745,938 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANK.TO</t>
+          <t>AVGO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
+          <t>Broadcom Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
+          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>882.9299999999999</v>
+        <v>1511612.87</v>
       </c>
       <c r="E5" t="n">
-        <v>9.77</v>
+        <v>318.82</v>
       </c>
       <c r="F5" t="n">
-        <v>9.91</v>
+        <v>319.55</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.41</v>
+        <v>-0.23</v>
       </c>
       <c r="H5" t="n">
-        <v>9.91</v>
+        <v>320.04</v>
       </c>
       <c r="I5" t="n">
-        <v>9.74</v>
+        <v>307.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K5" t="n">
+        <v>63887</v>
+      </c>
+      <c r="L5" t="n">
+        <v>63887</v>
+      </c>
+      <c r="M5" t="n">
+        <v>35819</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>23126</v>
+      </c>
+      <c r="P5" t="n">
+        <v>23126</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14082</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>40457</v>
+      </c>
+      <c r="T5" t="n">
+        <v>11105</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-01 15:59:09</t>
+          <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>BANK.TO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3771360.87</v>
+        <v>882.9299999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>311.76</v>
+        <v>9.77</v>
       </c>
       <c r="F6" t="n">
-        <v>307.38</v>
+        <v>9.91</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>-1.41</v>
       </c>
       <c r="H6" t="n">
-        <v>312.37</v>
+        <v>9.91</v>
       </c>
       <c r="I6" t="n">
-        <v>303.8</v>
-      </c>
-      <c r="J6" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="K6" t="n">
-        <v>402836</v>
-      </c>
-      <c r="L6" t="n">
-        <v>402836</v>
-      </c>
-      <c r="M6" t="n">
-        <v>307394</v>
-      </c>
-      <c r="O6" t="n">
-        <v>132170</v>
-      </c>
-      <c r="P6" t="n">
-        <v>132170</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>73795</v>
-      </c>
-      <c r="S6" t="n">
-        <v>66996</v>
-      </c>
-      <c r="T6" t="n">
-        <v>126843</v>
-      </c>
+        <v>9.74</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:06</t>
+          <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68288.39</v>
+        <v>3771360.87</v>
       </c>
       <c r="E7" t="n">
-        <v>75.84999999999999</v>
+        <v>311.76</v>
       </c>
       <c r="F7" t="n">
-        <v>79.45</v>
+        <v>307.38</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.53</v>
+        <v>1.42</v>
       </c>
       <c r="H7" t="n">
-        <v>77.79000000000001</v>
+        <v>312.37</v>
       </c>
       <c r="I7" t="n">
-        <v>74.81999999999999</v>
+        <v>303.8</v>
       </c>
       <c r="J7" t="n">
-        <v>2.05</v>
+        <v>10.82</v>
       </c>
       <c r="K7" t="n">
-        <v>4473</v>
+        <v>402836</v>
       </c>
       <c r="L7" t="n">
-        <v>4473</v>
+        <v>402836</v>
       </c>
       <c r="M7" t="n">
-        <v>1865</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>307394</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1883</v>
+        <v>132170</v>
       </c>
       <c r="P7" t="n">
-        <v>1883</v>
+        <v>132170</v>
       </c>
       <c r="Q7" t="n">
-        <v>-541</v>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>73795</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12449</v>
+        <v>66996</v>
       </c>
       <c r="T7" t="n">
-        <v>12646</v>
+        <v>126843</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:07</t>
+          <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2918992.05</v>
+        <v>68288.39</v>
       </c>
       <c r="E8" t="n">
-        <v>392.74</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>401.72</v>
+        <v>79.45</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.24</v>
+        <v>-4.53</v>
       </c>
       <c r="H8" t="n">
-        <v>396.8</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>390</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>15.98</v>
+        <v>2.05</v>
       </c>
       <c r="K8" t="n">
-        <v>305453.01</v>
+        <v>4473</v>
       </c>
       <c r="L8" t="n">
-        <v>281724</v>
+        <v>4473</v>
       </c>
       <c r="M8" t="n">
-        <v>211915</v>
-      </c>
+        <v>1865</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>119262</v>
+        <v>1883</v>
       </c>
       <c r="P8" t="n">
-        <v>101832</v>
+        <v>1883</v>
       </c>
       <c r="Q8" t="n">
-        <v>72361</v>
-      </c>
+        <v>-541</v>
+      </c>
+      <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>123278</v>
+        <v>12449</v>
       </c>
       <c r="T8" t="n">
-        <v>89462</v>
+        <v>12646</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>K.TO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>Kinross Gold Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>408239.44</v>
+        <v>60705.06</v>
       </c>
       <c r="E9" t="n">
-        <v>96.23999999999999</v>
+        <v>50.29</v>
       </c>
       <c r="F9" t="n">
-        <v>84.607</v>
+        <v>50.42</v>
       </c>
       <c r="G9" t="n">
-        <v>13.75</v>
+        <v>-0.26</v>
       </c>
       <c r="H9" t="n">
-        <v>96.75</v>
+        <v>51.69</v>
       </c>
       <c r="I9" t="n">
-        <v>90.59999999999999</v>
+        <v>49.05</v>
       </c>
       <c r="J9" t="n">
-        <v>2.53</v>
+        <v>2.67</v>
       </c>
       <c r="K9" t="n">
-        <v>45183.04</v>
+        <v>7051.1</v>
       </c>
       <c r="L9" t="n">
-        <v>45183.04</v>
+        <v>7051.1</v>
       </c>
       <c r="M9" t="n">
-        <v>33723.3</v>
-      </c>
+        <v>4239.7</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>10981.2</v>
+        <v>2390.1</v>
       </c>
       <c r="P9" t="n">
-        <v>10981.2</v>
+        <v>2390.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>5407.99</v>
-      </c>
+        <v>416.3</v>
+      </c>
+      <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>16975.84</v>
+        <v>758.5</v>
       </c>
       <c r="T9" t="n">
-        <v>9062.360000000001</v>
+        <v>1761.7</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4306603.08</v>
+        <v>2918992.05</v>
       </c>
       <c r="E10" t="n">
-        <v>177.19</v>
+        <v>392.74</v>
       </c>
       <c r="F10" t="n">
-        <v>184.89</v>
+        <v>401.72</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.16</v>
+        <v>-2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>182.58</v>
+        <v>396.8</v>
       </c>
       <c r="I10" t="n">
-        <v>176.38</v>
+        <v>390</v>
       </c>
       <c r="J10" t="n">
-        <v>4.91</v>
+        <v>15.98</v>
       </c>
       <c r="K10" t="n">
-        <v>215938.01</v>
+        <v>305453.01</v>
       </c>
       <c r="L10" t="n">
-        <v>215938</v>
+        <v>281724</v>
       </c>
       <c r="M10" t="n">
-        <v>60922</v>
-      </c>
+        <v>211915</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>120067</v>
+        <v>119262</v>
       </c>
       <c r="P10" t="n">
-        <v>120067</v>
+        <v>101832</v>
       </c>
       <c r="Q10" t="n">
-        <v>29760</v>
-      </c>
+        <v>72361</v>
+      </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>11412</v>
+        <v>123278</v>
       </c>
       <c r="T10" t="n">
-        <v>62556</v>
+        <v>89462</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>328113.98</v>
+        <v>464463.92</v>
       </c>
       <c r="E11" t="n">
-        <v>137.19</v>
+        <v>412.67</v>
       </c>
       <c r="F11" t="n">
-        <v>135.94</v>
+        <v>412.37</v>
       </c>
       <c r="G11" t="n">
-        <v>0.92</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>138.1</v>
+        <v>417.61</v>
       </c>
       <c r="I11" t="n">
-        <v>133.99</v>
+        <v>397.0101</v>
       </c>
       <c r="J11" t="n">
-        <v>0.63</v>
+        <v>10.52</v>
       </c>
       <c r="K11" t="n">
-        <v>4475.45</v>
+        <v>42312</v>
       </c>
       <c r="L11" t="n">
-        <v>4475.45</v>
+        <v>37378</v>
       </c>
       <c r="M11" t="n">
-        <v>2225.01</v>
+        <v>15540</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="O11" t="n">
-        <v>1625.03</v>
+        <v>11909</v>
       </c>
       <c r="P11" t="n">
-        <v>1625.03</v>
+        <v>8539</v>
       </c>
       <c r="Q11" t="n">
-        <v>209.82</v>
+        <v>-5833</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
       </c>
       <c r="S11" t="n">
-        <v>229.34</v>
+        <v>12493</v>
       </c>
       <c r="T11" t="n">
-        <v>7177.04</v>
+        <v>10318</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>2026-03-02 22:15:27</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>22648.69</v>
+        <v>408239.44</v>
       </c>
       <c r="E12" t="n">
-        <v>17.76</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>19.1</v>
+        <v>84.607</v>
       </c>
       <c r="G12" t="n">
-        <v>-7.02</v>
+        <v>13.75</v>
       </c>
       <c r="H12" t="n">
-        <v>18.21</v>
+        <v>96.75</v>
       </c>
       <c r="I12" t="n">
-        <v>17.31</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>0.39</v>
+        <v>2.53</v>
       </c>
       <c r="K12" t="n">
-        <v>3583.03</v>
+        <v>45183.04</v>
       </c>
       <c r="L12" t="n">
-        <v>3613.35</v>
+        <v>45183.04</v>
       </c>
       <c r="M12" t="n">
-        <v>2108.22</v>
-      </c>
+        <v>33723.3</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>481.32</v>
+        <v>10981.2</v>
       </c>
       <c r="P12" t="n">
-        <v>481.32</v>
+        <v>10981.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>-300.74</v>
-      </c>
+        <v>5407.99</v>
+      </c>
+      <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>1939.17</v>
+        <v>16975.84</v>
       </c>
       <c r="T12" t="n">
-        <v>5001.41</v>
+        <v>9062.360000000001</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TD.TO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>223066.26</v>
+        <v>4306603.08</v>
       </c>
       <c r="E13" t="n">
-        <v>132.88</v>
+        <v>177.19</v>
       </c>
       <c r="F13" t="n">
-        <v>135.14</v>
+        <v>184.89</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.67</v>
+        <v>-4.16</v>
       </c>
       <c r="H13" t="n">
-        <v>136.49</v>
+        <v>182.58</v>
       </c>
       <c r="I13" t="n">
-        <v>132.48</v>
+        <v>176.38</v>
       </c>
       <c r="J13" t="n">
-        <v>11.56</v>
+        <v>4.91</v>
       </c>
       <c r="K13" t="n">
-        <v>65980</v>
+        <v>215938.01</v>
       </c>
       <c r="L13" t="n">
-        <v>61281</v>
+        <v>215938</v>
       </c>
       <c r="M13" t="n">
-        <v>51524</v>
-      </c>
+        <v>60922</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>21208</v>
+        <v>120067</v>
       </c>
       <c r="P13" t="n">
-        <v>20538</v>
+        <v>120067</v>
       </c>
       <c r="Q13" t="n">
-        <v>10634</v>
-      </c>
+        <v>29760</v>
+      </c>
+      <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>528488.99</v>
+        <v>11412</v>
       </c>
       <c r="T13" t="n">
-        <v>654255</v>
+        <v>62556</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1510391.41</v>
+        <v>328113.98</v>
       </c>
       <c r="E14" t="n">
-        <v>402.51</v>
+        <v>137.19</v>
       </c>
       <c r="F14" t="n">
-        <v>408.58</v>
+        <v>135.94</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.49</v>
+        <v>0.92</v>
       </c>
       <c r="H14" t="n">
-        <v>407.11</v>
+        <v>138.1</v>
       </c>
       <c r="I14" t="n">
-        <v>398.12</v>
+        <v>133.99</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>0.63</v>
       </c>
       <c r="K14" t="n">
-        <v>94827</v>
+        <v>4475.45</v>
       </c>
       <c r="L14" t="n">
-        <v>94827</v>
+        <v>4475.45</v>
       </c>
       <c r="M14" t="n">
-        <v>96773</v>
-      </c>
+        <v>2225.01</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>3794</v>
+        <v>1625.03</v>
       </c>
       <c r="P14" t="n">
-        <v>3794</v>
+        <v>1625.03</v>
       </c>
       <c r="Q14" t="n">
-        <v>14999</v>
-      </c>
+        <v>209.82</v>
+      </c>
+      <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>14719</v>
+        <v>229.34</v>
       </c>
       <c r="T14" t="n">
-        <v>44059</v>
+        <v>7177.04</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>22648.69</v>
+      </c>
+      <c r="E15" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="F15" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="H15" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I15" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3583.03</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3613.35</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2108.22</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="P15" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-300.74</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>1939.17</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5001.41</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:33:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E16" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F16" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H16" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I16" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J16" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K16" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L16" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M16" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P16" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T16" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E17" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H17" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K17" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L17" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M17" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T17" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D18" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E18" t="n">
         <v>38.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F18" t="n">
         <v>38.67</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G18" t="n">
         <v>0.08</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H18" t="n">
         <v>38.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I18" t="n">
         <v>38.5</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Broadcom Inc.</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>1511612.87</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>318.82</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>319.55</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>-0.23</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>320.04</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>307.2</v>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>4.76</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>63887</v>
-      </c>
-      <c r="L16" s="2" t="n">
-        <v>63887</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>35819</v>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>23126</v>
-      </c>
-      <c r="P16" s="2" t="n">
-        <v>23126</v>
-      </c>
-      <c r="Q16" s="2" t="n">
-        <v>14082</v>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="n">
-        <v>40457</v>
-      </c>
-      <c r="T16" s="2" t="n">
-        <v>11105</v>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:46:42</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>K.TO</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>60705.06</v>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="J17" s="4" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="M17" s="4" t="n">
-        <v>4239.7</v>
-      </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" s="4" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="P17" s="4" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="Q17" s="4" t="n">
-        <v>416.3</v>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S17" s="4" t="n">
-        <v>758.5</v>
-      </c>
-      <c r="T17" s="4" t="n">
-        <v>1761.7</v>
-      </c>
-      <c r="U17" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,12 +29,24 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +67,28 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -536,1145 +566,1169 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="6" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="6" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="6" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="6" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="6" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="6" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="6" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="6" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="6" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="N2" s="6" t="n"/>
+      <c r="O2" s="6" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="6" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="6" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
+      <c r="R2" s="6" t="n"/>
+      <c r="S2" s="6" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="6" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="7" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="7" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="7" t="n">
         <v>200.21</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="7" t="n">
         <v>203.68</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="7" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="7" t="n">
         <v>201.88</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="7" t="n">
         <v>197.74</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="7" t="n">
         <v>2.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="7" t="n">
         <v>34639</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="7" t="n">
         <v>34639</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="7" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N3" s="7" t="n"/>
+      <c r="O3" s="7" t="n">
         <v>4269</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="7" t="n">
         <v>4335</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="7" t="n">
         <v>854</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R3" s="7" t="n"/>
+      <c r="S3" s="7" t="n">
         <v>4006</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="7" t="n">
         <v>10552</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="7" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="6" t="n">
         <v>210</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="6" t="n">
         <v>207.92</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="6" t="n">
         <v>210.33</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="6" t="n">
         <v>205.2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="6" t="n">
         <v>7.16</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="6" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="6" t="n">
         <v>716924</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="6" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="N4" s="6" t="n"/>
+      <c r="O4" s="6" t="n">
         <v>77670</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="6" t="n">
         <v>77670</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="6" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
+      <c r="R4" s="6" t="n"/>
+      <c r="S4" s="6" t="n">
         <v>178547</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="6" t="n">
         <v>123029</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>1511612.87</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="7" t="n">
         <v>318.82</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>319.55</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="7" t="n">
         <v>-0.23</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="7" t="n">
         <v>320.04</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="7" t="n">
         <v>307.2</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="7" t="n">
         <v>4.76</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="7" t="n">
         <v>63887</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="7" t="n">
         <v>63887</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="7" t="n">
         <v>35819</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="7" t="n">
         <v>23126</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="7" t="n">
         <v>23126</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="7" t="n">
         <v>14082</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="R5" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="n">
         <v>40457</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="7" t="n">
         <v>11105</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" s="7" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="6" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="6" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="6" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="6" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
+      <c r="J6" s="6" t="n"/>
+      <c r="K6" s="6" t="n"/>
+      <c r="L6" s="6" t="n"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="7" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="7" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="7" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="7" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="7" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="7" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="7" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="N7" s="7" t="n"/>
+      <c r="O7" s="7" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="7" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="7" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
+      <c r="R7" s="7" t="n"/>
+      <c r="S7" s="7" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="7" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="7" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="6" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="6" t="n">
         <v>79.45</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="6" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="6" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="6" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="6" t="n">
         <v>2.05</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="6" t="n">
         <v>4473</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="6" t="n">
         <v>4473</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="6" t="n">
         <v>1865</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="n">
         <v>1883</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="6" t="n">
         <v>1883</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="6" t="n">
         <v>-541</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="6" t="n">
         <v>12449</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="6" t="n">
         <v>12646</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="6" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>K.TO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Kinross Gold Corporation</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>60705.06</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="7" t="n">
         <v>50.29</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>50.42</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>-0.26</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="7" t="n">
         <v>51.69</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="7" t="n">
         <v>49.05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="7" t="n">
         <v>2.67</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="7" t="n">
         <v>7051.1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9" s="7" t="n">
         <v>7051.1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9" s="7" t="n">
         <v>4239.7</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="n">
         <v>2390.1</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="7" t="n">
         <v>2390.1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q9" s="7" t="n">
         <v>416.3</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
+      <c r="R9" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="n">
         <v>758.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T9" s="7" t="n">
         <v>1761.7</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="6" t="n">
         <v>392.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="6" t="n">
         <v>401.72</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="6" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10" s="6" t="n">
         <v>396.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10" s="6" t="n">
         <v>390</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" s="6" t="n">
         <v>15.98</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" s="6" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10" s="6" t="n">
         <v>281724</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10" s="6" t="n">
         <v>211915</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="N10" s="6" t="n"/>
+      <c r="O10" s="6" t="n">
         <v>119262</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P10" s="6" t="n">
         <v>101832</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q10" s="6" t="n">
         <v>72361</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
+      <c r="R10" s="6" t="n"/>
+      <c r="S10" s="6" t="n">
         <v>123278</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T10" s="6" t="n">
         <v>89462</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>464463.92</v>
-      </c>
-      <c r="E11" t="n">
-        <v>412.67</v>
-      </c>
-      <c r="F11" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>417.61</v>
-      </c>
-      <c r="I11" t="n">
-        <v>397.0101</v>
-      </c>
-      <c r="J11" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K11" t="n">
-        <v>42312</v>
-      </c>
-      <c r="L11" t="n">
-        <v>37378</v>
-      </c>
-      <c r="M11" t="n">
-        <v>15540</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>11909</v>
-      </c>
-      <c r="P11" t="n">
-        <v>8539</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-5833</v>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" t="n">
-        <v>12493</v>
-      </c>
-      <c r="T11" t="n">
-        <v>10318</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2026-03-02 22:15:27</t>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>408239.44</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>84.607</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J11" s="7" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>33723.3</v>
+      </c>
+      <c r="N11" s="7" t="n"/>
+      <c r="O11" s="7" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>5407.99</v>
+      </c>
+      <c r="R11" s="7" t="n"/>
+      <c r="S11" s="7" t="n">
+        <v>16975.84</v>
+      </c>
+      <c r="T11" s="7" t="n">
+        <v>9062.360000000001</v>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E12" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F12" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G12" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H12" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I12" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K12" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L12" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M12" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P12" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T12" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N12" s="6" t="n"/>
+      <c r="O12" s="6" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R12" s="6" t="n"/>
+      <c r="S12" s="6" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T12" s="6" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U12" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E13" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F13" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H13" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I13" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J13" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K13" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L13" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M13" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P13" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T13" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>328113.98</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>133.99</v>
+      </c>
+      <c r="J13" s="7" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K13" s="7" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N13" s="7" t="n"/>
+      <c r="O13" s="7" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P13" s="7" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q13" s="7" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R13" s="7" t="n"/>
+      <c r="S13" s="7" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T13" s="7" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E14" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F14" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H14" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I14" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K14" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L14" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T14" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K14" s="6" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L14" s="6" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M14" s="6" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="6" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v>132</v>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="n">
+        <v>188</v>
+      </c>
+      <c r="T14" s="6" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="7" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="7" t="n">
         <v>22648.69</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="7" t="n">
         <v>17.76</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="7" t="n">
         <v>19.1</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="7" t="n">
         <v>-7.02</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15" s="7" t="n">
         <v>18.21</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15" s="7" t="n">
         <v>17.31</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="7" t="n">
         <v>0.39</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15" s="7" t="n">
         <v>3583.03</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15" s="7" t="n">
         <v>3613.35</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15" s="7" t="n">
         <v>2108.22</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="N15" s="7" t="n"/>
+      <c r="O15" s="7" t="n">
         <v>481.32</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P15" s="7" t="n">
         <v>481.32</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q15" s="7" t="n">
         <v>-300.74</v>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
+      <c r="R15" s="7" t="n"/>
+      <c r="S15" s="7" t="n">
         <v>1939.17</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T15" s="7" t="n">
         <v>5001.41</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U15" s="7" t="inlineStr">
         <is>
           <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>TD.TO</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="6" t="n">
         <v>223066.26</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="6" t="n">
         <v>132.88</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="6" t="n">
         <v>135.14</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="6" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16" s="6" t="n">
         <v>136.49</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16" s="6" t="n">
         <v>132.48</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="6" t="n">
         <v>11.56</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16" s="6" t="n">
         <v>65980</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16" s="6" t="n">
         <v>61281</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16" s="6" t="n">
         <v>51524</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="N16" s="6" t="n"/>
+      <c r="O16" s="6" t="n">
         <v>21208</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P16" s="6" t="n">
         <v>20538</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q16" s="6" t="n">
         <v>10634</v>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
+      <c r="R16" s="6" t="n"/>
+      <c r="S16" s="6" t="n">
         <v>528488.99</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T16" s="6" t="n">
         <v>654255</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U16" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="7" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="7" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="7" t="n">
         <v>402.51</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>408.58</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="7" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17" s="7" t="n">
         <v>407.11</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17" s="7" t="n">
         <v>398.12</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17" s="7" t="n">
         <v>1.09</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17" s="7" t="n">
         <v>94827</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17" s="7" t="n">
         <v>94827</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17" s="7" t="n">
         <v>96773</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="N17" s="7" t="n"/>
+      <c r="O17" s="7" t="n">
         <v>3794</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P17" s="7" t="n">
         <v>3794</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q17" s="7" t="n">
         <v>14999</v>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
+      <c r="R17" s="7" t="n"/>
+      <c r="S17" s="7" t="n">
         <v>14719</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T17" s="7" t="n">
         <v>44059</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U17" s="7" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="6" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="6" t="n">
         <v>38.7</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="6" t="n">
         <v>38.67</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H18" s="6" t="n">
         <v>38.8</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18" s="6" t="n">
         <v>38.5</v>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
+      <c r="J18" s="6" t="n"/>
+      <c r="K18" s="6" t="n"/>
+      <c r="L18" s="6" t="n"/>
+      <c r="M18" s="6" t="n"/>
+      <c r="N18" s="6" t="n"/>
+      <c r="O18" s="6" t="n"/>
+      <c r="P18" s="6" t="n"/>
+      <c r="Q18" s="6" t="n"/>
+      <c r="R18" s="6" t="n"/>
+      <c r="S18" s="6" t="n"/>
+      <c r="T18" s="6" t="n"/>
+      <c r="U18" s="6" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,15 +25,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,23 +71,62 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,9 +490,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="40.35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stock Ticker</t>
@@ -535,1284 +599,1324 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="40.35" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="10" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="10" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="10" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="10" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="10" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="10" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="10" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="10" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="10" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="10" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="10" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="10" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="10" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="10" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="40.35" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="11" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="11" t="n">
         <v>200.21</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="11" t="n">
         <v>203.68</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="11" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="11" t="n">
         <v>201.88</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="11" t="n">
         <v>197.74</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="11" t="n">
         <v>2.6</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="11" t="n">
         <v>34639</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="11" t="n">
         <v>34639</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="11" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N3" s="11" t="n"/>
+      <c r="O3" s="11" t="n">
         <v>4269</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="11" t="n">
         <v>4335</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="11" t="n">
         <v>854</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="11" t="n">
         <v>4006</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="11" t="n">
         <v>10552</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="40.35" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="10" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="10" t="n">
         <v>210</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="10" t="n">
         <v>207.92</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="10" t="n">
         <v>210.33</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="10" t="n">
         <v>205.2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="10" t="n">
         <v>7.16</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="10" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="10" t="n">
         <v>716924</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="10" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n">
         <v>77670</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" s="10" t="n">
         <v>77670</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q4" s="10" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n">
         <v>178547</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T4" s="10" t="n">
         <v>123029</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="5" ht="40.35" customHeight="1">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="11" t="n">
         <v>1511612.87</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="11" t="n">
         <v>318.82</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="11" t="n">
         <v>319.55</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="11" t="n">
         <v>-0.23</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5" s="11" t="n">
         <v>320.04</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5" s="11" t="n">
         <v>307.2</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" s="11" t="n">
         <v>4.76</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" s="11" t="n">
         <v>63887</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="11" t="n">
         <v>63887</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="11" t="n">
         <v>35819</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="n">
         <v>23126</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P5" s="11" t="n">
         <v>23126</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q5" s="11" t="n">
         <v>14082</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="n">
         <v>40457</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T5" s="11" t="n">
         <v>11105</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" s="11" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="6" ht="40.35" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="10" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="10" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="10" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" s="10" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6" s="10" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6" s="10" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr">
+      <c r="J6" s="10" t="n"/>
+      <c r="K6" s="10" t="n"/>
+      <c r="L6" s="10" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="7" ht="40.35" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="11" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="11" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="11" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="11" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="11" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7" s="11" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" s="11" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" s="11" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="11" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="11" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P7" s="11" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q7" s="11" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
+      <c r="R7" s="11" t="n"/>
+      <c r="S7" s="11" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T7" s="11" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="8" ht="40.35" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="10" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="10" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="10" t="n">
         <v>79.45</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="10" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8" s="10" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8" s="10" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" s="10" t="n">
         <v>2.05</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" s="10" t="n">
         <v>4473</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8" s="10" t="n">
         <v>4473</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8" s="10" t="n">
         <v>1865</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="n">
         <v>1883</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P8" s="10" t="n">
         <v>1883</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q8" s="10" t="n">
         <v>-541</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
+      <c r="R8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="n">
         <v>12449</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T8" s="10" t="n">
         <v>12646</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" s="10" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="9" ht="40.35" customHeight="1">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>IREN</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t>IREN Limited</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>IREN Limited operates in the vertically integrated data center business in Australia and Canada. The company owns and operates computing hardware, as well as electrical infrastructure and data centers. It also mines Bitcoin, a scarce digital asset that is created and transmitted through the operation of a peer-to-peer network of computers running the Bitcoin software. The company was formerly known as Iris Energy Limited and changed its name to IREN Limited in November 2024. The company was incorporated in 2018 and is based in Sydney, Australia.</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>13731.51</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>41.39</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>40.95</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>42.2399</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>38.829</v>
+      </c>
+      <c r="J9" s="11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>757.1</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>501.02</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>75.51000000000001</v>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="11" t="n">
+        <v>389.74</v>
+      </c>
+      <c r="P9" s="11" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="Q9" s="11" t="n">
+        <v>-171.83</v>
+      </c>
+      <c r="R9" s="11" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="11" t="n">
+        <v>3842.55</v>
+      </c>
+      <c r="T9" s="11" t="n">
+        <v>3260.59</v>
+      </c>
+      <c r="U9" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:32:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="40.35" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>K.TO</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Kinross Gold Corporation</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" s="10" t="n">
         <v>60705.06</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" s="10" t="n">
         <v>50.29</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" s="10" t="n">
         <v>50.42</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" s="10" t="n">
         <v>-0.26</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" s="10" t="n">
         <v>51.69</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" s="10" t="n">
         <v>49.05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" s="10" t="n">
         <v>2.67</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" s="10" t="n">
         <v>7051.1</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" s="10" t="n">
         <v>7051.1</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" s="10" t="n">
         <v>4239.7</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="N10" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="10" t="n">
         <v>2390.1</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" s="10" t="n">
         <v>2390.1</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" s="10" t="n">
         <v>416.3</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
+      <c r="R10" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="n">
         <v>758.5</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" s="10" t="n">
         <v>1761.7</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" s="10" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="40.35" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" s="11" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" s="11" t="n">
         <v>392.74</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" s="11" t="n">
         <v>401.72</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" s="11" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" s="11" t="n">
         <v>396.8</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" s="11" t="n">
         <v>390</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" s="11" t="n">
         <v>15.98</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" s="11" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" s="11" t="n">
         <v>281724</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" s="11" t="n">
         <v>211915</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="N11" s="11" t="n"/>
+      <c r="O11" s="11" t="n">
         <v>119262</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" s="11" t="n">
         <v>101832</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" s="11" t="n">
         <v>72361</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="11" t="n">
         <v>123278</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" s="11" t="n">
         <v>89462</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="40.35" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" s="10" t="n">
         <v>464463.92</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" s="10" t="n">
         <v>412.67</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" s="10" t="n">
         <v>412.37</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" s="10" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" s="10" t="n">
         <v>417.61</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" s="10" t="n">
         <v>397.0101</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" s="10" t="n">
         <v>10.52</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" s="10" t="n">
         <v>42312</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" s="10" t="n">
         <v>37378</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" s="10" t="n">
         <v>15540</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O12" s="10" t="n">
         <v>11909</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P12" s="10" t="n">
         <v>8539</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" s="10" t="n">
         <v>-5833</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="n">
         <v>12493</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" s="10" t="n">
         <v>10318</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" s="10" t="inlineStr">
         <is>
           <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13" ht="40.35" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D13" s="11" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E13" s="11" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" s="11" t="n">
         <v>84.607</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G13" s="11" t="n">
         <v>13.75</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H13" s="11" t="n">
         <v>96.75</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I13" s="11" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J13" s="11" t="n">
         <v>2.53</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K13" s="11" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L13" s="11" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M13" s="11" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="n">
+      <c r="N13" s="11" t="n"/>
+      <c r="O13" s="11" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P12" t="n">
+      <c r="P13" s="11" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="Q13" s="11" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="n">
+      <c r="R13" s="11" t="n"/>
+      <c r="S13" s="11" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T12" t="n">
+      <c r="T13" s="11" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="U13" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+    <row r="14" ht="40.35" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="D14" s="10" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E14" s="10" t="n">
         <v>177.19</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F14" s="10" t="n">
         <v>184.89</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G14" s="10" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H14" s="10" t="n">
         <v>182.58</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I14" s="10" t="n">
         <v>176.38</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J14" s="10" t="n">
         <v>4.91</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K14" s="10" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L14" s="10" t="n">
         <v>215938</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M14" s="10" t="n">
         <v>60922</v>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n">
         <v>120067</v>
       </c>
-      <c r="P13" t="n">
+      <c r="P14" s="10" t="n">
         <v>120067</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="Q14" s="10" t="n">
         <v>29760</v>
       </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="n">
         <v>11412</v>
       </c>
-      <c r="T13" t="n">
+      <c r="T14" s="10" t="n">
         <v>62556</v>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="U14" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="15" ht="40.35" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc.</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" s="11" t="n">
         <v>328113.98</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" s="11" t="n">
         <v>137.19</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F15" s="11" t="n">
         <v>135.94</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G15" s="11" t="n">
         <v>0.92</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H15" s="11" t="n">
         <v>138.1</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I15" s="11" t="n">
         <v>133.99</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J15" s="11" t="n">
         <v>0.63</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K15" s="11" t="n">
         <v>4475.45</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L15" s="11" t="n">
         <v>4475.45</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M15" s="11" t="n">
         <v>2225.01</v>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
+      <c r="N15" s="11" t="n"/>
+      <c r="O15" s="11" t="n">
         <v>1625.03</v>
       </c>
-      <c r="P14" t="n">
+      <c r="P15" s="11" t="n">
         <v>1625.03</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="Q15" s="11" t="n">
         <v>209.82</v>
       </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
+      <c r="R15" s="11" t="n"/>
+      <c r="S15" s="11" t="n">
         <v>229.34</v>
       </c>
-      <c r="T14" t="n">
+      <c r="T15" s="11" t="n">
         <v>7177.04</v>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="U15" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="16" ht="40.35" customHeight="1">
+      <c r="A16" s="10" t="inlineStr">
         <is>
           <t>SHOP.TO</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>Shopify Inc.</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" s="10" t="n">
         <v>213981.48</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" s="10" t="n">
         <v>163.32</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" s="10" t="n">
         <v>164.67</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" s="10" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" s="10" t="n">
         <v>164.76</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" s="10" t="n">
         <v>156.66</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J16" s="10" t="n">
         <v>1.28</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K16" s="10" t="n">
         <v>11556</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L16" s="10" t="n">
         <v>11556</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M16" s="10" t="n">
         <v>7060</v>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="n">
         <v>1231</v>
       </c>
-      <c r="P15" t="n">
+      <c r="P16" s="10" t="n">
         <v>1231</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="Q16" s="10" t="n">
         <v>132</v>
       </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="n">
         <v>188</v>
       </c>
-      <c r="T15" t="n">
+      <c r="T16" s="10" t="n">
         <v>5847</v>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="U16" s="10" t="inlineStr">
         <is>
           <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
+    <row r="17" ht="40.35" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
         <is>
           <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
         </is>
       </c>
-      <c r="D16" t="n">
+      <c r="D17" s="11" t="n">
         <v>22648.69</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E17" s="11" t="n">
         <v>17.76</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F17" s="11" t="n">
         <v>19.1</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G17" s="11" t="n">
         <v>-7.02</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H17" s="11" t="n">
         <v>18.21</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I17" s="11" t="n">
         <v>17.31</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J17" s="11" t="n">
         <v>0.39</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K17" s="11" t="n">
         <v>3583.03</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L17" s="11" t="n">
         <v>3613.35</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M17" s="11" t="n">
         <v>2108.22</v>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="n">
+      <c r="N17" s="11" t="n"/>
+      <c r="O17" s="11" t="n">
         <v>481.32</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P17" s="11" t="n">
         <v>481.32</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q17" s="11" t="n">
         <v>-300.74</v>
       </c>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="n">
+      <c r="R17" s="11" t="n"/>
+      <c r="S17" s="11" t="n">
         <v>1939.17</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" s="11" t="n">
         <v>5001.41</v>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" s="11" t="inlineStr">
         <is>
           <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18" ht="40.35" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
         <is>
           <t>TD.TO</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
-      <c r="D17" t="n">
+      <c r="D18" s="10" t="n">
         <v>223066.26</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E18" s="10" t="n">
         <v>132.88</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F18" s="10" t="n">
         <v>135.14</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" s="10" t="n">
         <v>-1.67</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" s="10" t="n">
         <v>136.49</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" s="10" t="n">
         <v>132.48</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J18" s="10" t="n">
         <v>11.56</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K18" s="10" t="n">
         <v>65980</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L18" s="10" t="n">
         <v>61281</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M18" s="10" t="n">
         <v>51524</v>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="n">
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n">
         <v>21208</v>
       </c>
-      <c r="P17" t="n">
+      <c r="P18" s="10" t="n">
         <v>20538</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="Q18" s="10" t="n">
         <v>10634</v>
       </c>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="n">
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n">
         <v>528488.99</v>
       </c>
-      <c r="T17" t="n">
+      <c r="T18" s="10" t="n">
         <v>654255</v>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="U18" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:50</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E18" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F18" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G18" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H18" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I18" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K18" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L18" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M18" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T18" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>TSM</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Taiwan Semiconductor Manufacturing Company Limited, together with its subsidiaries, manufactures, packages, tests, and sells integrated circuits and other semiconductor devices in Taiwan, China, Europe, the Middle East, Africa, Japan, the United States, and internationally. It provides various wafer fabrication processes, such as processes to manufacture complementary metal- oxide-semiconductor (CMOS) logic, mixed-signal, radio frequency, embedded memory, bipolar CMOS mixed-signal, and others. The company also involved in providing customer and engineering support services; manufacturing of masks; investment in technology start-up companies; research, designing, developing, manufacturing, packaging, testing, and sale of color filters; and investment activities. Its products are used in high performance computing, smartphones, Internet of things, automotive, and digital consumer electronics. The company was incorporated in 1987 and is headquartered in Hsinchu City, Taiwan.</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1914390.71</v>
-      </c>
-      <c r="E19" t="n">
-        <v>369.11</v>
-      </c>
-      <c r="F19" t="n">
-        <v>374.58</v>
-      </c>
-      <c r="G19" t="n">
-        <v>-1.46</v>
-      </c>
-      <c r="H19" t="n">
-        <v>373.1</v>
-      </c>
-      <c r="I19" t="n">
-        <v>364.65</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>3809054.29</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3809054.27</v>
-      </c>
-      <c r="M19" t="n">
-        <v>2161735.8</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O19" t="n">
-        <v>1717882.59</v>
-      </c>
-      <c r="P19" t="n">
-        <v>1717882.63</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>851740</v>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S19" t="n">
-        <v>1068416.57</v>
-      </c>
-      <c r="T19" t="n">
-        <v>3068494.61</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>2026-03-02 22:30:28</t>
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I19" s="11" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J19" s="11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K19" s="11" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L19" s="11" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M19" s="11" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="11" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P19" s="11" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q19" s="11" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R19" s="11" t="n"/>
+      <c r="S19" s="11" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T19" s="11" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="10" t="inlineStr">
         <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="10" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="10" t="n">
         <v>38.7</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="10" t="n">
         <v>38.67</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="10" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" t="n">
+      <c r="H20" s="10" t="n">
         <v>38.8</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20" s="10" t="n">
         <v>38.5</v>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr">
+      <c r="J20" s="10" t="n"/>
+      <c r="K20" s="10" t="n"/>
+      <c r="L20" s="10" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -489,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -600,12 +606,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
@@ -615,66 +621,66 @@
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" s="10" t="n">
+      <c r="D2" s="12" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" s="10" t="n">
+      <c r="E2" s="12" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" s="10" t="n">
+      <c r="F2" s="12" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" s="10" t="n">
+      <c r="G2" s="12" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" s="10" t="n">
+      <c r="H2" s="12" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" s="10" t="n">
+      <c r="I2" s="12" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="J2" s="12" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" s="10" t="n">
+      <c r="K2" s="12" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" s="10" t="n">
+      <c r="L2" s="12" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" s="10" t="n">
+      <c r="M2" s="12" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n">
+      <c r="N2" s="12" t="n"/>
+      <c r="O2" s="12" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" s="10" t="n">
+      <c r="P2" s="12" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" s="10" t="n">
+      <c r="Q2" s="12" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n">
+      <c r="R2" s="12" t="n"/>
+      <c r="S2" s="12" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" s="10" t="n">
+      <c r="T2" s="12" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" s="10" t="inlineStr">
+      <c r="U2" s="12" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
@@ -684,66 +690,66 @@
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" s="11" t="n">
+      <c r="D3" s="13" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="13" t="n">
         <v>200.21</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="13" t="n">
         <v>203.68</v>
       </c>
-      <c r="G3" s="11" t="n">
+      <c r="G3" s="13" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="13" t="n">
         <v>201.88</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="13" t="n">
         <v>197.74</v>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" s="13" t="n">
         <v>2.6</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" s="13" t="n">
         <v>34639</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="13" t="n">
         <v>34639</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M3" s="13" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" s="11" t="n"/>
-      <c r="O3" s="11" t="n">
+      <c r="N3" s="13" t="n"/>
+      <c r="O3" s="13" t="n">
         <v>4269</v>
       </c>
-      <c r="P3" s="11" t="n">
+      <c r="P3" s="13" t="n">
         <v>4335</v>
       </c>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" s="13" t="n">
         <v>854</v>
       </c>
-      <c r="R3" s="11" t="n"/>
-      <c r="S3" s="11" t="n">
+      <c r="R3" s="13" t="n"/>
+      <c r="S3" s="13" t="n">
         <v>4006</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" s="13" t="n">
         <v>10552</v>
       </c>
-      <c r="U3" s="11" t="inlineStr">
+      <c r="U3" s="13" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="10" t="inlineStr">
+      <c r="A4" s="12" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" s="10" t="inlineStr">
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -753,66 +759,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D4" s="10" t="n">
+      <c r="D4" s="12" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="12" t="n">
         <v>210</v>
       </c>
-      <c r="F4" s="10" t="n">
+      <c r="F4" s="12" t="n">
         <v>207.92</v>
       </c>
-      <c r="G4" s="10" t="n">
+      <c r="G4" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="10" t="n">
+      <c r="H4" s="12" t="n">
         <v>210.33</v>
       </c>
-      <c r="I4" s="10" t="n">
+      <c r="I4" s="12" t="n">
         <v>205.2</v>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="J4" s="12" t="n">
         <v>7.16</v>
       </c>
-      <c r="K4" s="10" t="n">
+      <c r="K4" s="12" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L4" s="10" t="n">
+      <c r="L4" s="12" t="n">
         <v>716924</v>
       </c>
-      <c r="M4" s="10" t="n">
+      <c r="M4" s="12" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n">
+      <c r="N4" s="12" t="n"/>
+      <c r="O4" s="12" t="n">
         <v>77670</v>
       </c>
-      <c r="P4" s="10" t="n">
+      <c r="P4" s="12" t="n">
         <v>77670</v>
       </c>
-      <c r="Q4" s="10" t="n">
+      <c r="Q4" s="12" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n">
+      <c r="R4" s="12" t="n"/>
+      <c r="S4" s="12" t="n">
         <v>178547</v>
       </c>
-      <c r="T4" s="10" t="n">
+      <c r="T4" s="12" t="n">
         <v>123029</v>
       </c>
-      <c r="U4" s="10" t="inlineStr">
+      <c r="U4" s="12" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
@@ -822,74 +828,74 @@
           <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="13" t="n">
         <v>1511612.87</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="13" t="n">
         <v>318.82</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="13" t="n">
         <v>319.55</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="13" t="n">
         <v>-0.23</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="13" t="n">
         <v>320.04</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="13" t="n">
         <v>307.2</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="13" t="n">
         <v>4.76</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="13" t="n">
         <v>63887</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="13" t="n">
         <v>63887</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="13" t="n">
         <v>35819</v>
       </c>
-      <c r="N5" s="11" t="inlineStr">
+      <c r="N5" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="O5" s="13" t="n">
         <v>23126</v>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" s="13" t="n">
         <v>23126</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="13" t="n">
         <v>14082</v>
       </c>
-      <c r="R5" s="11" t="inlineStr">
+      <c r="R5" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="S5" s="13" t="n">
         <v>40457</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="13" t="n">
         <v>11105</v>
       </c>
-      <c r="U5" s="11" t="inlineStr">
+      <c r="U5" s="13" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -899,48 +905,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="12" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="12" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" s="10" t="n">
+      <c r="F6" s="12" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" s="10" t="n">
+      <c r="G6" s="12" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" s="10" t="n">
+      <c r="H6" s="12" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" s="10" t="n">
+      <c r="I6" s="12" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" s="10" t="n"/>
-      <c r="K6" s="10" t="n"/>
-      <c r="L6" s="10" t="n"/>
-      <c r="M6" s="10" t="n"/>
-      <c r="N6" s="10" t="n"/>
-      <c r="O6" s="10" t="n"/>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="n"/>
-      <c r="S6" s="10" t="n"/>
-      <c r="T6" s="10" t="n"/>
-      <c r="U6" s="10" t="inlineStr">
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
+      <c r="L6" s="12" t="n"/>
+      <c r="M6" s="12" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="12" t="n"/>
+      <c r="P6" s="12" t="n"/>
+      <c r="Q6" s="12" t="n"/>
+      <c r="R6" s="12" t="n"/>
+      <c r="S6" s="12" t="n"/>
+      <c r="T6" s="12" t="n"/>
+      <c r="U6" s="12" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -950,66 +956,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="13" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="13" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="13" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="13" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="13" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="13" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="13" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="13" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="13" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="13" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" s="11" t="n"/>
-      <c r="O7" s="11" t="n">
+      <c r="N7" s="13" t="n"/>
+      <c r="O7" s="13" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" s="11" t="n">
+      <c r="P7" s="13" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="13" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" s="11" t="n"/>
-      <c r="S7" s="11" t="n">
+      <c r="R7" s="13" t="n"/>
+      <c r="S7" s="13" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="13" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" s="11" t="inlineStr">
+      <c r="U7" s="13" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
@@ -1019,904 +1025,827 @@
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="12" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="12" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="12" t="n">
         <v>79.45</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="12" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="12" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="12" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="J8" s="12" t="n">
         <v>2.05</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="12" t="n">
         <v>4473</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="12" t="n">
         <v>4473</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="12" t="n">
         <v>1865</v>
       </c>
-      <c r="N8" s="10" t="inlineStr">
+      <c r="N8" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="12" t="n">
         <v>1883</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="12" t="n">
         <v>1883</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="12" t="n">
         <v>-541</v>
       </c>
-      <c r="R8" s="10" t="inlineStr">
+      <c r="R8" s="12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="10" t="n">
+      <c r="S8" s="12" t="n">
         <v>12449</v>
       </c>
-      <c r="T8" s="10" t="n">
+      <c r="T8" s="12" t="n">
         <v>12646</v>
       </c>
-      <c r="U8" s="10" t="inlineStr">
+      <c r="U8" s="12" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>IREN</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>IREN Limited</t>
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>K.TO</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Kinross Gold Corporation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>IREN Limited operates in the vertically integrated data center business in Australia and Canada. The company owns and operates computing hardware, as well as electrical infrastructure and data centers. It also mines Bitcoin, a scarce digital asset that is created and transmitted through the operation of a peer-to-peer network of computers running the Bitcoin software. The company was formerly known as Iris Energy Limited and changed its name to IREN Limited in November 2024. The company was incorporated in 2018 and is based in Sydney, Australia.</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>13731.51</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>41.39</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>40.95</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>42.2399</v>
-      </c>
-      <c r="I9" s="11" t="n">
-        <v>38.829</v>
-      </c>
-      <c r="J9" s="11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>757.1</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>501.02</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>75.51000000000001</v>
-      </c>
-      <c r="N9" s="11" t="inlineStr">
+          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>60705.06</v>
+      </c>
+      <c r="E9" s="13" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="G9" s="13" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="H9" s="13" t="n">
+        <v>51.69</v>
+      </c>
+      <c r="I9" s="13" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K9" s="13" t="n">
+        <v>7051.1</v>
+      </c>
+      <c r="L9" s="13" t="n">
+        <v>7051.1</v>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>4239.7</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O9" s="11" t="n">
-        <v>389.74</v>
-      </c>
-      <c r="P9" s="11" t="n">
-        <v>86.94</v>
-      </c>
-      <c r="Q9" s="11" t="n">
-        <v>-171.83</v>
-      </c>
-      <c r="R9" s="11" t="inlineStr">
+      <c r="O9" s="13" t="n">
+        <v>2390.1</v>
+      </c>
+      <c r="P9" s="13" t="n">
+        <v>2390.1</v>
+      </c>
+      <c r="Q9" s="13" t="n">
+        <v>416.3</v>
+      </c>
+      <c r="R9" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S9" s="11" t="n">
-        <v>3842.55</v>
-      </c>
-      <c r="T9" s="11" t="n">
-        <v>3260.59</v>
-      </c>
-      <c r="U9" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:32:16</t>
+      <c r="S9" s="13" t="n">
+        <v>758.5</v>
+      </c>
+      <c r="T9" s="13" t="n">
+        <v>1761.7</v>
+      </c>
+      <c r="U9" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-02 16:46:56</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>K.TO</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>60705.06</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="I10" s="10" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="L10" s="10" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="M10" s="10" t="n">
-        <v>4239.7</v>
-      </c>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="P10" s="10" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="Q10" s="10" t="n">
-        <v>416.3</v>
-      </c>
-      <c r="R10" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="n">
-        <v>758.5</v>
-      </c>
-      <c r="T10" s="10" t="n">
-        <v>1761.7</v>
-      </c>
-      <c r="U10" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:46:56</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>2918992.05</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="I10" s="12" t="n">
+        <v>390</v>
+      </c>
+      <c r="J10" s="12" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K10" s="12" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M10" s="12" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P10" s="12" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q10" s="12" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R10" s="12" t="n"/>
+      <c r="S10" s="12" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T10" s="12" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U10" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="n">
-        <v>2918992.05</v>
-      </c>
-      <c r="E11" s="11" t="n">
-        <v>392.74</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>401.72</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="H11" s="11" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="I11" s="11" t="n">
-        <v>390</v>
-      </c>
-      <c r="J11" s="11" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="K11" s="11" t="n">
-        <v>305453.01</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>281724</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N11" s="11" t="n"/>
-      <c r="O11" s="11" t="n">
-        <v>119262</v>
-      </c>
-      <c r="P11" s="11" t="n">
-        <v>101832</v>
-      </c>
-      <c r="Q11" s="11" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R11" s="11" t="n"/>
-      <c r="S11" s="11" t="n">
-        <v>123278</v>
-      </c>
-      <c r="T11" s="11" t="n">
-        <v>89462</v>
-      </c>
-      <c r="U11" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>464463.92</v>
+      </c>
+      <c r="E11" s="13" t="n">
+        <v>412.67</v>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H11" s="13" t="n">
+        <v>417.61</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>397.0101</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>42312</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>37378</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>15540</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>11909</v>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>8539</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>-5833</v>
+      </c>
+      <c r="R11" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="13" t="n">
+        <v>12493</v>
+      </c>
+      <c r="T11" s="13" t="n">
+        <v>10318</v>
+      </c>
+      <c r="U11" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="10" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>464463.92</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>412.67</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H12" s="10" t="n">
-        <v>417.61</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>397.0101</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>42312</v>
-      </c>
-      <c r="L12" s="10" t="n">
-        <v>37378</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>15540</v>
-      </c>
-      <c r="N12" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O12" s="10" t="n">
-        <v>11909</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>8539</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>-5833</v>
-      </c>
-      <c r="R12" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="n">
-        <v>12493</v>
-      </c>
-      <c r="T12" s="10" t="n">
-        <v>10318</v>
-      </c>
-      <c r="U12" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:28:51</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>408239.44</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>84.607</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J12" s="12" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K12" s="12" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="L12" s="12" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>33723.3</v>
+      </c>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="P12" s="12" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="Q12" s="12" t="n">
+        <v>5407.99</v>
+      </c>
+      <c r="R12" s="12" t="n"/>
+      <c r="S12" s="12" t="n">
+        <v>16975.84</v>
+      </c>
+      <c r="T12" s="12" t="n">
+        <v>9062.360000000001</v>
+      </c>
+      <c r="U12" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E13" s="11" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F13" s="11" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G13" s="11" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H13" s="11" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I13" s="11" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J13" s="11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K13" s="11" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M13" s="11" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N13" s="11" t="n"/>
-      <c r="O13" s="11" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P13" s="11" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q13" s="11" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R13" s="11" t="n"/>
-      <c r="S13" s="11" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T13" s="11" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U13" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G13" s="13" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H13" s="13" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I13" s="13" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J13" s="13" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K13" s="13" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L13" s="13" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N13" s="13" t="n"/>
+      <c r="O13" s="13" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P13" s="13" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q13" s="13" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R13" s="13" t="n"/>
+      <c r="S13" s="13" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T13" s="13" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U13" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40.35" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F14" s="10" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G14" s="10" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H14" s="10" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I14" s="10" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J14" s="10" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K14" s="10" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L14" s="10" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M14" s="10" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N14" s="10" t="n"/>
-      <c r="O14" s="10" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P14" s="10" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q14" s="10" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R14" s="10" t="n"/>
-      <c r="S14" s="10" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U14" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>328113.98</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I14" s="12" t="n">
+        <v>133.99</v>
+      </c>
+      <c r="J14" s="12" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K14" s="12" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L14" s="12" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P14" s="12" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q14" s="12" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R14" s="12" t="n"/>
+      <c r="S14" s="12" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T14" s="12" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U14" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40.35" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B15" s="11" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D15" s="11" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E15" s="11" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G15" s="11" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H15" s="11" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I15" s="11" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J15" s="11" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K15" s="11" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L15" s="11" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M15" s="11" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N15" s="11" t="n"/>
-      <c r="O15" s="11" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q15" s="11" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R15" s="11" t="n"/>
-      <c r="S15" s="11" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T15" s="11" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U15" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E15" s="13" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G15" s="13" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H15" s="13" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I15" s="13" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J15" s="13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K15" s="13" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L15" s="13" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P15" s="13" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q15" s="13" t="n">
+        <v>132</v>
+      </c>
+      <c r="R15" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S15" s="13" t="n">
+        <v>188</v>
+      </c>
+      <c r="T15" s="13" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U15" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40.35" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D16" s="10" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F16" s="10" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G16" s="10" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H16" s="10" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I16" s="10" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J16" s="10" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K16" s="10" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L16" s="10" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M16" s="10" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N16" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" s="10" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P16" s="10" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q16" s="10" t="n">
-        <v>132</v>
-      </c>
-      <c r="R16" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="n">
-        <v>188</v>
-      </c>
-      <c r="T16" s="10" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U16" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>22648.69</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="H16" s="12" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I16" s="12" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="J16" s="12" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K16" s="12" t="n">
+        <v>3583.03</v>
+      </c>
+      <c r="L16" s="12" t="n">
+        <v>3613.35</v>
+      </c>
+      <c r="M16" s="12" t="n">
+        <v>2108.22</v>
+      </c>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="P16" s="12" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="Q16" s="12" t="n">
+        <v>-300.74</v>
+      </c>
+      <c r="R16" s="12" t="n"/>
+      <c r="S16" s="12" t="n">
+        <v>1939.17</v>
+      </c>
+      <c r="T16" s="12" t="n">
+        <v>5001.41</v>
+      </c>
+      <c r="U16" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40.35" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>SoFi Technologies, Inc.</t>
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>22648.69</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>-7.02</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="I17" s="11" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="J17" s="11" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K17" s="11" t="n">
-        <v>3583.03</v>
-      </c>
-      <c r="L17" s="11" t="n">
-        <v>3613.35</v>
-      </c>
-      <c r="M17" s="11" t="n">
-        <v>2108.22</v>
-      </c>
-      <c r="N17" s="11" t="n"/>
-      <c r="O17" s="11" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="P17" s="11" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="Q17" s="11" t="n">
-        <v>-300.74</v>
-      </c>
-      <c r="R17" s="11" t="n"/>
-      <c r="S17" s="11" t="n">
-        <v>1939.17</v>
-      </c>
-      <c r="T17" s="11" t="n">
-        <v>5001.41</v>
-      </c>
-      <c r="U17" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E17" s="13" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G17" s="13" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H17" s="13" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I17" s="13" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J17" s="13" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K17" s="13" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L17" s="13" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N17" s="13" t="n"/>
+      <c r="O17" s="13" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P17" s="13" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q17" s="13" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R17" s="13" t="n"/>
+      <c r="S17" s="13" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T17" s="13" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U17" s="13" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40.35" customHeight="1">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M18" s="10" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N18" s="10" t="n"/>
-      <c r="O18" s="10" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P18" s="10" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q18" s="10" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R18" s="10" t="n"/>
-      <c r="S18" s="10" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T18" s="10" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U18" s="10" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P18" s="12" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q18" s="12" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R18" s="12" t="n"/>
+      <c r="S18" s="12" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T18" s="12" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U18" s="12" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D19" s="11" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E19" s="11" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F19" s="11" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G19" s="11" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H19" s="11" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I19" s="11" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J19" s="11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K19" s="11" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L19" s="11" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N19" s="11" t="n"/>
-      <c r="O19" s="11" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P19" s="11" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q19" s="11" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R19" s="11" t="n"/>
-      <c r="S19" s="11" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T19" s="11" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U19" s="11" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D19" s="13" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E19" s="13" t="n">
         <v>38.7</v>
       </c>
-      <c r="F20" s="10" t="n">
+      <c r="F19" s="13" t="n">
         <v>38.67</v>
       </c>
-      <c r="G20" s="10" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.08</v>
       </c>
-      <c r="H20" s="10" t="n">
+      <c r="H19" s="13" t="n">
         <v>38.8</v>
       </c>
-      <c r="I20" s="10" t="n">
+      <c r="I19" s="13" t="n">
         <v>38.5</v>
       </c>
-      <c r="J20" s="10" t="n"/>
-      <c r="K20" s="10" t="n"/>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="n"/>
-      <c r="N20" s="10" t="n"/>
-      <c r="O20" s="10" t="n"/>
-      <c r="P20" s="10" t="n"/>
-      <c r="Q20" s="10" t="n"/>
-      <c r="R20" s="10" t="n"/>
-      <c r="S20" s="10" t="n"/>
-      <c r="T20" s="10" t="n"/>
-      <c r="U20" s="10" t="inlineStr">
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
+      <c r="N19" s="13" t="n"/>
+      <c r="O19" s="13" t="n"/>
+      <c r="P19" s="13" t="n"/>
+      <c r="Q19" s="13" t="n"/>
+      <c r="R19" s="13" t="n"/>
+      <c r="S19" s="13" t="n"/>
+      <c r="T19" s="13" t="n"/>
+      <c r="U19" s="13" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -495,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -606,12 +612,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="14" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
@@ -621,66 +627,66 @@
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="14" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="14" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="14" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="14" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="14" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="14" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="14" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="14" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="14" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="14" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" s="12" t="n"/>
-      <c r="O2" s="12" t="n">
+      <c r="N2" s="14" t="n"/>
+      <c r="O2" s="14" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" s="12" t="n">
+      <c r="P2" s="14" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" s="12" t="n">
+      <c r="Q2" s="14" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" s="12" t="n"/>
-      <c r="S2" s="12" t="n">
+      <c r="R2" s="14" t="n"/>
+      <c r="S2" s="14" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" s="12" t="n">
+      <c r="T2" s="14" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" s="12" t="inlineStr">
+      <c r="U2" s="14" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="13" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
@@ -690,66 +696,66 @@
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" s="13" t="n">
+      <c r="D3" s="15" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E3" s="13" t="n">
+      <c r="E3" s="15" t="n">
         <v>200.21</v>
       </c>
-      <c r="F3" s="13" t="n">
+      <c r="F3" s="15" t="n">
         <v>203.68</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="15" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="15" t="n">
         <v>201.88</v>
       </c>
-      <c r="I3" s="13" t="n">
+      <c r="I3" s="15" t="n">
         <v>197.74</v>
       </c>
-      <c r="J3" s="13" t="n">
+      <c r="J3" s="15" t="n">
         <v>2.6</v>
       </c>
-      <c r="K3" s="13" t="n">
+      <c r="K3" s="15" t="n">
         <v>34639</v>
       </c>
-      <c r="L3" s="13" t="n">
+      <c r="L3" s="15" t="n">
         <v>34639</v>
       </c>
-      <c r="M3" s="13" t="n">
+      <c r="M3" s="15" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" s="13" t="n"/>
-      <c r="O3" s="13" t="n">
+      <c r="N3" s="15" t="n"/>
+      <c r="O3" s="15" t="n">
         <v>4269</v>
       </c>
-      <c r="P3" s="13" t="n">
+      <c r="P3" s="15" t="n">
         <v>4335</v>
       </c>
-      <c r="Q3" s="13" t="n">
+      <c r="Q3" s="15" t="n">
         <v>854</v>
       </c>
-      <c r="R3" s="13" t="n"/>
-      <c r="S3" s="13" t="n">
+      <c r="R3" s="15" t="n"/>
+      <c r="S3" s="15" t="n">
         <v>4006</v>
       </c>
-      <c r="T3" s="13" t="n">
+      <c r="T3" s="15" t="n">
         <v>10552</v>
       </c>
-      <c r="U3" s="13" t="inlineStr">
+      <c r="U3" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="12" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" s="12" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -759,66 +765,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D4" s="12" t="n">
+      <c r="D4" s="14" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E4" s="12" t="n">
+      <c r="E4" s="14" t="n">
         <v>210</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="14" t="n">
         <v>207.92</v>
       </c>
-      <c r="G4" s="12" t="n">
+      <c r="G4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="12" t="n">
+      <c r="H4" s="14" t="n">
         <v>210.33</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="14" t="n">
         <v>205.2</v>
       </c>
-      <c r="J4" s="12" t="n">
+      <c r="J4" s="14" t="n">
         <v>7.16</v>
       </c>
-      <c r="K4" s="12" t="n">
+      <c r="K4" s="14" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L4" s="12" t="n">
+      <c r="L4" s="14" t="n">
         <v>716924</v>
       </c>
-      <c r="M4" s="12" t="n">
+      <c r="M4" s="14" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" s="12" t="n"/>
-      <c r="O4" s="12" t="n">
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n">
         <v>77670</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="14" t="n">
         <v>77670</v>
       </c>
-      <c r="Q4" s="12" t="n">
+      <c r="Q4" s="14" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" s="12" t="n"/>
-      <c r="S4" s="12" t="n">
+      <c r="R4" s="14" t="n"/>
+      <c r="S4" s="14" t="n">
         <v>178547</v>
       </c>
-      <c r="T4" s="12" t="n">
+      <c r="T4" s="14" t="n">
         <v>123029</v>
       </c>
-      <c r="U4" s="12" t="inlineStr">
+      <c r="U4" s="14" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
@@ -828,74 +834,74 @@
           <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n">
+      <c r="D5" s="15" t="n">
         <v>1511612.87</v>
       </c>
-      <c r="E5" s="13" t="n">
+      <c r="E5" s="15" t="n">
         <v>318.82</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="15" t="n">
         <v>319.55</v>
       </c>
-      <c r="G5" s="13" t="n">
+      <c r="G5" s="15" t="n">
         <v>-0.23</v>
       </c>
-      <c r="H5" s="13" t="n">
+      <c r="H5" s="15" t="n">
         <v>320.04</v>
       </c>
-      <c r="I5" s="13" t="n">
+      <c r="I5" s="15" t="n">
         <v>307.2</v>
       </c>
-      <c r="J5" s="13" t="n">
+      <c r="J5" s="15" t="n">
         <v>4.76</v>
       </c>
-      <c r="K5" s="13" t="n">
+      <c r="K5" s="15" t="n">
         <v>63887</v>
       </c>
-      <c r="L5" s="13" t="n">
+      <c r="L5" s="15" t="n">
         <v>63887</v>
       </c>
-      <c r="M5" s="13" t="n">
+      <c r="M5" s="15" t="n">
         <v>35819</v>
       </c>
-      <c r="N5" s="13" t="inlineStr">
+      <c r="N5" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O5" s="13" t="n">
+      <c r="O5" s="15" t="n">
         <v>23126</v>
       </c>
-      <c r="P5" s="13" t="n">
+      <c r="P5" s="15" t="n">
         <v>23126</v>
       </c>
-      <c r="Q5" s="13" t="n">
+      <c r="Q5" s="15" t="n">
         <v>14082</v>
       </c>
-      <c r="R5" s="13" t="inlineStr">
+      <c r="R5" s="15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S5" s="13" t="n">
+      <c r="S5" s="15" t="n">
         <v>40457</v>
       </c>
-      <c r="T5" s="13" t="n">
+      <c r="T5" s="15" t="n">
         <v>11105</v>
       </c>
-      <c r="U5" s="13" t="inlineStr">
+      <c r="U5" s="15" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -905,48 +911,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="14" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="14" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="14" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="14" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="14" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="14" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" s="12" t="n"/>
-      <c r="K6" s="12" t="n"/>
-      <c r="L6" s="12" t="n"/>
-      <c r="M6" s="12" t="n"/>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="12" t="n"/>
-      <c r="P6" s="12" t="n"/>
-      <c r="Q6" s="12" t="n"/>
-      <c r="R6" s="12" t="n"/>
-      <c r="S6" s="12" t="n"/>
-      <c r="T6" s="12" t="n"/>
-      <c r="U6" s="12" t="inlineStr">
+      <c r="J6" s="14" t="n"/>
+      <c r="K6" s="14" t="n"/>
+      <c r="L6" s="14" t="n"/>
+      <c r="M6" s="14" t="n"/>
+      <c r="N6" s="14" t="n"/>
+      <c r="O6" s="14" t="n"/>
+      <c r="P6" s="14" t="n"/>
+      <c r="Q6" s="14" t="n"/>
+      <c r="R6" s="14" t="n"/>
+      <c r="S6" s="14" t="n"/>
+      <c r="T6" s="14" t="n"/>
+      <c r="U6" s="14" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -956,66 +962,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="15" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="15" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="15" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="15" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="15" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="15" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="15" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="15" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="15" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="15" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" s="13" t="n"/>
-      <c r="O7" s="13" t="n">
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="15" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" s="13" t="n">
+      <c r="Q7" s="15" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" s="13" t="n"/>
-      <c r="S7" s="13" t="n">
+      <c r="R7" s="15" t="n"/>
+      <c r="S7" s="15" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" s="13" t="n">
+      <c r="T7" s="15" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" s="13" t="inlineStr">
+      <c r="U7" s="15" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
@@ -1025,827 +1031,750 @@
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="14" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="E8" s="14" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="14" t="n">
         <v>79.45</v>
       </c>
-      <c r="G8" s="12" t="n">
+      <c r="G8" s="14" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H8" s="12" t="n">
+      <c r="H8" s="14" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I8" s="12" t="n">
+      <c r="I8" s="14" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J8" s="12" t="n">
+      <c r="J8" s="14" t="n">
         <v>2.05</v>
       </c>
-      <c r="K8" s="12" t="n">
+      <c r="K8" s="14" t="n">
         <v>4473</v>
       </c>
-      <c r="L8" s="12" t="n">
+      <c r="L8" s="14" t="n">
         <v>4473</v>
       </c>
-      <c r="M8" s="12" t="n">
+      <c r="M8" s="14" t="n">
         <v>1865</v>
       </c>
-      <c r="N8" s="12" t="inlineStr">
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="12" t="n">
+      <c r="O8" s="14" t="n">
         <v>1883</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="14" t="n">
         <v>1883</v>
       </c>
-      <c r="Q8" s="12" t="n">
+      <c r="Q8" s="14" t="n">
         <v>-541</v>
       </c>
-      <c r="R8" s="12" t="inlineStr">
+      <c r="R8" s="14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="12" t="n">
+      <c r="S8" s="14" t="n">
         <v>12449</v>
       </c>
-      <c r="T8" s="12" t="n">
+      <c r="T8" s="14" t="n">
         <v>12646</v>
       </c>
-      <c r="U8" s="12" t="inlineStr">
+      <c r="U8" s="14" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>K.TO</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Kinross Gold Corporation</t>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Kinross Gold Corporation, together with its subsidiaries, engages in the acquisition, exploration, and development of gold properties principally in the United States, Brazil, Chile, Canada, and Mauritania. It is also involved in the extraction and processing of gold-containing ores; reclamation of gold mining properties; and production and sale of silver. The company was founded in 1993 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>60705.06</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>50.29</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>49.05</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="L9" s="13" t="n">
-        <v>7051.1</v>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>4239.7</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="13" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="P9" s="13" t="n">
-        <v>2390.1</v>
-      </c>
-      <c r="Q9" s="13" t="n">
-        <v>416.3</v>
-      </c>
-      <c r="R9" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="13" t="n">
-        <v>758.5</v>
-      </c>
-      <c r="T9" s="13" t="n">
-        <v>1761.7</v>
-      </c>
-      <c r="U9" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-02 16:46:56</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>2918992.05</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>390</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M9" s="15" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q9" s="15" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R9" s="15" t="n"/>
+      <c r="S9" s="15" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T9" s="15" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U9" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
+      <c r="A10" s="14" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
-        </is>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>2918992.05</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>392.74</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>401.72</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>390</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>305453.01</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>281724</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n">
-        <v>119262</v>
-      </c>
-      <c r="P10" s="12" t="n">
-        <v>101832</v>
-      </c>
-      <c r="Q10" s="12" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R10" s="12" t="n"/>
-      <c r="S10" s="12" t="n">
-        <v>123278</v>
-      </c>
-      <c r="T10" s="12" t="n">
-        <v>89462</v>
-      </c>
-      <c r="U10" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>464463.92</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>412.67</v>
+      </c>
+      <c r="F10" s="14" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="G10" s="14" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>417.61</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>397.0101</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>42312</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>37378</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>15540</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="n">
+        <v>11909</v>
+      </c>
+      <c r="P10" s="14" t="n">
+        <v>8539</v>
+      </c>
+      <c r="Q10" s="14" t="n">
+        <v>-5833</v>
+      </c>
+      <c r="R10" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="14" t="n">
+        <v>12493</v>
+      </c>
+      <c r="T10" s="14" t="n">
+        <v>10318</v>
+      </c>
+      <c r="U10" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>464463.92</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>412.67</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>417.61</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>397.0101</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>42312</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>37378</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>15540</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>11909</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>8539</v>
-      </c>
-      <c r="Q11" s="13" t="n">
-        <v>-5833</v>
-      </c>
-      <c r="R11" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="13" t="n">
-        <v>12493</v>
-      </c>
-      <c r="T11" s="13" t="n">
-        <v>10318</v>
-      </c>
-      <c r="U11" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:28:51</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>408239.44</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>84.607</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="L11" s="15" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="M11" s="15" t="n">
+        <v>33723.3</v>
+      </c>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="P11" s="15" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="Q11" s="15" t="n">
+        <v>5407.99</v>
+      </c>
+      <c r="R11" s="15" t="n"/>
+      <c r="S11" s="15" t="n">
+        <v>16975.84</v>
+      </c>
+      <c r="T11" s="15" t="n">
+        <v>9062.360000000001</v>
+      </c>
+      <c r="U11" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
+      <c r="A12" s="14" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q12" s="12" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R12" s="12" t="n"/>
-      <c r="S12" s="12" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T12" s="12" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U12" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F12" s="14" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P12" s="14" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q12" s="14" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R12" s="14" t="n"/>
+      <c r="S12" s="14" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T12" s="14" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U12" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E13" s="13" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H13" s="13" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I13" s="13" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J13" s="13" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K13" s="13" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N13" s="13" t="n"/>
-      <c r="O13" s="13" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R13" s="13" t="n"/>
-      <c r="S13" s="13" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T13" s="13" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U13" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
+        <v>328113.98</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>133.99</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q13" s="15" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R13" s="15" t="n"/>
+      <c r="S13" s="15" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T13" s="15" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U13" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40.35" customHeight="1">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I14" s="12" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K14" s="12" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L14" s="12" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M14" s="12" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N14" s="12" t="n"/>
-      <c r="O14" s="12" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P14" s="12" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q14" s="12" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R14" s="12" t="n"/>
-      <c r="S14" s="12" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T14" s="12" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U14" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E14" s="14" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F14" s="14" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J14" s="14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K14" s="14" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L14" s="14" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M14" s="14" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N14" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P14" s="14" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q14" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="R14" s="14" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S14" s="14" t="n">
+        <v>188</v>
+      </c>
+      <c r="T14" s="14" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U14" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40.35" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc.</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N15" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q15" s="13" t="n">
-        <v>132</v>
-      </c>
-      <c r="R15" s="13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S15" s="13" t="n">
-        <v>188</v>
-      </c>
-      <c r="T15" s="13" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U15" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>22648.69</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="G15" s="15" t="n">
+        <v>-7.02</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>18.21</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>17.31</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>3583.03</v>
+      </c>
+      <c r="L15" s="15" t="n">
+        <v>3613.35</v>
+      </c>
+      <c r="M15" s="15" t="n">
+        <v>2108.22</v>
+      </c>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="P15" s="15" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="Q15" s="15" t="n">
+        <v>-300.74</v>
+      </c>
+      <c r="R15" s="15" t="n"/>
+      <c r="S15" s="15" t="n">
+        <v>1939.17</v>
+      </c>
+      <c r="T15" s="15" t="n">
+        <v>5001.41</v>
+      </c>
+      <c r="U15" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-01 18:33:42</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40.35" customHeight="1">
-      <c r="A16" s="12" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>SoFi Technologies, Inc.</t>
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
-        </is>
-      </c>
-      <c r="D16" s="12" t="n">
-        <v>22648.69</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>-7.02</v>
-      </c>
-      <c r="H16" s="12" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="I16" s="12" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="J16" s="12" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K16" s="12" t="n">
-        <v>3583.03</v>
-      </c>
-      <c r="L16" s="12" t="n">
-        <v>3613.35</v>
-      </c>
-      <c r="M16" s="12" t="n">
-        <v>2108.22</v>
-      </c>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="P16" s="12" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="Q16" s="12" t="n">
-        <v>-300.74</v>
-      </c>
-      <c r="R16" s="12" t="n"/>
-      <c r="S16" s="12" t="n">
-        <v>1939.17</v>
-      </c>
-      <c r="T16" s="12" t="n">
-        <v>5001.41</v>
-      </c>
-      <c r="U16" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E16" s="14" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F16" s="14" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L16" s="14" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M16" s="14" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P16" s="14" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q16" s="14" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R16" s="14" t="n"/>
+      <c r="S16" s="14" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T16" s="14" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U16" s="14" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40.35" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q17" s="13" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R17" s="13" t="n"/>
-      <c r="S17" s="13" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T17" s="13" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U17" s="13" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I17" s="15" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K17" s="15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L17" s="15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M17" s="15" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P17" s="15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q17" s="15" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R17" s="15" t="n"/>
+      <c r="S17" s="15" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T17" s="15" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U17" s="15" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="18" ht="40.35" customHeight="1">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A18" s="14" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H18" s="12" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I18" s="12" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J18" s="12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K18" s="12" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L18" s="12" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M18" s="12" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P18" s="12" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q18" s="12" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R18" s="12" t="n"/>
-      <c r="S18" s="12" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T18" s="12" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U18" s="12" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C19" s="9" t="inlineStr">
-        <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>38.7</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <v>38.67</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G18" s="14" t="n">
         <v>0.08</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H18" s="14" t="n">
         <v>38.8</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I18" s="14" t="n">
         <v>38.5</v>
       </c>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="13" t="n"/>
-      <c r="L19" s="13" t="n"/>
-      <c r="M19" s="13" t="n"/>
-      <c r="N19" s="13" t="n"/>
-      <c r="O19" s="13" t="n"/>
-      <c r="P19" s="13" t="n"/>
-      <c r="Q19" s="13" t="n"/>
-      <c r="R19" s="13" t="n"/>
-      <c r="S19" s="13" t="n"/>
-      <c r="T19" s="13" t="n"/>
-      <c r="U19" s="13" t="inlineStr">
+      <c r="J18" s="14" t="n"/>
+      <c r="K18" s="14" t="n"/>
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+      <c r="R18" s="14" t="n"/>
+      <c r="S18" s="14" t="n"/>
+      <c r="T18" s="14" t="n"/>
+      <c r="U18" s="14" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -501,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U18"/>
+  <dimension ref="A1:U17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -612,12 +618,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" s="14" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
@@ -627,66 +633,66 @@
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="16" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="16" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="16" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" s="14" t="n">
+      <c r="G2" s="16" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" s="14" t="n">
+      <c r="H2" s="16" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="16" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="16" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="K2" s="16" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" s="14" t="n">
+      <c r="L2" s="16" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" s="14" t="n">
+      <c r="M2" s="16" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" s="14" t="n"/>
-      <c r="O2" s="14" t="n">
+      <c r="N2" s="16" t="n"/>
+      <c r="O2" s="16" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" s="14" t="n">
+      <c r="P2" s="16" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" s="14" t="n">
+      <c r="Q2" s="16" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" s="14" t="n"/>
-      <c r="S2" s="14" t="n">
+      <c r="R2" s="16" t="n"/>
+      <c r="S2" s="16" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" s="14" t="n">
+      <c r="T2" s="16" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" s="14" t="inlineStr">
+      <c r="U2" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>AMD</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Advanced Micro Devices, Inc.</t>
         </is>
@@ -696,66 +702,66 @@
           <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" s="15" t="n">
+      <c r="D3" s="17" t="n">
         <v>326424.56</v>
       </c>
-      <c r="E3" s="15" t="n">
+      <c r="E3" s="17" t="n">
         <v>200.21</v>
       </c>
-      <c r="F3" s="15" t="n">
+      <c r="F3" s="17" t="n">
         <v>203.68</v>
       </c>
-      <c r="G3" s="15" t="n">
+      <c r="G3" s="17" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H3" s="15" t="n">
+      <c r="H3" s="17" t="n">
         <v>201.88</v>
       </c>
-      <c r="I3" s="15" t="n">
+      <c r="I3" s="17" t="n">
         <v>197.74</v>
       </c>
-      <c r="J3" s="15" t="n">
+      <c r="J3" s="17" t="n">
         <v>2.6</v>
       </c>
-      <c r="K3" s="15" t="n">
+      <c r="K3" s="17" t="n">
         <v>34639</v>
       </c>
-      <c r="L3" s="15" t="n">
+      <c r="L3" s="17" t="n">
         <v>34639</v>
       </c>
-      <c r="M3" s="15" t="n">
+      <c r="M3" s="17" t="n">
         <v>22680</v>
       </c>
-      <c r="N3" s="15" t="n"/>
-      <c r="O3" s="15" t="n">
+      <c r="N3" s="17" t="n"/>
+      <c r="O3" s="17" t="n">
         <v>4269</v>
       </c>
-      <c r="P3" s="15" t="n">
+      <c r="P3" s="17" t="n">
         <v>4335</v>
       </c>
-      <c r="Q3" s="15" t="n">
+      <c r="Q3" s="17" t="n">
         <v>854</v>
       </c>
-      <c r="R3" s="15" t="n"/>
-      <c r="S3" s="15" t="n">
+      <c r="R3" s="17" t="n"/>
+      <c r="S3" s="17" t="n">
         <v>4006</v>
       </c>
-      <c r="T3" s="15" t="n">
+      <c r="T3" s="17" t="n">
         <v>10552</v>
       </c>
-      <c r="U3" s="15" t="inlineStr">
+      <c r="U3" s="17" t="inlineStr">
         <is>
           <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -765,66 +771,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
+      <c r="D4" s="16" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E4" s="14" t="n">
+      <c r="E4" s="16" t="n">
         <v>210</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="16" t="n">
         <v>207.92</v>
       </c>
-      <c r="G4" s="14" t="n">
+      <c r="G4" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="14" t="n">
+      <c r="H4" s="16" t="n">
         <v>210.33</v>
       </c>
-      <c r="I4" s="14" t="n">
+      <c r="I4" s="16" t="n">
         <v>205.2</v>
       </c>
-      <c r="J4" s="14" t="n">
+      <c r="J4" s="16" t="n">
         <v>7.16</v>
       </c>
-      <c r="K4" s="14" t="n">
+      <c r="K4" s="16" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L4" s="14" t="n">
+      <c r="L4" s="16" t="n">
         <v>716924</v>
       </c>
-      <c r="M4" s="14" t="n">
+      <c r="M4" s="16" t="n">
         <v>574785</v>
       </c>
-      <c r="N4" s="14" t="n"/>
-      <c r="O4" s="14" t="n">
+      <c r="N4" s="16" t="n"/>
+      <c r="O4" s="16" t="n">
         <v>77670</v>
       </c>
-      <c r="P4" s="14" t="n">
+      <c r="P4" s="16" t="n">
         <v>77670</v>
       </c>
-      <c r="Q4" s="14" t="n">
+      <c r="Q4" s="16" t="n">
         <v>30425</v>
       </c>
-      <c r="R4" s="14" t="n"/>
-      <c r="S4" s="14" t="n">
+      <c r="R4" s="16" t="n"/>
+      <c r="S4" s="16" t="n">
         <v>178547</v>
       </c>
-      <c r="T4" s="14" t="n">
+      <c r="T4" s="16" t="n">
         <v>123029</v>
       </c>
-      <c r="U4" s="14" t="inlineStr">
+      <c r="U4" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>AVGO</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>Broadcom Inc.</t>
         </is>
@@ -834,74 +840,74 @@
           <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
         </is>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="17" t="n">
         <v>1511612.87</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="17" t="n">
         <v>318.82</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="17" t="n">
         <v>319.55</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="17" t="n">
         <v>-0.23</v>
       </c>
-      <c r="H5" s="15" t="n">
+      <c r="H5" s="17" t="n">
         <v>320.04</v>
       </c>
-      <c r="I5" s="15" t="n">
+      <c r="I5" s="17" t="n">
         <v>307.2</v>
       </c>
-      <c r="J5" s="15" t="n">
+      <c r="J5" s="17" t="n">
         <v>4.76</v>
       </c>
-      <c r="K5" s="15" t="n">
+      <c r="K5" s="17" t="n">
         <v>63887</v>
       </c>
-      <c r="L5" s="15" t="n">
+      <c r="L5" s="17" t="n">
         <v>63887</v>
       </c>
-      <c r="M5" s="15" t="n">
+      <c r="M5" s="17" t="n">
         <v>35819</v>
       </c>
-      <c r="N5" s="15" t="inlineStr">
+      <c r="N5" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O5" s="15" t="n">
+      <c r="O5" s="17" t="n">
         <v>23126</v>
       </c>
-      <c r="P5" s="15" t="n">
+      <c r="P5" s="17" t="n">
         <v>23126</v>
       </c>
-      <c r="Q5" s="15" t="n">
+      <c r="Q5" s="17" t="n">
         <v>14082</v>
       </c>
-      <c r="R5" s="15" t="inlineStr">
+      <c r="R5" s="17" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S5" s="15" t="n">
+      <c r="S5" s="17" t="n">
         <v>40457</v>
       </c>
-      <c r="T5" s="15" t="n">
+      <c r="T5" s="17" t="n">
         <v>11105</v>
       </c>
-      <c r="U5" s="15" t="inlineStr">
+      <c r="U5" s="17" t="inlineStr">
         <is>
           <t>2026-03-02 16:46:42</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -911,48 +917,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="16" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="16" t="n">
         <v>9.77</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="16" t="n">
         <v>9.91</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="16" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="16" t="n">
         <v>9.91</v>
       </c>
-      <c r="I6" s="14" t="n">
+      <c r="I6" s="16" t="n">
         <v>9.74</v>
       </c>
-      <c r="J6" s="14" t="n"/>
-      <c r="K6" s="14" t="n"/>
-      <c r="L6" s="14" t="n"/>
-      <c r="M6" s="14" t="n"/>
-      <c r="N6" s="14" t="n"/>
-      <c r="O6" s="14" t="n"/>
-      <c r="P6" s="14" t="n"/>
-      <c r="Q6" s="14" t="n"/>
-      <c r="R6" s="14" t="n"/>
-      <c r="S6" s="14" t="n"/>
-      <c r="T6" s="14" t="n"/>
-      <c r="U6" s="14" t="inlineStr">
+      <c r="J6" s="16" t="n"/>
+      <c r="K6" s="16" t="n"/>
+      <c r="L6" s="16" t="n"/>
+      <c r="M6" s="16" t="n"/>
+      <c r="N6" s="16" t="n"/>
+      <c r="O6" s="16" t="n"/>
+      <c r="P6" s="16" t="n"/>
+      <c r="Q6" s="16" t="n"/>
+      <c r="R6" s="16" t="n"/>
+      <c r="S6" s="16" t="n"/>
+      <c r="T6" s="16" t="n"/>
+      <c r="U6" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="17" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -962,66 +968,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="17" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="17" t="n">
         <v>311.76</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="17" t="n">
         <v>307.38</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="17" t="n">
         <v>1.42</v>
       </c>
-      <c r="H7" s="15" t="n">
+      <c r="H7" s="17" t="n">
         <v>312.37</v>
       </c>
-      <c r="I7" s="15" t="n">
+      <c r="I7" s="17" t="n">
         <v>303.8</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="17" t="n">
         <v>10.82</v>
       </c>
-      <c r="K7" s="15" t="n">
+      <c r="K7" s="17" t="n">
         <v>402836</v>
       </c>
-      <c r="L7" s="15" t="n">
+      <c r="L7" s="17" t="n">
         <v>402836</v>
       </c>
-      <c r="M7" s="15" t="n">
+      <c r="M7" s="17" t="n">
         <v>307394</v>
       </c>
-      <c r="N7" s="15" t="n"/>
-      <c r="O7" s="15" t="n">
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n">
         <v>132170</v>
       </c>
-      <c r="P7" s="15" t="n">
+      <c r="P7" s="17" t="n">
         <v>132170</v>
       </c>
-      <c r="Q7" s="15" t="n">
+      <c r="Q7" s="17" t="n">
         <v>73795</v>
       </c>
-      <c r="R7" s="15" t="n"/>
-      <c r="S7" s="15" t="n">
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n">
         <v>66996</v>
       </c>
-      <c r="T7" s="15" t="n">
+      <c r="T7" s="17" t="n">
         <v>126843</v>
       </c>
-      <c r="U7" s="15" t="inlineStr">
+      <c r="U7" s="17" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
@@ -1031,74 +1037,74 @@
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="16" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="16" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="16" t="n">
         <v>79.45</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="16" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="16" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="16" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="16" t="n">
         <v>2.05</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="16" t="n">
         <v>4473</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="16" t="n">
         <v>4473</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="16" t="n">
         <v>1865</v>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="16" t="n">
         <v>1883</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="16" t="n">
         <v>1883</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="Q8" s="16" t="n">
         <v>-541</v>
       </c>
-      <c r="R8" s="14" t="inlineStr">
+      <c r="R8" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="14" t="n">
+      <c r="S8" s="16" t="n">
         <v>12449</v>
       </c>
-      <c r="T8" s="14" t="n">
+      <c r="T8" s="16" t="n">
         <v>12646</v>
       </c>
-      <c r="U8" s="14" t="inlineStr">
+      <c r="U8" s="16" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -1108,66 +1114,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="17" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="17" t="n">
         <v>392.74</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="17" t="n">
         <v>401.72</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="17" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H9" s="15" t="n">
+      <c r="H9" s="17" t="n">
         <v>396.8</v>
       </c>
-      <c r="I9" s="15" t="n">
+      <c r="I9" s="17" t="n">
         <v>390</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="17" t="n">
         <v>15.98</v>
       </c>
-      <c r="K9" s="15" t="n">
+      <c r="K9" s="17" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L9" s="15" t="n">
+      <c r="L9" s="17" t="n">
         <v>281724</v>
       </c>
-      <c r="M9" s="15" t="n">
+      <c r="M9" s="17" t="n">
         <v>211915</v>
       </c>
-      <c r="N9" s="15" t="n"/>
-      <c r="O9" s="15" t="n">
+      <c r="N9" s="17" t="n"/>
+      <c r="O9" s="17" t="n">
         <v>119262</v>
       </c>
-      <c r="P9" s="15" t="n">
+      <c r="P9" s="17" t="n">
         <v>101832</v>
       </c>
-      <c r="Q9" s="15" t="n">
+      <c r="Q9" s="17" t="n">
         <v>72361</v>
       </c>
-      <c r="R9" s="15" t="n"/>
-      <c r="S9" s="15" t="n">
+      <c r="R9" s="17" t="n"/>
+      <c r="S9" s="17" t="n">
         <v>123278</v>
       </c>
-      <c r="T9" s="15" t="n">
+      <c r="T9" s="17" t="n">
         <v>89462</v>
       </c>
-      <c r="U9" s="15" t="inlineStr">
+      <c r="U9" s="17" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
@@ -1177,74 +1183,74 @@
           <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="16" t="n">
         <v>464463.92</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="16" t="n">
         <v>412.67</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="16" t="n">
         <v>412.37</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="16" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="16" t="n">
         <v>417.61</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="16" t="n">
         <v>397.0101</v>
       </c>
-      <c r="J10" s="14" t="n">
+      <c r="J10" s="16" t="n">
         <v>10.52</v>
       </c>
-      <c r="K10" s="14" t="n">
+      <c r="K10" s="16" t="n">
         <v>42312</v>
       </c>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="16" t="n">
         <v>37378</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="16" t="n">
         <v>15540</v>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O10" s="14" t="n">
+      <c r="O10" s="16" t="n">
         <v>11909</v>
       </c>
-      <c r="P10" s="14" t="n">
+      <c r="P10" s="16" t="n">
         <v>8539</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="Q10" s="16" t="n">
         <v>-5833</v>
       </c>
-      <c r="R10" s="14" t="inlineStr">
+      <c r="R10" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S10" s="14" t="n">
+      <c r="S10" s="16" t="n">
         <v>12493</v>
       </c>
-      <c r="T10" s="14" t="n">
+      <c r="T10" s="16" t="n">
         <v>10318</v>
       </c>
-      <c r="U10" s="14" t="inlineStr">
+      <c r="U10" s="16" t="inlineStr">
         <is>
           <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -1254,66 +1260,66 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="17" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="17" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="17" t="n">
         <v>84.607</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="17" t="n">
         <v>13.75</v>
       </c>
-      <c r="H11" s="15" t="n">
+      <c r="H11" s="17" t="n">
         <v>96.75</v>
       </c>
-      <c r="I11" s="15" t="n">
+      <c r="I11" s="17" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="17" t="n">
         <v>2.53</v>
       </c>
-      <c r="K11" s="15" t="n">
+      <c r="K11" s="17" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L11" s="15" t="n">
+      <c r="L11" s="17" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M11" s="15" t="n">
+      <c r="M11" s="17" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N11" s="15" t="n"/>
-      <c r="O11" s="15" t="n">
+      <c r="N11" s="17" t="n"/>
+      <c r="O11" s="17" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P11" s="15" t="n">
+      <c r="P11" s="17" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q11" s="15" t="n">
+      <c r="Q11" s="17" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="15" t="n">
+      <c r="R11" s="17" t="n"/>
+      <c r="S11" s="17" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T11" s="15" t="n">
+      <c r="T11" s="17" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U11" s="15" t="inlineStr">
+      <c r="U11" s="17" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B12" s="14" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -1323,66 +1329,66 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="16" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="16" t="n">
         <v>177.19</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="16" t="n">
         <v>184.89</v>
       </c>
-      <c r="G12" s="14" t="n">
+      <c r="G12" s="16" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H12" s="14" t="n">
+      <c r="H12" s="16" t="n">
         <v>182.58</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="16" t="n">
         <v>176.38</v>
       </c>
-      <c r="J12" s="14" t="n">
+      <c r="J12" s="16" t="n">
         <v>4.91</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="16" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L12" s="14" t="n">
+      <c r="L12" s="16" t="n">
         <v>215938</v>
       </c>
-      <c r="M12" s="14" t="n">
+      <c r="M12" s="16" t="n">
         <v>60922</v>
       </c>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="14" t="n">
+      <c r="N12" s="16" t="n"/>
+      <c r="O12" s="16" t="n">
         <v>120067</v>
       </c>
-      <c r="P12" s="14" t="n">
+      <c r="P12" s="16" t="n">
         <v>120067</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="16" t="n">
         <v>29760</v>
       </c>
-      <c r="R12" s="14" t="n"/>
-      <c r="S12" s="14" t="n">
+      <c r="R12" s="16" t="n"/>
+      <c r="S12" s="16" t="n">
         <v>11412</v>
       </c>
-      <c r="T12" s="14" t="n">
+      <c r="T12" s="16" t="n">
         <v>62556</v>
       </c>
-      <c r="U12" s="14" t="inlineStr">
+      <c r="U12" s="16" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc.</t>
         </is>
@@ -1392,66 +1398,66 @@
           <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="17" t="n">
         <v>328113.98</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="17" t="n">
         <v>137.19</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="17" t="n">
         <v>135.94</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="17" t="n">
         <v>0.92</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="17" t="n">
         <v>138.1</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="17" t="n">
         <v>133.99</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="17" t="n">
         <v>0.63</v>
       </c>
-      <c r="K13" s="15" t="n">
+      <c r="K13" s="17" t="n">
         <v>4475.45</v>
       </c>
-      <c r="L13" s="15" t="n">
+      <c r="L13" s="17" t="n">
         <v>4475.45</v>
       </c>
-      <c r="M13" s="15" t="n">
+      <c r="M13" s="17" t="n">
         <v>2225.01</v>
       </c>
-      <c r="N13" s="15" t="n"/>
-      <c r="O13" s="15" t="n">
+      <c r="N13" s="17" t="n"/>
+      <c r="O13" s="17" t="n">
         <v>1625.03</v>
       </c>
-      <c r="P13" s="15" t="n">
+      <c r="P13" s="17" t="n">
         <v>1625.03</v>
       </c>
-      <c r="Q13" s="15" t="n">
+      <c r="Q13" s="17" t="n">
         <v>209.82</v>
       </c>
-      <c r="R13" s="15" t="n"/>
-      <c r="S13" s="15" t="n">
+      <c r="R13" s="17" t="n"/>
+      <c r="S13" s="17" t="n">
         <v>229.34</v>
       </c>
-      <c r="T13" s="15" t="n">
+      <c r="T13" s="17" t="n">
         <v>7177.04</v>
       </c>
-      <c r="U13" s="15" t="inlineStr">
+      <c r="U13" s="17" t="inlineStr">
         <is>
           <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="14" ht="40.35" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>SHOP.TO</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>Shopify Inc.</t>
         </is>
@@ -1461,325 +1467,257 @@
           <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
         </is>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="16" t="n">
         <v>213981.48</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="16" t="n">
         <v>163.32</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="16" t="n">
         <v>164.67</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="16" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="16" t="n">
         <v>164.76</v>
       </c>
-      <c r="I14" s="14" t="n">
+      <c r="I14" s="16" t="n">
         <v>156.66</v>
       </c>
-      <c r="J14" s="14" t="n">
+      <c r="J14" s="16" t="n">
         <v>1.28</v>
       </c>
-      <c r="K14" s="14" t="n">
+      <c r="K14" s="16" t="n">
         <v>11556</v>
       </c>
-      <c r="L14" s="14" t="n">
+      <c r="L14" s="16" t="n">
         <v>11556</v>
       </c>
-      <c r="M14" s="14" t="n">
+      <c r="M14" s="16" t="n">
         <v>7060</v>
       </c>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O14" s="14" t="n">
+      <c r="O14" s="16" t="n">
         <v>1231</v>
       </c>
-      <c r="P14" s="14" t="n">
+      <c r="P14" s="16" t="n">
         <v>1231</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="16" t="n">
         <v>132</v>
       </c>
-      <c r="R14" s="14" t="inlineStr">
+      <c r="R14" s="16" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S14" s="14" t="n">
+      <c r="S14" s="16" t="n">
         <v>188</v>
       </c>
-      <c r="T14" s="14" t="n">
+      <c r="T14" s="16" t="n">
         <v>5847</v>
       </c>
-      <c r="U14" s="14" t="inlineStr">
+      <c r="U14" s="16" t="inlineStr">
         <is>
           <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40.35" customHeight="1">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>SoFi Technologies, Inc.</t>
+      <c r="A15" s="17" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>22648.69</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>17.76</v>
-      </c>
-      <c r="F15" s="15" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="G15" s="15" t="n">
-        <v>-7.02</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>18.21</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>17.31</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>3583.03</v>
-      </c>
-      <c r="L15" s="15" t="n">
-        <v>3613.35</v>
-      </c>
-      <c r="M15" s="15" t="n">
-        <v>2108.22</v>
-      </c>
-      <c r="N15" s="15" t="n"/>
-      <c r="O15" s="15" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="P15" s="15" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="Q15" s="15" t="n">
-        <v>-300.74</v>
-      </c>
-      <c r="R15" s="15" t="n"/>
-      <c r="S15" s="15" t="n">
-        <v>1939.17</v>
-      </c>
-      <c r="T15" s="15" t="n">
-        <v>5001.41</v>
-      </c>
-      <c r="U15" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-01 18:33:42</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G15" s="17" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N15" s="17" t="n"/>
+      <c r="O15" s="17" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P15" s="17" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q15" s="17" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R15" s="17" t="n"/>
+      <c r="S15" s="17" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T15" s="17" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U15" s="17" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="16" ht="40.35" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E16" s="14" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F16" s="14" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L16" s="14" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P16" s="14" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q16" s="14" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R16" s="14" t="n"/>
-      <c r="S16" s="14" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T16" s="14" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U16" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E16" s="16" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F16" s="16" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G16" s="16" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H16" s="16" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I16" s="16" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J16" s="16" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K16" s="16" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L16" s="16" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M16" s="16" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P16" s="16" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q16" s="16" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R16" s="16" t="n"/>
+      <c r="S16" s="16" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T16" s="16" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U16" s="16" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="17" ht="40.35" customHeight="1">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L17" s="15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M17" s="15" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N17" s="15" t="n"/>
-      <c r="O17" s="15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P17" s="15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q17" s="15" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R17" s="15" t="n"/>
-      <c r="S17" s="15" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T17" s="15" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U17" s="15" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D17" s="17" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F17" s="17" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G17" s="17" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H17" s="17" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J17" s="17" t="n"/>
+      <c r="K17" s="17" t="n"/>
+      <c r="L17" s="17" t="n"/>
+      <c r="M17" s="17" t="n"/>
+      <c r="N17" s="17" t="n"/>
+      <c r="O17" s="17" t="n"/>
+      <c r="P17" s="17" t="n"/>
+      <c r="Q17" s="17" t="n"/>
+      <c r="R17" s="17" t="n"/>
+      <c r="S17" s="17" t="n"/>
+      <c r="T17" s="17" t="n"/>
+      <c r="U17" s="17" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="40.35" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D18" s="14" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E18" s="14" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F18" s="14" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H18" s="14" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I18" s="14" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J18" s="14" t="n"/>
-      <c r="K18" s="14" t="n"/>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-      <c r="R18" s="14" t="n"/>
-      <c r="S18" s="14" t="n"/>
-      <c r="T18" s="14" t="n"/>
-      <c r="U18" s="14" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="18" ht="40.35" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -607,138 +607,138 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Advanced Micro Devices, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
+          <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2254333.28</v>
+        <v>326424.56</v>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>200.21</v>
       </c>
       <c r="F3" t="n">
-        <v>207.92</v>
+        <v>203.68</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>-1.7</v>
       </c>
       <c r="H3" t="n">
-        <v>210.33</v>
+        <v>201.88</v>
       </c>
       <c r="I3" t="n">
-        <v>205.2</v>
+        <v>197.74</v>
       </c>
       <c r="J3" t="n">
-        <v>7.16</v>
+        <v>2.6</v>
       </c>
       <c r="K3" t="n">
-        <v>716923.99</v>
+        <v>34639</v>
       </c>
       <c r="L3" t="n">
-        <v>716924</v>
+        <v>34639</v>
       </c>
       <c r="M3" t="n">
-        <v>574785</v>
+        <v>22680</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>77670</v>
+        <v>4269</v>
       </c>
       <c r="P3" t="n">
-        <v>77670</v>
+        <v>4335</v>
       </c>
       <c r="Q3" t="n">
-        <v>30425</v>
+        <v>854</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>178547</v>
+        <v>4006</v>
       </c>
       <c r="T3" t="n">
-        <v>123029</v>
+        <v>10552</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-01 18:39:12</t>
+          <t>2026-03-01 16:53:14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AVGO</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Broadcom Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
+          <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1511612.87</v>
+        <v>2254333.28</v>
       </c>
       <c r="E4" t="n">
-        <v>318.82</v>
+        <v>210</v>
       </c>
       <c r="F4" t="n">
-        <v>319.55</v>
+        <v>207.92</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.23</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>320.04</v>
+        <v>210.33</v>
       </c>
       <c r="I4" t="n">
-        <v>307.2</v>
+        <v>205.2</v>
       </c>
       <c r="J4" t="n">
-        <v>4.76</v>
+        <v>7.16</v>
       </c>
       <c r="K4" t="n">
-        <v>63887</v>
+        <v>716923.99</v>
       </c>
       <c r="L4" t="n">
-        <v>63887</v>
+        <v>716924</v>
       </c>
       <c r="M4" t="n">
-        <v>35819</v>
+        <v>574785</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>23126</v>
+        <v>77670</v>
       </c>
       <c r="P4" t="n">
-        <v>23126</v>
+        <v>77670</v>
       </c>
       <c r="Q4" t="n">
-        <v>14082</v>
+        <v>30425</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>40457</v>
+        <v>178547</v>
       </c>
       <c r="T4" t="n">
-        <v>11105</v>
+        <v>123029</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-02 16:46:42</t>
+          <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,928 +607,859 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>AMZN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc.</t>
+          <t>Amazon.com, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices, Inc. operates as a semiconductor company internationally. It operates in three segments: Data Center, Client and Gaming, and Embedded. The company offers artificial intelligence (AI) accelerators, microprocessors, and graphics processing units (GPUs) as standalone devices or as incorporated into accelerated processing units, chipsets, and data center and professional GPUs; and embedded processors and semi-custom system-on-chip (SoC) products, microprocessor and SoC development services and technology, data processing units, field programmable gate arrays (FPGA), system on modules, AI network interface cards, and adaptive SoC products. It provides processors under the AMD Ryzen, AMD Ryzen AI, AMD Ryzen PRO, AMD Ryzen Threadripper, AMD Ryzen Threadripper PRO, AMD Athlon, and AMD PRO A-Series brands; graphics under the AMD Radeon graphics and AMD Embedded Radeon graphics; professional graphics under the AMD Radeon Pro graphics brand; and AI and general-purpose compute infrastructure for hyperscale providers. The company offers data center graphics under the AMD Instinct accelerators and Radeon PRO V-series brands; server microprocessors under the AMD EPYC brand; low power solutions under the AMD Athlon, AMD Geode, AMD Ryzen, AMD EPYC, and AMD R-Series and G-Series brands; FPGA products under the Virtex-6, Virtex-7, Virtex UltraScale+, Kintex-7, Kintex UltraScale, Kintex UltraScale+, Artix-7, Artix UltraScale+, Spartan-6, and Spartan-7 brands; adaptive SOCs under the Zynq-7000, Zynq UltraScale+ MPSoC, Zynq UltraScale+ RFSoCs, Versal HBM, Versal Premium, Versal Prime, Versal AI Core, Versal AI Edge, Vitis, and Vivado brands; and compute and network acceleration board products under the Alveo and Pensando brands. It serves original equipment and design manufacturers, public cloud service providers, system integrators, distributors, and add-in-board manufacturers. The company was incorporated in 1969 and is headquartered in Santa Clara, California.</t>
+          <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>326424.56</v>
+        <v>2254333.28</v>
       </c>
       <c r="E3" t="n">
-        <v>200.21</v>
+        <v>210</v>
       </c>
       <c r="F3" t="n">
-        <v>203.68</v>
+        <v>207.92</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.7</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>201.88</v>
+        <v>210.33</v>
       </c>
       <c r="I3" t="n">
-        <v>197.74</v>
+        <v>205.2</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6</v>
+        <v>7.16</v>
       </c>
       <c r="K3" t="n">
-        <v>34639</v>
+        <v>716923.99</v>
       </c>
       <c r="L3" t="n">
-        <v>34639</v>
+        <v>716924</v>
       </c>
       <c r="M3" t="n">
-        <v>22680</v>
+        <v>574785</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>4269</v>
+        <v>77670</v>
       </c>
       <c r="P3" t="n">
-        <v>4335</v>
+        <v>77670</v>
       </c>
       <c r="Q3" t="n">
-        <v>854</v>
+        <v>30425</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>4006</v>
+        <v>178547</v>
       </c>
       <c r="T3" t="n">
-        <v>10552</v>
+        <v>123029</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-01 16:53:14</t>
+          <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>BANK.TO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
+          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2254333.28</v>
+        <v>882.9299999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>9.77</v>
       </c>
       <c r="F4" t="n">
-        <v>207.92</v>
+        <v>9.91</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>-1.41</v>
       </c>
       <c r="H4" t="n">
-        <v>210.33</v>
+        <v>9.91</v>
       </c>
       <c r="I4" t="n">
-        <v>205.2</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="K4" t="n">
-        <v>716923.99</v>
-      </c>
-      <c r="L4" t="n">
-        <v>716924</v>
-      </c>
-      <c r="M4" t="n">
-        <v>574785</v>
-      </c>
+        <v>9.74</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>77670</v>
-      </c>
-      <c r="P4" t="n">
-        <v>77670</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>30425</v>
-      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>178547</v>
-      </c>
-      <c r="T4" t="n">
-        <v>123029</v>
-      </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr">
         <is>
-          <t>2026-03-01 18:39:12</t>
+          <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BANK.TO</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>882.9299999999999</v>
+        <v>3771360.87</v>
       </c>
       <c r="E5" t="n">
-        <v>9.77</v>
+        <v>311.76</v>
       </c>
       <c r="F5" t="n">
-        <v>9.91</v>
+        <v>307.38</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.41</v>
+        <v>1.42</v>
       </c>
       <c r="H5" t="n">
-        <v>9.91</v>
+        <v>312.37</v>
       </c>
       <c r="I5" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>303.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="K5" t="n">
+        <v>402836</v>
+      </c>
+      <c r="L5" t="n">
+        <v>402836</v>
+      </c>
+      <c r="M5" t="n">
+        <v>307394</v>
+      </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>132170</v>
+      </c>
+      <c r="P5" t="n">
+        <v>132170</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>73795</v>
+      </c>
       <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>66996</v>
+      </c>
+      <c r="T5" t="n">
+        <v>126843</v>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-01 15:59:09</t>
+          <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>GOOGL</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Alphabet Inc.</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
+          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3771360.87</v>
+        <v>68288.39</v>
       </c>
       <c r="E6" t="n">
-        <v>311.76</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>307.38</v>
+        <v>79.45</v>
       </c>
       <c r="G6" t="n">
-        <v>1.42</v>
+        <v>-4.53</v>
       </c>
       <c r="H6" t="n">
-        <v>312.37</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>303.8</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>10.82</v>
+        <v>2.05</v>
       </c>
       <c r="K6" t="n">
-        <v>402836</v>
+        <v>4473</v>
       </c>
       <c r="L6" t="n">
-        <v>402836</v>
+        <v>4473</v>
       </c>
       <c r="M6" t="n">
-        <v>307394</v>
+        <v>1865</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>132170</v>
+        <v>1883</v>
       </c>
       <c r="P6" t="n">
-        <v>132170</v>
+        <v>1883</v>
       </c>
       <c r="Q6" t="n">
-        <v>73795</v>
+        <v>-541</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>66996</v>
+        <v>12449</v>
       </c>
       <c r="T6" t="n">
-        <v>126843</v>
+        <v>12646</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:06</t>
+          <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>68288.39</v>
+        <v>2918992.05</v>
       </c>
       <c r="E7" t="n">
-        <v>75.84999999999999</v>
+        <v>392.74</v>
       </c>
       <c r="F7" t="n">
-        <v>79.45</v>
+        <v>401.72</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.53</v>
+        <v>-2.24</v>
       </c>
       <c r="H7" t="n">
-        <v>77.79000000000001</v>
+        <v>396.8</v>
       </c>
       <c r="I7" t="n">
-        <v>74.81999999999999</v>
+        <v>390</v>
       </c>
       <c r="J7" t="n">
-        <v>2.05</v>
+        <v>15.98</v>
       </c>
       <c r="K7" t="n">
-        <v>4473</v>
+        <v>305453.01</v>
       </c>
       <c r="L7" t="n">
-        <v>4473</v>
+        <v>281724</v>
       </c>
       <c r="M7" t="n">
-        <v>1865</v>
+        <v>211915</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="n">
-        <v>1883</v>
+        <v>119262</v>
       </c>
       <c r="P7" t="n">
-        <v>1883</v>
+        <v>101832</v>
       </c>
       <c r="Q7" t="n">
-        <v>-541</v>
+        <v>72361</v>
       </c>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>12449</v>
+        <v>123278</v>
       </c>
       <c r="T7" t="n">
-        <v>12646</v>
+        <v>89462</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2026-03-02 00:00:07</t>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>MU</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2918992.05</v>
+        <v>464463.92</v>
       </c>
       <c r="E8" t="n">
-        <v>392.74</v>
+        <v>412.67</v>
       </c>
       <c r="F8" t="n">
-        <v>401.72</v>
+        <v>412.37</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.24</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>396.8</v>
+        <v>417.61</v>
       </c>
       <c r="I8" t="n">
-        <v>390</v>
+        <v>397.0101</v>
       </c>
       <c r="J8" t="n">
-        <v>15.98</v>
+        <v>10.52</v>
       </c>
       <c r="K8" t="n">
-        <v>305453.01</v>
+        <v>42312</v>
       </c>
       <c r="L8" t="n">
-        <v>281724</v>
+        <v>37378</v>
       </c>
       <c r="M8" t="n">
-        <v>211915</v>
+        <v>15540</v>
       </c>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="n">
-        <v>119262</v>
+        <v>11909</v>
       </c>
       <c r="P8" t="n">
-        <v>101832</v>
+        <v>8539</v>
       </c>
       <c r="Q8" t="n">
-        <v>72361</v>
+        <v>-5833</v>
       </c>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>123278</v>
+        <v>12493</v>
       </c>
       <c r="T8" t="n">
-        <v>89462</v>
+        <v>10318</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NFLX</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc.</t>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>464463.92</v>
+        <v>408239.44</v>
       </c>
       <c r="E9" t="n">
-        <v>412.67</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>412.37</v>
+        <v>84.607</v>
       </c>
       <c r="G9" t="n">
-        <v>0.07000000000000001</v>
+        <v>13.75</v>
       </c>
       <c r="H9" t="n">
-        <v>417.61</v>
+        <v>96.75</v>
       </c>
       <c r="I9" t="n">
-        <v>397.0101</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>10.52</v>
+        <v>2.53</v>
       </c>
       <c r="K9" t="n">
-        <v>42312</v>
+        <v>45183.04</v>
       </c>
       <c r="L9" t="n">
-        <v>37378</v>
+        <v>45183.04</v>
       </c>
       <c r="M9" t="n">
-        <v>15540</v>
+        <v>33723.3</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>11909</v>
+        <v>10981.2</v>
       </c>
       <c r="P9" t="n">
-        <v>8539</v>
+        <v>10981.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>-5833</v>
+        <v>5407.99</v>
       </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>12493</v>
+        <v>16975.84</v>
       </c>
       <c r="T9" t="n">
-        <v>10318</v>
+        <v>9062.360000000001</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>2026-03-02 17:28:51</t>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NFLX</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Netflix, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>408239.44</v>
+        <v>4306603.08</v>
       </c>
       <c r="E10" t="n">
-        <v>96.23999999999999</v>
+        <v>177.19</v>
       </c>
       <c r="F10" t="n">
-        <v>84.607</v>
+        <v>184.89</v>
       </c>
       <c r="G10" t="n">
-        <v>13.75</v>
+        <v>-4.16</v>
       </c>
       <c r="H10" t="n">
-        <v>96.75</v>
+        <v>182.58</v>
       </c>
       <c r="I10" t="n">
-        <v>90.59999999999999</v>
+        <v>176.38</v>
       </c>
       <c r="J10" t="n">
-        <v>2.53</v>
+        <v>4.91</v>
       </c>
       <c r="K10" t="n">
-        <v>45183.04</v>
+        <v>215938.01</v>
       </c>
       <c r="L10" t="n">
-        <v>45183.04</v>
+        <v>215938</v>
       </c>
       <c r="M10" t="n">
-        <v>33723.3</v>
+        <v>60922</v>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="n">
-        <v>10981.2</v>
+        <v>120067</v>
       </c>
       <c r="P10" t="n">
-        <v>10981.2</v>
+        <v>120067</v>
       </c>
       <c r="Q10" t="n">
-        <v>5407.99</v>
+        <v>29760</v>
       </c>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>16975.84</v>
+        <v>11412</v>
       </c>
       <c r="T10" t="n">
-        <v>9062.360000000001</v>
+        <v>62556</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4306603.08</v>
+        <v>328113.98</v>
       </c>
       <c r="E11" t="n">
-        <v>177.19</v>
+        <v>137.19</v>
       </c>
       <c r="F11" t="n">
-        <v>184.89</v>
+        <v>135.94</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.16</v>
+        <v>0.92</v>
       </c>
       <c r="H11" t="n">
-        <v>182.58</v>
+        <v>138.1</v>
       </c>
       <c r="I11" t="n">
-        <v>176.38</v>
+        <v>133.99</v>
       </c>
       <c r="J11" t="n">
-        <v>4.91</v>
+        <v>0.63</v>
       </c>
       <c r="K11" t="n">
-        <v>215938.01</v>
+        <v>4475.45</v>
       </c>
       <c r="L11" t="n">
-        <v>215938</v>
+        <v>4475.45</v>
       </c>
       <c r="M11" t="n">
-        <v>60922</v>
+        <v>2225.01</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>120067</v>
+        <v>1625.03</v>
       </c>
       <c r="P11" t="n">
-        <v>120067</v>
+        <v>1625.03</v>
       </c>
       <c r="Q11" t="n">
-        <v>29760</v>
+        <v>209.82</v>
       </c>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>11412</v>
+        <v>229.34</v>
       </c>
       <c r="T11" t="n">
-        <v>62556</v>
+        <v>7177.04</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>SHOP.TO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc.</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>328113.98</v>
+        <v>213981.48</v>
       </c>
       <c r="E12" t="n">
-        <v>137.19</v>
+        <v>163.32</v>
       </c>
       <c r="F12" t="n">
-        <v>135.94</v>
+        <v>164.67</v>
       </c>
       <c r="G12" t="n">
-        <v>0.92</v>
+        <v>-0.82</v>
       </c>
       <c r="H12" t="n">
-        <v>138.1</v>
+        <v>164.76</v>
       </c>
       <c r="I12" t="n">
-        <v>133.99</v>
+        <v>156.66</v>
       </c>
       <c r="J12" t="n">
-        <v>0.63</v>
+        <v>1.28</v>
       </c>
       <c r="K12" t="n">
-        <v>4475.45</v>
+        <v>11556</v>
       </c>
       <c r="L12" t="n">
-        <v>4475.45</v>
+        <v>11556</v>
       </c>
       <c r="M12" t="n">
-        <v>2225.01</v>
+        <v>7060</v>
       </c>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="n">
-        <v>1625.03</v>
+        <v>1231</v>
       </c>
       <c r="P12" t="n">
-        <v>1625.03</v>
+        <v>1231</v>
       </c>
       <c r="Q12" t="n">
-        <v>209.82</v>
+        <v>132</v>
       </c>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>229.34</v>
+        <v>188</v>
       </c>
       <c r="T12" t="n">
-        <v>7177.04</v>
+        <v>5847</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SHOP.TO</t>
+          <t>TD.TO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>213981.48</v>
+        <v>223066.26</v>
       </c>
       <c r="E13" t="n">
-        <v>163.32</v>
+        <v>132.88</v>
       </c>
       <c r="F13" t="n">
-        <v>164.67</v>
+        <v>135.14</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.82</v>
+        <v>-1.67</v>
       </c>
       <c r="H13" t="n">
-        <v>164.76</v>
+        <v>136.49</v>
       </c>
       <c r="I13" t="n">
-        <v>156.66</v>
+        <v>132.48</v>
       </c>
       <c r="J13" t="n">
-        <v>1.28</v>
+        <v>11.56</v>
       </c>
       <c r="K13" t="n">
-        <v>11556</v>
+        <v>65980</v>
       </c>
       <c r="L13" t="n">
-        <v>11556</v>
+        <v>61281</v>
       </c>
       <c r="M13" t="n">
-        <v>7060</v>
+        <v>51524</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>1231</v>
+        <v>21208</v>
       </c>
       <c r="P13" t="n">
-        <v>1231</v>
+        <v>20538</v>
       </c>
       <c r="Q13" t="n">
-        <v>132</v>
+        <v>10634</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>188</v>
+        <v>528488.99</v>
       </c>
       <c r="T13" t="n">
-        <v>5847</v>
+        <v>654255</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TD.TO</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>223066.26</v>
+        <v>1510391.41</v>
       </c>
       <c r="E14" t="n">
-        <v>132.88</v>
+        <v>402.51</v>
       </c>
       <c r="F14" t="n">
-        <v>135.14</v>
+        <v>408.58</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.67</v>
+        <v>-1.49</v>
       </c>
       <c r="H14" t="n">
-        <v>136.49</v>
+        <v>407.11</v>
       </c>
       <c r="I14" t="n">
-        <v>132.48</v>
+        <v>398.12</v>
       </c>
       <c r="J14" t="n">
-        <v>11.56</v>
+        <v>1.09</v>
       </c>
       <c r="K14" t="n">
-        <v>65980</v>
+        <v>94827</v>
       </c>
       <c r="L14" t="n">
-        <v>61281</v>
+        <v>94827</v>
       </c>
       <c r="M14" t="n">
-        <v>51524</v>
+        <v>96773</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>21208</v>
+        <v>3794</v>
       </c>
       <c r="P14" t="n">
-        <v>20538</v>
+        <v>3794</v>
       </c>
       <c r="Q14" t="n">
-        <v>10634</v>
+        <v>14999</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>528488.99</v>
+        <v>14719</v>
       </c>
       <c r="T14" t="n">
-        <v>654255</v>
+        <v>44059</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>XDIV.TO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1510391.41</v>
+        <v>3940.24</v>
       </c>
       <c r="E15" t="n">
-        <v>402.51</v>
+        <v>38.7</v>
       </c>
       <c r="F15" t="n">
-        <v>408.58</v>
+        <v>38.67</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.49</v>
+        <v>0.08</v>
       </c>
       <c r="H15" t="n">
-        <v>407.11</v>
+        <v>38.8</v>
       </c>
       <c r="I15" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M15" t="n">
-        <v>96773</v>
-      </c>
+        <v>38.5</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>14999</v>
-      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T15" t="n">
-        <v>44059</v>
-      </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E16" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H16" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -26,15 +25,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD9E1F2"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -46,23 +71,86 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,9 +514,9 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:U16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="40.35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stock Ticker</t>
@@ -535,1013 +623,1039 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="40.35" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>AAPL</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>Apple Inc.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>Apple Inc. designs, manufactures, and markets smartphones, personal computers, tablets, wearables, and accessories worldwide. The company offers iPhone, a line of smartphones; Mac, a line of personal computers; iPad, a line of multi-purpose tablets; and wearables, home, and accessories comprising AirPods, Apple Vision Pro, Apple TV, Apple Watch, Beats products, and HomePod, as well as Apple branded and third-party accessories. It also provides AppleCare support and cloud services; and operates various platforms, including the App Store that allow customers to discover and download applications and digital content, such as books, music, video, games, and podcasts, as well as advertising services include third-party licensing arrangements and its own advertising platforms. In addition, the company offers various subscription-based services, such as Apple Arcade, a game subscription service; Apple Fitness+, a personalized fitness service; Apple Music, which offers users a curated listening experience with on-demand radio stations; Apple News+, a subscription news and magazine service; Apple TV, which offers exclusive original content and live sports; Apple Card, a co-branded credit card; and Apple Pay, a cashless payment service, as well as licenses its intellectual property. The company serves consumers, and small and mid-sized businesses; and the education, enterprise, and government markets. It distributes third-party applications for its products through the App Store. The company also sells its products through its retail and online stores, and direct sales force; and third-party cellular network carriers and resellers. The company was formerly known as Apple Computer, Inc. and changed its name to Apple Inc. in January 2007. Apple Inc. was founded in 1976 and is headquartered in Cupertino, California.</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="18" t="n">
         <v>3882897.9</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="18" t="n">
         <v>264.18</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="18" t="n">
         <v>272.95</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="18" t="n">
         <v>-3.21</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="18" t="n">
         <v>272.81</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="18" t="n">
         <v>262.89</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" s="18" t="n">
         <v>7.9</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="18" t="n">
         <v>435617.01</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="18" t="n">
         <v>416161</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="18" t="n">
         <v>383285</v>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
+      <c r="N2" s="18" t="n"/>
+      <c r="O2" s="18" t="n">
         <v>117777</v>
       </c>
-      <c r="P2" t="n">
+      <c r="P2" s="18" t="n">
         <v>112010</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="Q2" s="18" t="n">
         <v>96995</v>
       </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
+      <c r="R2" s="18" t="n"/>
+      <c r="S2" s="18" t="n">
         <v>90509</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="18" t="n">
         <v>66907</v>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" s="18" t="inlineStr">
         <is>
           <t>2026-03-01 17:06:08</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="40.35" customHeight="1">
+      <c r="A3" s="19" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="19" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="19" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="19" t="n">
         <v>210</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="19" t="n">
         <v>207.92</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="19" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="19" t="n">
         <v>210.33</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="19" t="n">
         <v>205.2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="19" t="n">
         <v>7.16</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="19" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="19" t="n">
         <v>716924</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="19" t="n">
         <v>574785</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N3" s="19" t="n"/>
+      <c r="O3" s="19" t="n">
         <v>77670</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="19" t="n">
         <v>77670</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="19" t="n">
         <v>30425</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R3" s="19" t="n"/>
+      <c r="S3" s="19" t="n">
         <v>178547</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="19" t="n">
         <v>123029</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="19" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="4" ht="40.35" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Broadcom Inc. designs, develops, and supplies various semiconductor devices and infrastructure software solutions internationally. The company operates in two segments: Semiconductor Solutions and Infrastructure Software. The company offers networking connectivity, such as custom silicon solutions, ethernet switching &amp; routing, ethernet NIC controllers, physical layer devices, and fiber optic components; wireless device connectivity, including RF semiconductor devices, connectivity solutions, custom touch controllers, and inductive charging ASICS; servers and storage system solutions, such as PCIE switches, SAS &amp; raid products, fibre channel products, and HDD &amp; SSD solutions; broadband solutions, includes set-top box, and broadband access; and industrial. The company also offers a private cloud software portfolio, including the VMware Cloud Foundation, Edge, vSphere foundation, telco cloud platform, private AI, live recovery, application networking and security, application development and data services; mainframe software, such as AIOPS &amp; automation, database &amp; data management, DEVX &amp; DEVOPS, cybersecurity &amp; compliance management, beyond code programs, foundational &amp; open mainframe solutions; cybersecurity, such as endpoint, network, information, application security, and identity &amp; access management; enterprise software; and fc san management. Its products are used in various applications in enterprise and data center networking, including artificial intelligence networking and connectivity, home connectivity, set-top boxes, broadband access, telecommunication equipment, wireless device and base stations, data center servers and storage systems, factory automation, power generation and alternative energy systems, and electronic displays. Broadcom Inc. was founded in 1961 and is headquartered in Palo Alto, California.</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>1511612.87</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>318.82</v>
+      </c>
+      <c r="F4" s="18" t="n">
+        <v>319.55</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>320.04</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>307.2</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>63887</v>
+      </c>
+      <c r="L4" s="18" t="n">
+        <v>63887</v>
+      </c>
+      <c r="M4" s="18" t="n">
+        <v>35819</v>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="18" t="n">
+        <v>23126</v>
+      </c>
+      <c r="P4" s="18" t="n">
+        <v>23126</v>
+      </c>
+      <c r="Q4" s="18" t="n">
+        <v>14082</v>
+      </c>
+      <c r="R4" s="18" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" s="18" t="n">
+        <v>40457</v>
+      </c>
+      <c r="T4" s="18" t="n">
+        <v>11105</v>
+      </c>
+      <c r="U4" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-02 16:46:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40.35" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" s="19" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" s="19" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" s="19" t="n">
         <v>9.77</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" s="19" t="n">
         <v>9.91</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" s="19" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" s="19" t="n">
         <v>9.91</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" s="19" t="n">
         <v>9.74</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr">
+      <c r="J5" s="19" t="n"/>
+      <c r="K5" s="19" t="n"/>
+      <c r="L5" s="19" t="n"/>
+      <c r="M5" s="19" t="n"/>
+      <c r="N5" s="19" t="n"/>
+      <c r="O5" s="19" t="n"/>
+      <c r="P5" s="19" t="n"/>
+      <c r="Q5" s="19" t="n"/>
+      <c r="R5" s="19" t="n"/>
+      <c r="S5" s="19" t="n"/>
+      <c r="T5" s="19" t="n"/>
+      <c r="U5" s="19" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+    <row r="6" ht="40.35" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" s="18" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" s="18" t="n">
         <v>311.76</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" s="18" t="n">
         <v>307.38</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" s="18" t="n">
         <v>1.42</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" s="18" t="n">
         <v>312.37</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" s="18" t="n">
         <v>303.8</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" s="18" t="n">
         <v>10.82</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" s="18" t="n">
         <v>402836</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" s="18" t="n">
         <v>402836</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" s="18" t="n">
         <v>307394</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="18" t="n">
         <v>132170</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" s="18" t="n">
         <v>132170</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" s="18" t="n">
         <v>73795</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="R6" s="18" t="n"/>
+      <c r="S6" s="18" t="n">
         <v>66996</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" s="18" t="n">
         <v>126843</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" s="18" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+    <row r="7" ht="40.35" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" s="19" t="n">
         <v>68288.39</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" s="19" t="n">
         <v>75.84999999999999</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" s="19" t="n">
         <v>79.45</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" s="19" t="n">
         <v>-4.53</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H7" s="19" t="n">
         <v>77.79000000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I7" s="19" t="n">
         <v>74.81999999999999</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J7" s="19" t="n">
         <v>2.05</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K7" s="19" t="n">
         <v>4473</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L7" s="19" t="n">
         <v>4473</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M7" s="19" t="n">
         <v>1865</v>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="n">
+      <c r="N7" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="n">
         <v>1883</v>
       </c>
-      <c r="P6" t="n">
+      <c r="P7" s="19" t="n">
         <v>1883</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" s="19" t="n">
         <v>-541</v>
       </c>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="n">
+      <c r="R7" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="19" t="n">
         <v>12449</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" s="19" t="n">
         <v>12646</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" s="19" t="inlineStr">
         <is>
           <t>2026-03-02 00:00:07</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="40.35" customHeight="1">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" s="18" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E8" s="18" t="n">
         <v>392.74</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F8" s="18" t="n">
         <v>401.72</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G8" s="18" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H8" s="18" t="n">
         <v>396.8</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" s="18" t="n">
         <v>390</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" s="18" t="n">
         <v>15.98</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K8" s="18" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L8" s="18" t="n">
         <v>281724</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M8" s="18" t="n">
         <v>211915</v>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n">
         <v>119262</v>
       </c>
-      <c r="P7" t="n">
+      <c r="P8" s="18" t="n">
         <v>101832</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="Q8" s="18" t="n">
         <v>72361</v>
       </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
+      <c r="R8" s="18" t="n"/>
+      <c r="S8" s="18" t="n">
         <v>123278</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" s="18" t="n">
         <v>89462</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="U8" s="18" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
+    <row r="9" ht="40.35" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D9" s="19" t="n">
         <v>464463.92</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" s="19" t="n">
         <v>412.67</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F9" s="19" t="n">
         <v>412.37</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" s="19" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H9" s="19" t="n">
         <v>417.61</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" s="19" t="n">
         <v>397.0101</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J9" s="19" t="n">
         <v>10.52</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" s="19" t="n">
         <v>42312</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" s="19" t="n">
         <v>37378</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M9" s="19" t="n">
         <v>15540</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="n">
+      <c r="N9" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="n">
         <v>11909</v>
       </c>
-      <c r="P8" t="n">
+      <c r="P9" s="19" t="n">
         <v>8539</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="Q9" s="19" t="n">
         <v>-5833</v>
       </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="n">
+      <c r="R9" s="19" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="19" t="n">
         <v>12493</v>
       </c>
-      <c r="T8" t="n">
+      <c r="T9" s="19" t="n">
         <v>10318</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="U9" s="19" t="inlineStr">
         <is>
           <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
+    <row r="10" ht="40.35" customHeight="1">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D10" s="18" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E10" s="18" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F10" s="18" t="n">
         <v>84.607</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" s="18" t="n">
         <v>13.75</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H10" s="18" t="n">
         <v>96.75</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" s="18" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J10" s="18" t="n">
         <v>2.53</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K10" s="18" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L10" s="18" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M10" s="18" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="n">
+      <c r="N10" s="18" t="n"/>
+      <c r="O10" s="18" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P10" s="18" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q10" s="18" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="n">
+      <c r="R10" s="18" t="n"/>
+      <c r="S10" s="18" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T10" s="18" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U10" s="18" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+    <row r="11" ht="40.35" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D11" s="19" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E11" s="19" t="n">
         <v>177.19</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F11" s="19" t="n">
         <v>184.89</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G11" s="19" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H11" s="19" t="n">
         <v>182.58</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I11" s="19" t="n">
         <v>176.38</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J11" s="19" t="n">
         <v>4.91</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K11" s="19" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L11" s="19" t="n">
         <v>215938</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" s="19" t="n">
         <v>60922</v>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="n">
+      <c r="N11" s="19" t="n"/>
+      <c r="O11" s="19" t="n">
         <v>120067</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" s="19" t="n">
         <v>120067</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" s="19" t="n">
         <v>29760</v>
       </c>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="n">
+      <c r="R11" s="19" t="n"/>
+      <c r="S11" s="19" t="n">
         <v>11412</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T11" s="19" t="n">
         <v>62556</v>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="U11" s="19" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+    <row r="12" ht="40.35" customHeight="1">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc.</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D12" s="18" t="n">
         <v>328113.98</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E12" s="18" t="n">
         <v>137.19</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F12" s="18" t="n">
         <v>135.94</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G12" s="18" t="n">
         <v>0.92</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H12" s="18" t="n">
         <v>138.1</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I12" s="18" t="n">
         <v>133.99</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J12" s="18" t="n">
         <v>0.63</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K12" s="18" t="n">
         <v>4475.45</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L12" s="18" t="n">
         <v>4475.45</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M12" s="18" t="n">
         <v>2225.01</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="n">
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n">
         <v>1625.03</v>
       </c>
-      <c r="P11" t="n">
+      <c r="P12" s="18" t="n">
         <v>1625.03</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="Q12" s="18" t="n">
         <v>209.82</v>
       </c>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="n">
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="18" t="n">
         <v>229.34</v>
       </c>
-      <c r="T11" t="n">
+      <c r="T12" s="18" t="n">
         <v>7177.04</v>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="U12" s="18" t="inlineStr">
         <is>
           <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RKLB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Rocket Lab Corporation</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Rocket Lab Corporation, a space company, provides launch services and space systems solutions in the United States, Canada, Japan, and internationally. The company provides launch services, spacecraft design services, spacecraft components, spacecraft manufacturing, and other spacecraft and on-orbit management solutions; and constellation management services, as well as designs and manufactures small and medium-class rockets. It also designs, manufactures, and sells Electron, an orbital small launch vehicle for small spacecraft launch services, as well as develops Neutron launch vehicles for large constellation deployments, interplanetary missions and potentially for human spaceflight. In addition, the company designs and manufactures a range of components and subsystems for its launch vehicles and spacecraft. It serves commercial, aerospace prime contractors, and government customers. Rocket Lab Corporation was founded in 2006 and is headquartered in Long Beach, California.</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>37909.07</v>
-      </c>
-      <c r="E12" t="n">
-        <v>70.97</v>
-      </c>
-      <c r="F12" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="H12" t="n">
-        <v>72.09999999999999</v>
-      </c>
-      <c r="I12" t="n">
-        <v>66.45</v>
-      </c>
-      <c r="J12" t="n">
-        <v>-0.38</v>
-      </c>
-      <c r="K12" t="n">
-        <v>601.8</v>
-      </c>
-      <c r="L12" t="n">
-        <v>436.21</v>
-      </c>
-      <c r="M12" t="n">
-        <v>211</v>
-      </c>
-      <c r="N12" t="inlineStr">
+    <row r="13" ht="40.35" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I13" s="19" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L13" s="19" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O12" t="n">
-        <v>-198.21</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-190.18</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>-135.94</v>
-      </c>
-      <c r="R12" t="inlineStr">
+      <c r="O13" s="19" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P13" s="19" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q13" s="19" t="n">
+        <v>132</v>
+      </c>
+      <c r="R13" s="19" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S12" t="n">
-        <v>265.09</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1016.58</v>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>2026-03-02 22:55:02</t>
+      <c r="S13" s="19" t="n">
+        <v>188</v>
+      </c>
+      <c r="T13" s="19" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U13" s="19" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E13" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F13" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G13" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H13" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I13" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K13" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L13" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M13" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>132</v>
-      </c>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="n">
-        <v>188</v>
-      </c>
-      <c r="T13" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+    <row r="14" ht="40.35" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="18" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P14" s="18" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q14" s="18" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="18" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T14" s="18" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U14" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E14" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F14" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H14" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I14" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J14" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K14" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L14" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M14" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P14" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T14" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+    <row r="15" ht="40.35" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I15" s="19" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J15" s="19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K15" s="19" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L15" s="19" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="19" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P15" s="19" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q15" s="19" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R15" s="19" t="n"/>
+      <c r="S15" s="19" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T15" s="19" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U15" s="19" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E15" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F15" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H15" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I15" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L15" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M15" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P15" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T15" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+    <row r="16" ht="40.35" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="18" t="n"/>
+      <c r="T16" s="18" t="n"/>
+      <c r="U16" s="18" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E16" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F16" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H16" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I16" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="17" ht="40.35" customHeight="1"/>
+    <row r="18" ht="40.35" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -525,7 +531,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -636,12 +642,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="22" t="inlineStr">
+      <c r="A2" s="24" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="22" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -651,66 +657,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="22" t="n">
+      <c r="D2" s="24" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="22" t="n">
+      <c r="E2" s="24" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="22" t="n">
+      <c r="F2" s="24" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="22" t="n">
+      <c r="G2" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="22" t="n">
+      <c r="H2" s="24" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="22" t="n">
+      <c r="I2" s="24" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="22" t="n">
+      <c r="J2" s="24" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="22" t="n">
+      <c r="K2" s="24" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="22" t="n">
+      <c r="L2" s="24" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="22" t="n">
+      <c r="M2" s="24" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="22" t="n"/>
-      <c r="O2" s="22" t="n">
+      <c r="N2" s="24" t="n"/>
+      <c r="O2" s="24" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="22" t="n">
+      <c r="P2" s="24" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="22" t="n">
+      <c r="Q2" s="24" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="22" t="n"/>
-      <c r="S2" s="22" t="n">
+      <c r="R2" s="24" t="n"/>
+      <c r="S2" s="24" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="22" t="n">
+      <c r="T2" s="24" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="22" t="inlineStr">
+      <c r="U2" s="24" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="25" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="25" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -720,48 +726,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="23" t="n">
+      <c r="D3" s="25" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="23" t="n">
+      <c r="E3" s="25" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="23" t="n">
+      <c r="F3" s="25" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="23" t="n">
+      <c r="G3" s="25" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="23" t="n">
+      <c r="H3" s="25" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="23" t="n">
+      <c r="I3" s="25" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="23" t="n"/>
-      <c r="K3" s="23" t="n"/>
-      <c r="L3" s="23" t="n"/>
-      <c r="M3" s="23" t="n"/>
-      <c r="N3" s="23" t="n"/>
-      <c r="O3" s="23" t="n"/>
-      <c r="P3" s="23" t="n"/>
-      <c r="Q3" s="23" t="n"/>
-      <c r="R3" s="23" t="n"/>
-      <c r="S3" s="23" t="n"/>
-      <c r="T3" s="23" t="n"/>
-      <c r="U3" s="23" t="inlineStr">
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="22" t="inlineStr">
+      <c r="A4" s="24" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="22" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -771,755 +777,679 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="22" t="n">
+      <c r="D4" s="24" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="22" t="n">
+      <c r="E4" s="24" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="22" t="n">
+      <c r="F4" s="24" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="22" t="n">
+      <c r="G4" s="24" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="22" t="n">
+      <c r="H4" s="24" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="22" t="n">
+      <c r="I4" s="24" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="24" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="22" t="n">
+      <c r="K4" s="24" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="22" t="n">
+      <c r="L4" s="24" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="22" t="n">
+      <c r="M4" s="24" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="22" t="n"/>
-      <c r="O4" s="22" t="n">
+      <c r="N4" s="24" t="n"/>
+      <c r="O4" s="24" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="22" t="n">
+      <c r="P4" s="24" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="22" t="n">
+      <c r="Q4" s="24" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="22" t="n"/>
-      <c r="S4" s="22" t="n">
+      <c r="R4" s="24" t="n"/>
+      <c r="S4" s="24" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="22" t="n">
+      <c r="T4" s="24" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="22" t="inlineStr">
+      <c r="U4" s="24" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="23" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="inlineStr">
-        <is>
-          <t>Robinhood Markets, Inc.</t>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="n">
-        <v>68288.39</v>
-      </c>
-      <c r="E5" s="23" t="n">
-        <v>75.84999999999999</v>
-      </c>
-      <c r="F5" s="23" t="n">
-        <v>79.45</v>
-      </c>
-      <c r="G5" s="23" t="n">
-        <v>-4.53</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>77.79000000000001</v>
-      </c>
-      <c r="I5" s="23" t="n">
-        <v>74.81999999999999</v>
-      </c>
-      <c r="J5" s="23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="K5" s="23" t="n">
-        <v>4473</v>
-      </c>
-      <c r="L5" s="23" t="n">
-        <v>4473</v>
-      </c>
-      <c r="M5" s="23" t="n">
-        <v>1865</v>
-      </c>
-      <c r="N5" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" s="23" t="n">
-        <v>1883</v>
-      </c>
-      <c r="P5" s="23" t="n">
-        <v>1883</v>
-      </c>
-      <c r="Q5" s="23" t="n">
-        <v>-541</v>
-      </c>
-      <c r="R5" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S5" s="23" t="n">
-        <v>12449</v>
-      </c>
-      <c r="T5" s="23" t="n">
-        <v>12646</v>
-      </c>
-      <c r="U5" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-02 00:00:07</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="n">
+        <v>2918992.05</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="I5" s="25" t="n">
+        <v>390</v>
+      </c>
+      <c r="J5" s="25" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K5" s="25" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L5" s="25" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M5" s="25" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P5" s="25" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q5" s="25" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T5" s="25" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U5" s="25" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
-        </is>
-      </c>
-      <c r="D6" s="22" t="n">
-        <v>2918992.05</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>392.74</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>401.72</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="I6" s="22" t="n">
-        <v>390</v>
-      </c>
-      <c r="J6" s="22" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>305453.01</v>
-      </c>
-      <c r="L6" s="22" t="n">
-        <v>281724</v>
-      </c>
-      <c r="M6" s="22" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N6" s="22" t="n"/>
-      <c r="O6" s="22" t="n">
-        <v>119262</v>
-      </c>
-      <c r="P6" s="22" t="n">
-        <v>101832</v>
-      </c>
-      <c r="Q6" s="22" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R6" s="22" t="n"/>
-      <c r="S6" s="22" t="n">
-        <v>123278</v>
-      </c>
-      <c r="T6" s="22" t="n">
-        <v>89462</v>
-      </c>
-      <c r="U6" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:58</t>
+          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="n">
+        <v>464463.92</v>
+      </c>
+      <c r="E6" s="24" t="n">
+        <v>412.67</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>412.37</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H6" s="24" t="n">
+        <v>417.61</v>
+      </c>
+      <c r="I6" s="24" t="n">
+        <v>397.0101</v>
+      </c>
+      <c r="J6" s="24" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="K6" s="24" t="n">
+        <v>42312</v>
+      </c>
+      <c r="L6" s="24" t="n">
+        <v>37378</v>
+      </c>
+      <c r="M6" s="24" t="n">
+        <v>15540</v>
+      </c>
+      <c r="N6" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O6" s="24" t="n">
+        <v>11909</v>
+      </c>
+      <c r="P6" s="24" t="n">
+        <v>8539</v>
+      </c>
+      <c r="Q6" s="24" t="n">
+        <v>-5833</v>
+      </c>
+      <c r="R6" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S6" s="24" t="n">
+        <v>12493</v>
+      </c>
+      <c r="T6" s="24" t="n">
+        <v>10318</v>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="23" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
+      <c r="A7" s="25" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
-        </is>
-      </c>
-      <c r="D7" s="23" t="n">
-        <v>464463.92</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>412.67</v>
-      </c>
-      <c r="F7" s="23" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="G7" s="23" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <v>417.61</v>
-      </c>
-      <c r="I7" s="23" t="n">
-        <v>397.0101</v>
-      </c>
-      <c r="J7" s="23" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K7" s="23" t="n">
-        <v>42312</v>
-      </c>
-      <c r="L7" s="23" t="n">
-        <v>37378</v>
-      </c>
-      <c r="M7" s="23" t="n">
-        <v>15540</v>
-      </c>
-      <c r="N7" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="23" t="n">
-        <v>11909</v>
-      </c>
-      <c r="P7" s="23" t="n">
-        <v>8539</v>
-      </c>
-      <c r="Q7" s="23" t="n">
-        <v>-5833</v>
-      </c>
-      <c r="R7" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="23" t="n">
-        <v>12493</v>
-      </c>
-      <c r="T7" s="23" t="n">
-        <v>10318</v>
-      </c>
-      <c r="U7" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:28:51</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>408239.44</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>84.607</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J7" s="25" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K7" s="25" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="L7" s="25" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="M7" s="25" t="n">
+        <v>33723.3</v>
+      </c>
+      <c r="N7" s="25" t="n"/>
+      <c r="O7" s="25" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="P7" s="25" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="Q7" s="25" t="n">
+        <v>5407.99</v>
+      </c>
+      <c r="R7" s="25" t="n"/>
+      <c r="S7" s="25" t="n">
+        <v>16975.84</v>
+      </c>
+      <c r="T7" s="25" t="n">
+        <v>9062.360000000001</v>
+      </c>
+      <c r="U7" s="25" t="inlineStr">
+        <is>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="22" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I8" s="22" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L8" s="22" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N8" s="22" t="n"/>
-      <c r="O8" s="22" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P8" s="22" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q8" s="22" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R8" s="22" t="n"/>
-      <c r="S8" s="22" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T8" s="22" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U8" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E8" s="24" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I8" s="24" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J8" s="24" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K8" s="24" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L8" s="24" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M8" s="24" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N8" s="24" t="n"/>
+      <c r="O8" s="24" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P8" s="24" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q8" s="24" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R8" s="24" t="n"/>
+      <c r="S8" s="24" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T8" s="24" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="23" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A9" s="25" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I9" s="23" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L9" s="23" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M9" s="23" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N9" s="23" t="n"/>
-      <c r="O9" s="23" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P9" s="23" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q9" s="23" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R9" s="23" t="n"/>
-      <c r="S9" s="23" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T9" s="23" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U9" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>328113.98</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>133.99</v>
+      </c>
+      <c r="J9" s="25" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K9" s="25" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L9" s="25" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M9" s="25" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N9" s="25" t="n"/>
+      <c r="O9" s="25" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P9" s="25" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q9" s="25" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R9" s="25" t="n"/>
+      <c r="S9" s="25" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T9" s="25" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U9" s="25" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="22" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I10" s="22" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L10" s="22" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N10" s="22" t="n"/>
-      <c r="O10" s="22" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P10" s="22" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q10" s="22" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R10" s="22" t="n"/>
-      <c r="S10" s="22" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T10" s="22" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U10" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I10" s="24" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L10" s="24" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M10" s="24" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N10" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="24" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P10" s="24" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q10" s="24" t="n">
+        <v>132</v>
+      </c>
+      <c r="R10" s="24" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="24" t="n">
+        <v>188</v>
+      </c>
+      <c r="T10" s="24" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="23" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A11" s="25" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I11" s="23" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L11" s="23" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M11" s="23" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N11" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="23" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P11" s="23" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q11" s="23" t="n">
-        <v>132</v>
-      </c>
-      <c r="R11" s="23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="23" t="n">
-        <v>188</v>
-      </c>
-      <c r="T11" s="23" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U11" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E11" s="25" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F11" s="25" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G11" s="25" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H11" s="25" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J11" s="25" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K11" s="25" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L11" s="25" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M11" s="25" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N11" s="25" t="n"/>
+      <c r="O11" s="25" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P11" s="25" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q11" s="25" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R11" s="25" t="n"/>
+      <c r="S11" s="25" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T11" s="25" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U11" s="25" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="22" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H12" s="22" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I12" s="22" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J12" s="22" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K12" s="22" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L12" s="22" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M12" s="22" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N12" s="22" t="n"/>
-      <c r="O12" s="22" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P12" s="22" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q12" s="22" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R12" s="22" t="n"/>
-      <c r="S12" s="22" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T12" s="22" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U12" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I12" s="24" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L12" s="24" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M12" s="24" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N12" s="24" t="n"/>
+      <c r="O12" s="24" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P12" s="24" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q12" s="24" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R12" s="24" t="n"/>
+      <c r="S12" s="24" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T12" s="24" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="23" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A13" s="25" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D13" s="23" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I13" s="23" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L13" s="23" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M13" s="23" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N13" s="23" t="n"/>
-      <c r="O13" s="23" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P13" s="23" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q13" s="23" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R13" s="23" t="n"/>
-      <c r="S13" s="23" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T13" s="23" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U13" s="23" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E13" s="25" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F13" s="25" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G13" s="25" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H13" s="25" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="25" t="n"/>
+      <c r="L13" s="25" t="n"/>
+      <c r="M13" s="25" t="n"/>
+      <c r="N13" s="25" t="n"/>
+      <c r="O13" s="25" t="n"/>
+      <c r="P13" s="25" t="n"/>
+      <c r="Q13" s="25" t="n"/>
+      <c r="R13" s="25" t="n"/>
+      <c r="S13" s="25" t="n"/>
+      <c r="T13" s="25" t="n"/>
+      <c r="U13" s="25" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40.35" customHeight="1">
-      <c r="A14" s="22" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I14" s="22" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J14" s="22" t="n"/>
-      <c r="K14" s="22" t="n"/>
-      <c r="L14" s="22" t="n"/>
-      <c r="M14" s="22" t="n"/>
-      <c r="N14" s="22" t="n"/>
-      <c r="O14" s="22" t="n"/>
-      <c r="P14" s="22" t="n"/>
-      <c r="Q14" s="22" t="n"/>
-      <c r="R14" s="22" t="n"/>
-      <c r="S14" s="22" t="n"/>
-      <c r="T14" s="22" t="n"/>
-      <c r="U14" s="22" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="14" ht="40.35" customHeight="1"/>
     <row r="15" ht="40.35" customHeight="1"/>
     <row r="16" ht="40.35" customHeight="1"/>
     <row r="17" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -531,7 +537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -642,12 +648,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
+      <c r="A2" s="26" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="24" t="inlineStr">
+      <c r="B2" s="26" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -657,66 +663,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="24" t="n">
+      <c r="D2" s="26" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="24" t="n">
+      <c r="E2" s="26" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="24" t="n">
+      <c r="F2" s="26" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="24" t="n">
+      <c r="G2" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="24" t="n">
+      <c r="H2" s="26" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="24" t="n">
+      <c r="I2" s="26" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="24" t="n">
+      <c r="J2" s="26" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="24" t="n">
+      <c r="K2" s="26" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="24" t="n">
+      <c r="L2" s="26" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="24" t="n">
+      <c r="M2" s="26" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="24" t="n"/>
-      <c r="O2" s="24" t="n">
+      <c r="N2" s="26" t="n"/>
+      <c r="O2" s="26" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="24" t="n">
+      <c r="P2" s="26" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="24" t="n">
+      <c r="Q2" s="26" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="24" t="n"/>
-      <c r="S2" s="24" t="n">
+      <c r="R2" s="26" t="n"/>
+      <c r="S2" s="26" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="24" t="n">
+      <c r="T2" s="26" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="24" t="inlineStr">
+      <c r="U2" s="26" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="27" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="25" t="inlineStr">
+      <c r="B3" s="27" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -726,48 +732,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="25" t="n">
+      <c r="D3" s="27" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="25" t="n">
+      <c r="E3" s="27" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="25" t="n">
+      <c r="F3" s="27" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="25" t="n">
+      <c r="G3" s="27" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="25" t="n">
+      <c r="H3" s="27" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="25" t="n">
+      <c r="I3" s="27" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="inlineStr">
+      <c r="J3" s="27" t="n"/>
+      <c r="K3" s="27" t="n"/>
+      <c r="L3" s="27" t="n"/>
+      <c r="M3" s="27" t="n"/>
+      <c r="N3" s="27" t="n"/>
+      <c r="O3" s="27" t="n"/>
+      <c r="P3" s="27" t="n"/>
+      <c r="Q3" s="27" t="n"/>
+      <c r="R3" s="27" t="n"/>
+      <c r="S3" s="27" t="n"/>
+      <c r="T3" s="27" t="n"/>
+      <c r="U3" s="27" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="24" t="inlineStr">
+      <c r="A4" s="26" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="24" t="inlineStr">
+      <c r="B4" s="26" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -777,66 +783,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="24" t="n">
+      <c r="D4" s="26" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="24" t="n">
+      <c r="E4" s="26" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="24" t="n">
+      <c r="F4" s="26" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="24" t="n">
+      <c r="G4" s="26" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="24" t="n">
+      <c r="H4" s="26" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="24" t="n">
+      <c r="I4" s="26" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="24" t="n">
+      <c r="J4" s="26" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="24" t="n">
+      <c r="K4" s="26" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="24" t="n">
+      <c r="L4" s="26" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="24" t="n">
+      <c r="M4" s="26" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="24" t="n"/>
-      <c r="O4" s="24" t="n">
+      <c r="N4" s="26" t="n"/>
+      <c r="O4" s="26" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="24" t="n">
+      <c r="P4" s="26" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="24" t="n">
+      <c r="Q4" s="26" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="24" t="n"/>
-      <c r="S4" s="24" t="n">
+      <c r="R4" s="26" t="n"/>
+      <c r="S4" s="26" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="24" t="n">
+      <c r="T4" s="26" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="24" t="inlineStr">
+      <c r="U4" s="26" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -846,66 +852,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n">
+      <c r="D5" s="27" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="25" t="n">
+      <c r="E5" s="27" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="25" t="n">
+      <c r="F5" s="27" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="25" t="n">
+      <c r="G5" s="27" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="25" t="n">
+      <c r="H5" s="27" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="25" t="n">
+      <c r="I5" s="27" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="25" t="n">
+      <c r="J5" s="27" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="25" t="n">
+      <c r="K5" s="27" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="25" t="n">
+      <c r="L5" s="27" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="25" t="n">
+      <c r="M5" s="27" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n">
+      <c r="N5" s="27" t="n"/>
+      <c r="O5" s="27" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="25" t="n">
+      <c r="P5" s="27" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="25" t="n">
+      <c r="Q5" s="27" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n">
+      <c r="R5" s="27" t="n"/>
+      <c r="S5" s="27" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="25" t="n">
+      <c r="T5" s="27" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="25" t="inlineStr">
+      <c r="U5" s="27" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B6" s="24" t="inlineStr">
+      <c r="B6" s="26" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
@@ -915,74 +921,74 @@
           <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
-      <c r="D6" s="24" t="n">
+      <c r="D6" s="26" t="n">
         <v>464463.92</v>
       </c>
-      <c r="E6" s="24" t="n">
+      <c r="E6" s="26" t="n">
         <v>412.67</v>
       </c>
-      <c r="F6" s="24" t="n">
+      <c r="F6" s="26" t="n">
         <v>412.37</v>
       </c>
-      <c r="G6" s="24" t="n">
+      <c r="G6" s="26" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H6" s="24" t="n">
+      <c r="H6" s="26" t="n">
         <v>417.61</v>
       </c>
-      <c r="I6" s="24" t="n">
+      <c r="I6" s="26" t="n">
         <v>397.0101</v>
       </c>
-      <c r="J6" s="24" t="n">
+      <c r="J6" s="26" t="n">
         <v>10.52</v>
       </c>
-      <c r="K6" s="24" t="n">
+      <c r="K6" s="26" t="n">
         <v>42312</v>
       </c>
-      <c r="L6" s="24" t="n">
+      <c r="L6" s="26" t="n">
         <v>37378</v>
       </c>
-      <c r="M6" s="24" t="n">
+      <c r="M6" s="26" t="n">
         <v>15540</v>
       </c>
-      <c r="N6" s="24" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O6" s="24" t="n">
+      <c r="O6" s="26" t="n">
         <v>11909</v>
       </c>
-      <c r="P6" s="24" t="n">
+      <c r="P6" s="26" t="n">
         <v>8539</v>
       </c>
-      <c r="Q6" s="24" t="n">
+      <c r="Q6" s="26" t="n">
         <v>-5833</v>
       </c>
-      <c r="R6" s="24" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S6" s="24" t="n">
+      <c r="S6" s="26" t="n">
         <v>12493</v>
       </c>
-      <c r="T6" s="24" t="n">
+      <c r="T6" s="26" t="n">
         <v>10318</v>
       </c>
-      <c r="U6" s="24" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="27" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -992,464 +998,540 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D7" s="25" t="n">
+      <c r="D7" s="27" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E7" s="25" t="n">
+      <c r="E7" s="27" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F7" s="25" t="n">
+      <c r="F7" s="27" t="n">
         <v>84.607</v>
       </c>
-      <c r="G7" s="25" t="n">
+      <c r="G7" s="27" t="n">
         <v>13.75</v>
       </c>
-      <c r="H7" s="25" t="n">
+      <c r="H7" s="27" t="n">
         <v>96.75</v>
       </c>
-      <c r="I7" s="25" t="n">
+      <c r="I7" s="27" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J7" s="25" t="n">
+      <c r="J7" s="27" t="n">
         <v>2.53</v>
       </c>
-      <c r="K7" s="25" t="n">
+      <c r="K7" s="27" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L7" s="25" t="n">
+      <c r="L7" s="27" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M7" s="25" t="n">
+      <c r="M7" s="27" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N7" s="25" t="n"/>
-      <c r="O7" s="25" t="n">
+      <c r="N7" s="27" t="n"/>
+      <c r="O7" s="27" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P7" s="25" t="n">
+      <c r="P7" s="27" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q7" s="25" t="n">
+      <c r="Q7" s="27" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R7" s="25" t="n"/>
-      <c r="S7" s="25" t="n">
+      <c r="R7" s="27" t="n"/>
+      <c r="S7" s="27" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T7" s="25" t="n">
+      <c r="T7" s="27" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U7" s="25" t="inlineStr">
+      <c r="U7" s="27" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B8" s="24" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D8" s="24" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E8" s="24" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H8" s="24" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I8" s="24" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J8" s="24" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K8" s="24" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L8" s="24" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M8" s="24" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N8" s="24" t="n"/>
-      <c r="O8" s="24" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P8" s="24" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q8" s="24" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R8" s="24" t="n"/>
-      <c r="S8" s="24" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T8" s="24" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U8" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>11935.27</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I8" s="26" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M8" s="26" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N8" s="26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="26" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P8" s="26" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q8" s="26" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R8" s="26" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="26" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T8" s="26" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U8" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:52:03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="25" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B9" s="25" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J9" s="25" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K9" s="25" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L9" s="25" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M9" s="25" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N9" s="25" t="n"/>
-      <c r="O9" s="25" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P9" s="25" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q9" s="25" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R9" s="25" t="n"/>
-      <c r="S9" s="25" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T9" s="25" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U9" s="25" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I9" s="27" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J9" s="27" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K9" s="27" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L9" s="27" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N9" s="27" t="n"/>
+      <c r="O9" s="27" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P9" s="27" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q9" s="27" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R9" s="27" t="n"/>
+      <c r="S9" s="27" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T9" s="27" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U9" s="27" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="24" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B10" s="24" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B10" s="26" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D10" s="24" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I10" s="24" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L10" s="24" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M10" s="24" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N10" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="24" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P10" s="24" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q10" s="24" t="n">
-        <v>132</v>
-      </c>
-      <c r="R10" s="24" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="24" t="n">
-        <v>188</v>
-      </c>
-      <c r="T10" s="24" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U10" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>328113.98</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>137.19</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>135.94</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>138.1</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>133.99</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M10" s="26" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N10" s="26" t="n"/>
+      <c r="O10" s="26" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P10" s="26" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q10" s="26" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R10" s="26" t="n"/>
+      <c r="S10" s="26" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T10" s="26" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U10" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:48:23</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="25" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B11" s="25" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D11" s="25" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E11" s="25" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I11" s="25" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J11" s="25" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K11" s="25" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L11" s="25" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M11" s="25" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N11" s="25" t="n"/>
-      <c r="O11" s="25" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P11" s="25" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q11" s="25" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R11" s="25" t="n"/>
-      <c r="S11" s="25" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T11" s="25" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U11" s="25" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I11" s="27" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J11" s="27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K11" s="27" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L11" s="27" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N11" s="27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O11" s="27" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P11" s="27" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q11" s="27" t="n">
+        <v>132</v>
+      </c>
+      <c r="R11" s="27" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S11" s="27" t="n">
+        <v>188</v>
+      </c>
+      <c r="T11" s="27" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U11" s="27" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B12" s="24" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D12" s="24" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I12" s="24" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L12" s="24" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M12" s="24" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N12" s="24" t="n"/>
-      <c r="O12" s="24" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P12" s="24" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q12" s="24" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R12" s="24" t="n"/>
-      <c r="S12" s="24" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T12" s="24" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U12" s="24" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M12" s="26" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N12" s="26" t="n"/>
+      <c r="O12" s="26" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P12" s="26" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q12" s="26" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R12" s="26" t="n"/>
+      <c r="S12" s="26" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T12" s="26" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U12" s="26" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="25" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E13" s="27" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G13" s="27" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H13" s="27" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I13" s="27" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J13" s="27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K13" s="27" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L13" s="27" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N13" s="27" t="n"/>
+      <c r="O13" s="27" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P13" s="27" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q13" s="27" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R13" s="27" t="n"/>
+      <c r="S13" s="27" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T13" s="27" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U13" s="27" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="40.35" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
         <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D13" s="25" t="n">
+      <c r="D14" s="26" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="E14" s="26" t="n">
         <v>38.7</v>
       </c>
-      <c r="F13" s="25" t="n">
+      <c r="F14" s="26" t="n">
         <v>38.67</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G14" s="26" t="n">
         <v>0.08</v>
       </c>
-      <c r="H13" s="25" t="n">
+      <c r="H14" s="26" t="n">
         <v>38.8</v>
       </c>
-      <c r="I13" s="25" t="n">
+      <c r="I14" s="26" t="n">
         <v>38.5</v>
       </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="25" t="n"/>
-      <c r="M13" s="25" t="n"/>
-      <c r="N13" s="25" t="n"/>
-      <c r="O13" s="25" t="n"/>
-      <c r="P13" s="25" t="n"/>
-      <c r="Q13" s="25" t="n"/>
-      <c r="R13" s="25" t="n"/>
-      <c r="S13" s="25" t="n"/>
-      <c r="T13" s="25" t="n"/>
-      <c r="U13" s="25" t="inlineStr">
+      <c r="J14" s="26" t="n"/>
+      <c r="K14" s="26" t="n"/>
+      <c r="L14" s="26" t="n"/>
+      <c r="M14" s="26" t="n"/>
+      <c r="N14" s="26" t="n"/>
+      <c r="O14" s="26" t="n"/>
+      <c r="P14" s="26" t="n"/>
+      <c r="Q14" s="26" t="n"/>
+      <c r="R14" s="26" t="n"/>
+      <c r="S14" s="26" t="n"/>
+      <c r="T14" s="26" t="n"/>
+      <c r="U14" s="26" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40.35" customHeight="1"/>
     <row r="15" ht="40.35" customHeight="1"/>
     <row r="16" ht="40.35" customHeight="1"/>
     <row r="17" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -537,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U14"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -648,12 +654,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
+      <c r="A2" s="28" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="28" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -663,66 +669,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="26" t="n">
+      <c r="D2" s="28" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="26" t="n">
+      <c r="E2" s="28" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="26" t="n">
+      <c r="F2" s="28" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="26" t="n">
+      <c r="G2" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="26" t="n">
+      <c r="H2" s="28" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="26" t="n">
+      <c r="I2" s="28" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="26" t="n">
+      <c r="J2" s="28" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="26" t="n">
+      <c r="K2" s="28" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="26" t="n">
+      <c r="L2" s="28" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="26" t="n">
+      <c r="M2" s="28" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="26" t="n"/>
-      <c r="O2" s="26" t="n">
+      <c r="N2" s="28" t="n"/>
+      <c r="O2" s="28" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="26" t="n">
+      <c r="P2" s="28" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="26" t="n">
+      <c r="Q2" s="28" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="26" t="n"/>
-      <c r="S2" s="26" t="n">
+      <c r="R2" s="28" t="n"/>
+      <c r="S2" s="28" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="26" t="n">
+      <c r="T2" s="28" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="26" t="inlineStr">
+      <c r="U2" s="28" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="27" t="inlineStr">
+      <c r="A3" s="29" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="27" t="inlineStr">
+      <c r="B3" s="29" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -732,48 +738,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="27" t="n">
+      <c r="D3" s="29" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="27" t="n">
+      <c r="E3" s="29" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="27" t="n">
+      <c r="F3" s="29" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="27" t="n">
+      <c r="G3" s="29" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="27" t="n">
+      <c r="H3" s="29" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="27" t="n">
+      <c r="I3" s="29" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-      <c r="O3" s="27" t="n"/>
-      <c r="P3" s="27" t="n"/>
-      <c r="Q3" s="27" t="n"/>
-      <c r="R3" s="27" t="n"/>
-      <c r="S3" s="27" t="n"/>
-      <c r="T3" s="27" t="n"/>
-      <c r="U3" s="27" t="inlineStr">
+      <c r="J3" s="29" t="n"/>
+      <c r="K3" s="29" t="n"/>
+      <c r="L3" s="29" t="n"/>
+      <c r="M3" s="29" t="n"/>
+      <c r="N3" s="29" t="n"/>
+      <c r="O3" s="29" t="n"/>
+      <c r="P3" s="29" t="n"/>
+      <c r="Q3" s="29" t="n"/>
+      <c r="R3" s="29" t="n"/>
+      <c r="S3" s="29" t="n"/>
+      <c r="T3" s="29" t="n"/>
+      <c r="U3" s="29" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="26" t="inlineStr">
+      <c r="A4" s="28" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -783,66 +789,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="26" t="n">
+      <c r="D4" s="28" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="26" t="n">
+      <c r="E4" s="28" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="26" t="n">
+      <c r="F4" s="28" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="26" t="n">
+      <c r="G4" s="28" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="26" t="n">
+      <c r="H4" s="28" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="26" t="n">
+      <c r="I4" s="28" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="26" t="n">
+      <c r="J4" s="28" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="26" t="n">
+      <c r="K4" s="28" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="26" t="n">
+      <c r="L4" s="28" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="26" t="n">
+      <c r="M4" s="28" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="26" t="n"/>
-      <c r="O4" s="26" t="n">
+      <c r="N4" s="28" t="n"/>
+      <c r="O4" s="28" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="26" t="n">
+      <c r="P4" s="28" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="26" t="n">
+      <c r="Q4" s="28" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="26" t="n"/>
-      <c r="S4" s="26" t="n">
+      <c r="R4" s="28" t="n"/>
+      <c r="S4" s="28" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="26" t="n">
+      <c r="T4" s="28" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="26" t="inlineStr">
+      <c r="U4" s="28" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="29" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="29" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -852,66 +858,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="29" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="29" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="29" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="27" t="n">
+      <c r="G5" s="29" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="27" t="n">
+      <c r="H5" s="29" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="27" t="n">
+      <c r="I5" s="29" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="27" t="n">
+      <c r="J5" s="29" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="27" t="n">
+      <c r="K5" s="29" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="27" t="n">
+      <c r="L5" s="29" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="29" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="27" t="n"/>
-      <c r="O5" s="27" t="n">
+      <c r="N5" s="29" t="n"/>
+      <c r="O5" s="29" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="27" t="n">
+      <c r="P5" s="29" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="27" t="n">
+      <c r="Q5" s="29" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="27" t="n"/>
-      <c r="S5" s="27" t="n">
+      <c r="R5" s="29" t="n"/>
+      <c r="S5" s="29" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="27" t="n">
+      <c r="T5" s="29" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="27" t="inlineStr">
+      <c r="U5" s="29" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="28" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
@@ -921,74 +927,74 @@
           <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
         </is>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="28" t="n">
         <v>464463.92</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="28" t="n">
         <v>412.67</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="28" t="n">
         <v>412.37</v>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="28" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="H6" s="26" t="n">
+      <c r="H6" s="28" t="n">
         <v>417.61</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="28" t="n">
         <v>397.0101</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="28" t="n">
         <v>10.52</v>
       </c>
-      <c r="K6" s="26" t="n">
+      <c r="K6" s="28" t="n">
         <v>42312</v>
       </c>
-      <c r="L6" s="26" t="n">
+      <c r="L6" s="28" t="n">
         <v>37378</v>
       </c>
-      <c r="M6" s="26" t="n">
+      <c r="M6" s="28" t="n">
         <v>15540</v>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="N6" s="28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O6" s="26" t="n">
+      <c r="O6" s="28" t="n">
         <v>11909</v>
       </c>
-      <c r="P6" s="26" t="n">
+      <c r="P6" s="28" t="n">
         <v>8539</v>
       </c>
-      <c r="Q6" s="26" t="n">
+      <c r="Q6" s="28" t="n">
         <v>-5833</v>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="R6" s="28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S6" s="26" t="n">
+      <c r="S6" s="28" t="n">
         <v>12493</v>
       </c>
-      <c r="T6" s="26" t="n">
+      <c r="T6" s="28" t="n">
         <v>10318</v>
       </c>
-      <c r="U6" s="26" t="inlineStr">
+      <c r="U6" s="28" t="inlineStr">
         <is>
           <t>2026-03-02 17:28:51</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="29" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -998,66 +1004,66 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="29" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="29" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="29" t="n">
         <v>84.607</v>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="29" t="n">
         <v>13.75</v>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="29" t="n">
         <v>96.75</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="29" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J7" s="29" t="n">
         <v>2.53</v>
       </c>
-      <c r="K7" s="27" t="n">
+      <c r="K7" s="29" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L7" s="27" t="n">
+      <c r="L7" s="29" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="29" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N7" s="27" t="n"/>
-      <c r="O7" s="27" t="n">
+      <c r="N7" s="29" t="n"/>
+      <c r="O7" s="29" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P7" s="27" t="n">
+      <c r="P7" s="29" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q7" s="27" t="n">
+      <c r="Q7" s="29" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R7" s="27" t="n"/>
-      <c r="S7" s="27" t="n">
+      <c r="R7" s="29" t="n"/>
+      <c r="S7" s="29" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T7" s="27" t="n">
+      <c r="T7" s="29" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U7" s="27" t="inlineStr">
+      <c r="U7" s="29" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>NIO</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>NIO Inc.</t>
         </is>
@@ -1067,74 +1073,74 @@
           <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
         </is>
       </c>
-      <c r="D8" s="26" t="n">
+      <c r="D8" s="28" t="n">
         <v>11935.27</v>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="28" t="n">
         <v>4.72</v>
       </c>
-      <c r="F8" s="26" t="n">
+      <c r="F8" s="28" t="n">
         <v>4.87</v>
       </c>
-      <c r="G8" s="26" t="n">
+      <c r="G8" s="28" t="n">
         <v>-3.08</v>
       </c>
-      <c r="H8" s="26" t="n">
+      <c r="H8" s="28" t="n">
         <v>4.79</v>
       </c>
-      <c r="I8" s="26" t="n">
+      <c r="I8" s="28" t="n">
         <v>4.64</v>
       </c>
-      <c r="J8" s="26" t="n">
+      <c r="J8" s="28" t="n">
         <v>-1.68</v>
       </c>
-      <c r="K8" s="26" t="n">
+      <c r="K8" s="28" t="n">
         <v>72540.69</v>
       </c>
-      <c r="L8" s="26" t="n">
+      <c r="L8" s="28" t="n">
         <v>65731.56</v>
       </c>
-      <c r="M8" s="26" t="n">
+      <c r="M8" s="28" t="n">
         <v>49268.56</v>
       </c>
-      <c r="N8" s="26" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="26" t="n">
+      <c r="O8" s="28" t="n">
         <v>-22824.89</v>
       </c>
-      <c r="P8" s="26" t="n">
+      <c r="P8" s="28" t="n">
         <v>-22657.69</v>
       </c>
-      <c r="Q8" s="26" t="n">
+      <c r="Q8" s="28" t="n">
         <v>-14559.44</v>
       </c>
-      <c r="R8" s="26" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="26" t="n">
+      <c r="S8" s="28" t="n">
         <v>27640.48</v>
       </c>
-      <c r="T8" s="26" t="n">
+      <c r="T8" s="28" t="n">
         <v>24106.16</v>
       </c>
-      <c r="U8" s="26" t="inlineStr">
+      <c r="U8" s="28" t="inlineStr">
         <is>
           <t>2026-03-02 17:52:03</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="27" t="inlineStr">
+      <c r="A9" s="29" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B9" s="27" t="inlineStr">
+      <c r="B9" s="29" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -1144,394 +1150,326 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="29" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="29" t="n">
         <v>177.19</v>
       </c>
-      <c r="F9" s="27" t="n">
+      <c r="F9" s="29" t="n">
         <v>184.89</v>
       </c>
-      <c r="G9" s="27" t="n">
+      <c r="G9" s="29" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H9" s="27" t="n">
+      <c r="H9" s="29" t="n">
         <v>182.58</v>
       </c>
-      <c r="I9" s="27" t="n">
+      <c r="I9" s="29" t="n">
         <v>176.38</v>
       </c>
-      <c r="J9" s="27" t="n">
+      <c r="J9" s="29" t="n">
         <v>4.91</v>
       </c>
-      <c r="K9" s="27" t="n">
+      <c r="K9" s="29" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L9" s="27" t="n">
+      <c r="L9" s="29" t="n">
         <v>215938</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="29" t="n">
         <v>60922</v>
       </c>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n">
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="29" t="n">
         <v>120067</v>
       </c>
-      <c r="P9" s="27" t="n">
+      <c r="P9" s="29" t="n">
         <v>120067</v>
       </c>
-      <c r="Q9" s="27" t="n">
+      <c r="Q9" s="29" t="n">
         <v>29760</v>
       </c>
-      <c r="R9" s="27" t="n"/>
-      <c r="S9" s="27" t="n">
+      <c r="R9" s="29" t="n"/>
+      <c r="S9" s="29" t="n">
         <v>11412</v>
       </c>
-      <c r="T9" s="27" t="n">
+      <c r="T9" s="29" t="n">
         <v>62556</v>
       </c>
-      <c r="U9" s="27" t="inlineStr">
+      <c r="U9" s="29" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="26" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="B10" s="26" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B10" s="28" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
-        </is>
-      </c>
-      <c r="D10" s="26" t="n">
-        <v>328113.98</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>137.19</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>135.94</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>138.1</v>
-      </c>
-      <c r="I10" s="26" t="n">
-        <v>133.99</v>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="K10" s="26" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="L10" s="26" t="n">
-        <v>4475.45</v>
-      </c>
-      <c r="M10" s="26" t="n">
-        <v>2225.01</v>
-      </c>
-      <c r="N10" s="26" t="n"/>
-      <c r="O10" s="26" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="P10" s="26" t="n">
-        <v>1625.03</v>
-      </c>
-      <c r="Q10" s="26" t="n">
-        <v>209.82</v>
-      </c>
-      <c r="R10" s="26" t="n"/>
-      <c r="S10" s="26" t="n">
-        <v>229.34</v>
-      </c>
-      <c r="T10" s="26" t="n">
-        <v>7177.04</v>
-      </c>
-      <c r="U10" s="26" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:48:23</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I10" s="28" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J10" s="28" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K10" s="28" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L10" s="28" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M10" s="28" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N10" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P10" s="28" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q10" s="28" t="n">
+        <v>132</v>
+      </c>
+      <c r="R10" s="28" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S10" s="28" t="n">
+        <v>188</v>
+      </c>
+      <c r="T10" s="28" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U10" s="28" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="27" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A11" s="29" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J11" s="27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K11" s="27" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L11" s="27" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M11" s="27" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N11" s="27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O11" s="27" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P11" s="27" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q11" s="27" t="n">
-        <v>132</v>
-      </c>
-      <c r="R11" s="27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S11" s="27" t="n">
-        <v>188</v>
-      </c>
-      <c r="T11" s="27" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U11" s="27" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I11" s="29" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K11" s="29" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L11" s="29" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M11" s="29" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N11" s="29" t="n"/>
+      <c r="O11" s="29" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P11" s="29" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q11" s="29" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R11" s="29" t="n"/>
+      <c r="S11" s="29" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T11" s="29" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U11" s="29" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B12" s="26" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E12" s="26" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F12" s="26" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G12" s="26" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I12" s="26" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J12" s="26" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K12" s="26" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L12" s="26" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M12" s="26" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P12" s="26" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q12" s="26" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R12" s="26" t="n"/>
-      <c r="S12" s="26" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T12" s="26" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U12" s="26" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E12" s="28" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F12" s="28" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G12" s="28" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H12" s="28" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I12" s="28" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J12" s="28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K12" s="28" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L12" s="28" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M12" s="28" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N12" s="28" t="n"/>
+      <c r="O12" s="28" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P12" s="28" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q12" s="28" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R12" s="28" t="n"/>
+      <c r="S12" s="28" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T12" s="28" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U12" s="28" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="27" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B13" s="27" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A13" s="29" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B13" s="29" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D13" s="27" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E13" s="27" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F13" s="27" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G13" s="27" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J13" s="27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K13" s="27" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L13" s="27" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M13" s="27" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N13" s="27" t="n"/>
-      <c r="O13" s="27" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P13" s="27" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q13" s="27" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R13" s="27" t="n"/>
-      <c r="S13" s="27" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T13" s="27" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U13" s="27" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G13" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I13" s="29" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J13" s="29" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="29" t="n"/>
+      <c r="O13" s="29" t="n"/>
+      <c r="P13" s="29" t="n"/>
+      <c r="Q13" s="29" t="n"/>
+      <c r="R13" s="29" t="n"/>
+      <c r="S13" s="29" t="n"/>
+      <c r="T13" s="29" t="n"/>
+      <c r="U13" s="29" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="40.35" customHeight="1">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B14" s="26" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D14" s="26" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I14" s="26" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="26" t="n"/>
-      <c r="L14" s="26" t="n"/>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="26" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="26" t="n"/>
-      <c r="R14" s="26" t="n"/>
-      <c r="S14" s="26" t="n"/>
-      <c r="T14" s="26" t="n"/>
-      <c r="U14" s="26" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="14" ht="40.35" customHeight="1"/>
     <row r="15" ht="40.35" customHeight="1"/>
     <row r="16" ht="40.35" customHeight="1"/>
     <row r="17" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1210,256 +1210,333 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SHOP.TO</t>
+          <t>RKLB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Shopify Inc.</t>
+          <t>Rocket Lab Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+          <t>Rocket Lab Corporation, a space company, provides launch services and space systems solutions in the United States, Canada, Japan, and internationally. The company provides launch services, spacecraft design services, spacecraft components, spacecraft manufacturing, and other spacecraft and on-orbit management solutions; and constellation management services, as well as designs and manufactures small and medium-class rockets. It also designs, manufactures, and sells Electron, an orbital small launch vehicle for small spacecraft launch services, as well as develops Neutron launch vehicles for large constellation deployments, interplanetary missions and potentially for human spaceflight. In addition, the company designs and manufactures a range of components and subsystems for its launch vehicles and spacecraft. It serves commercial, aerospace prime contractors, and government customers. Rocket Lab Corporation was founded in 2006 and is headquartered in Long Beach, California.</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>213981.48</v>
+        <v>37909.07</v>
       </c>
       <c r="E12" t="n">
-        <v>163.32</v>
+        <v>70.97</v>
       </c>
       <c r="F12" t="n">
-        <v>164.67</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.82</v>
+        <v>2.71</v>
       </c>
       <c r="H12" t="n">
-        <v>164.76</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>156.66</v>
+        <v>66.45</v>
       </c>
       <c r="J12" t="n">
-        <v>1.28</v>
+        <v>-0.38</v>
       </c>
       <c r="K12" t="n">
-        <v>11556</v>
+        <v>601.8</v>
       </c>
       <c r="L12" t="n">
-        <v>11556</v>
+        <v>436.21</v>
       </c>
       <c r="M12" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O12" t="n">
-        <v>1231</v>
+        <v>-198.21</v>
       </c>
       <c r="P12" t="n">
-        <v>1231</v>
+        <v>-190.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>132</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>-135.94</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="S12" t="n">
-        <v>188</v>
+        <v>265.09</v>
       </c>
       <c r="T12" t="n">
-        <v>5847</v>
+        <v>1016.58</v>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>2026-03-02 22:55:02</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TD.TO</t>
+          <t>SHOP.TO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank</t>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>223066.26</v>
+        <v>213981.48</v>
       </c>
       <c r="E13" t="n">
-        <v>132.88</v>
+        <v>163.32</v>
       </c>
       <c r="F13" t="n">
-        <v>135.14</v>
+        <v>164.67</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.67</v>
+        <v>-0.82</v>
       </c>
       <c r="H13" t="n">
-        <v>136.49</v>
+        <v>164.76</v>
       </c>
       <c r="I13" t="n">
-        <v>132.48</v>
+        <v>156.66</v>
       </c>
       <c r="J13" t="n">
-        <v>11.56</v>
+        <v>1.28</v>
       </c>
       <c r="K13" t="n">
-        <v>65980</v>
+        <v>11556</v>
       </c>
       <c r="L13" t="n">
-        <v>61281</v>
+        <v>11556</v>
       </c>
       <c r="M13" t="n">
-        <v>51524</v>
+        <v>7060</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="n">
-        <v>21208</v>
+        <v>1231</v>
       </c>
       <c r="P13" t="n">
-        <v>20538</v>
+        <v>1231</v>
       </c>
       <c r="Q13" t="n">
-        <v>10634</v>
+        <v>132</v>
       </c>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>528488.99</v>
+        <v>188</v>
       </c>
       <c r="T13" t="n">
-        <v>654255</v>
+        <v>5847</v>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>TD.TO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1510391.41</v>
+        <v>223066.26</v>
       </c>
       <c r="E14" t="n">
-        <v>402.51</v>
+        <v>132.88</v>
       </c>
       <c r="F14" t="n">
-        <v>408.58</v>
+        <v>135.14</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.49</v>
+        <v>-1.67</v>
       </c>
       <c r="H14" t="n">
-        <v>407.11</v>
+        <v>136.49</v>
       </c>
       <c r="I14" t="n">
-        <v>398.12</v>
+        <v>132.48</v>
       </c>
       <c r="J14" t="n">
-        <v>1.09</v>
+        <v>11.56</v>
       </c>
       <c r="K14" t="n">
-        <v>94827</v>
+        <v>65980</v>
       </c>
       <c r="L14" t="n">
-        <v>94827</v>
+        <v>61281</v>
       </c>
       <c r="M14" t="n">
-        <v>96773</v>
+        <v>51524</v>
       </c>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="n">
-        <v>3794</v>
+        <v>21208</v>
       </c>
       <c r="P14" t="n">
-        <v>3794</v>
+        <v>20538</v>
       </c>
       <c r="Q14" t="n">
-        <v>14999</v>
+        <v>10634</v>
       </c>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>14719</v>
+        <v>528488.99</v>
       </c>
       <c r="T14" t="n">
-        <v>44059</v>
+        <v>654255</v>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E15" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F15" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H15" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I15" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L15" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M15" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T15" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>XDIV.TO</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
         </is>
       </c>
-      <c r="D15" t="n">
+      <c r="D16" t="n">
         <v>3940.24</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E16" t="n">
         <v>38.7</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F16" t="n">
         <v>38.67</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G16" t="n">
         <v>0.08</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H16" t="n">
         <v>38.8</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I16" t="n">
         <v>38.5</v>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr">
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:02</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -543,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -654,12 +660,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="28" t="inlineStr">
+      <c r="A2" s="30" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="28" t="inlineStr">
+      <c r="B2" s="30" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -669,66 +675,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="28" t="n">
+      <c r="D2" s="30" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="28" t="n">
+      <c r="E2" s="30" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="28" t="n">
+      <c r="F2" s="30" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="28" t="n">
+      <c r="G2" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="28" t="n">
+      <c r="H2" s="30" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="28" t="n">
+      <c r="I2" s="30" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="28" t="n">
+      <c r="J2" s="30" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="28" t="n">
+      <c r="K2" s="30" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="28" t="n">
+      <c r="L2" s="30" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="28" t="n">
+      <c r="M2" s="30" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="28" t="n"/>
-      <c r="O2" s="28" t="n">
+      <c r="N2" s="30" t="n"/>
+      <c r="O2" s="30" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="28" t="n">
+      <c r="P2" s="30" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="28" t="n">
+      <c r="Q2" s="30" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="28" t="n"/>
-      <c r="S2" s="28" t="n">
+      <c r="R2" s="30" t="n"/>
+      <c r="S2" s="30" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="28" t="n">
+      <c r="T2" s="30" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="28" t="inlineStr">
+      <c r="U2" s="30" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="31" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="29" t="inlineStr">
+      <c r="B3" s="31" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -738,48 +744,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="29" t="n">
+      <c r="D3" s="31" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="29" t="n">
+      <c r="E3" s="31" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="29" t="n">
+      <c r="F3" s="31" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="29" t="n">
+      <c r="G3" s="31" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="29" t="n">
+      <c r="H3" s="31" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="29" t="n">
+      <c r="I3" s="31" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="29" t="n"/>
-      <c r="K3" s="29" t="n"/>
-      <c r="L3" s="29" t="n"/>
-      <c r="M3" s="29" t="n"/>
-      <c r="N3" s="29" t="n"/>
-      <c r="O3" s="29" t="n"/>
-      <c r="P3" s="29" t="n"/>
-      <c r="Q3" s="29" t="n"/>
-      <c r="R3" s="29" t="n"/>
-      <c r="S3" s="29" t="n"/>
-      <c r="T3" s="29" t="n"/>
-      <c r="U3" s="29" t="inlineStr">
+      <c r="J3" s="31" t="n"/>
+      <c r="K3" s="31" t="n"/>
+      <c r="L3" s="31" t="n"/>
+      <c r="M3" s="31" t="n"/>
+      <c r="N3" s="31" t="n"/>
+      <c r="O3" s="31" t="n"/>
+      <c r="P3" s="31" t="n"/>
+      <c r="Q3" s="31" t="n"/>
+      <c r="R3" s="31" t="n"/>
+      <c r="S3" s="31" t="n"/>
+      <c r="T3" s="31" t="n"/>
+      <c r="U3" s="31" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="28" t="inlineStr">
+      <c r="A4" s="30" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="28" t="inlineStr">
+      <c r="B4" s="30" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -789,66 +795,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="30" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="30" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="30" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="28" t="n">
+      <c r="G4" s="30" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="30" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="30" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="28" t="n">
+      <c r="J4" s="30" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="28" t="n">
+      <c r="K4" s="30" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="28" t="n">
+      <c r="L4" s="30" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="28" t="n">
+      <c r="M4" s="30" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="28" t="n"/>
-      <c r="O4" s="28" t="n">
+      <c r="N4" s="30" t="n"/>
+      <c r="O4" s="30" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="28" t="n">
+      <c r="P4" s="30" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="28" t="n">
+      <c r="Q4" s="30" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="28" t="n"/>
-      <c r="S4" s="28" t="n">
+      <c r="R4" s="30" t="n"/>
+      <c r="S4" s="30" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="28" t="n">
+      <c r="T4" s="30" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="28" t="inlineStr">
+      <c r="U4" s="30" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="31" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="31" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -858,617 +864,541 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="31" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="31" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="31" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="29" t="n">
+      <c r="G5" s="31" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="29" t="n">
+      <c r="H5" s="31" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="29" t="n">
+      <c r="I5" s="31" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="29" t="n">
+      <c r="J5" s="31" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="29" t="n">
+      <c r="K5" s="31" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="29" t="n">
+      <c r="L5" s="31" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="29" t="n">
+      <c r="M5" s="31" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="29" t="n"/>
-      <c r="O5" s="29" t="n">
+      <c r="N5" s="31" t="n"/>
+      <c r="O5" s="31" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="29" t="n">
+      <c r="P5" s="31" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="29" t="n">
+      <c r="Q5" s="31" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="29" t="n"/>
-      <c r="S5" s="29" t="n">
+      <c r="R5" s="31" t="n"/>
+      <c r="S5" s="31" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="29" t="n">
+      <c r="T5" s="31" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="29" t="inlineStr">
+      <c r="U5" s="31" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="28" t="inlineStr">
-        <is>
-          <t>MU</t>
-        </is>
-      </c>
-      <c r="B6" s="28" t="inlineStr">
-        <is>
-          <t>Micron Technology, Inc.</t>
+      <c r="A6" s="30" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Micron Technology, Inc. designs, develops, manufactures, and sells memory and storage products in the United States, Taiwan, Japan, Mainland China, Hong Kong, Europe, and internationally. It operates through the Cloud Memory Business Unit; Core Data Center Business Unit; Mobile and Client Business Unit; and Automotive and Embedded Business Unit segments. The company provides memory products, including dynamic random access memory components and modules, CXL-based memory, LPDDR components and modules, graphics memory, high-bandwidth memory, and data center memory products; multichip packages (MCP) comprising embedded multimedia card-based, universal flash storage-based, and NAND-based MCPs; and technology leadership products that include 1y DRAM and G9 NAND technologies. It also offers storage products, such as data center solid-state drives (SSD), client SSD storage, and auto and industrial SSD storage; managed NAND; NAND flash; NOR flash; and memory cards. In addition, the company provides design tools, including FBGA and part decoders; DRAM power calculators; NAND power calculators; simulation models; chipset compatibility guides; serial presence-detection tools; cross-reference tools; UFSparm; SSD firmware; software and drivers; storage executive software; and obsolete part catalogs. It markets its semiconductor memory and storage products under the Micron and Crucial brands. The company serves the data center, PC, graphics, networking, automotive, industrial, and consumer embedded markets, as well as the smartphone and other mobile-device markets. It sells its products through its direct sales force, independent sales representatives, distributors, and retailers; web-based customer direct sales channel; and channel and distribution partners. Micron Technology, Inc. was founded in 1978 and is headquartered in Boise, Idaho.</t>
-        </is>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>464463.92</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>412.67</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>412.37</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>417.61</v>
-      </c>
-      <c r="I6" s="28" t="n">
-        <v>397.0101</v>
-      </c>
-      <c r="J6" s="28" t="n">
-        <v>10.52</v>
-      </c>
-      <c r="K6" s="28" t="n">
-        <v>42312</v>
-      </c>
-      <c r="L6" s="28" t="n">
-        <v>37378</v>
-      </c>
-      <c r="M6" s="28" t="n">
-        <v>15540</v>
-      </c>
-      <c r="N6" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O6" s="28" t="n">
-        <v>11909</v>
-      </c>
-      <c r="P6" s="28" t="n">
-        <v>8539</v>
-      </c>
-      <c r="Q6" s="28" t="n">
-        <v>-5833</v>
-      </c>
-      <c r="R6" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S6" s="28" t="n">
-        <v>12493</v>
-      </c>
-      <c r="T6" s="28" t="n">
-        <v>10318</v>
-      </c>
-      <c r="U6" s="28" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:28:51</t>
+          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
+        </is>
+      </c>
+      <c r="D6" s="30" t="n">
+        <v>408239.44</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>96.23999999999999</v>
+      </c>
+      <c r="F6" s="30" t="n">
+        <v>84.607</v>
+      </c>
+      <c r="G6" s="30" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="I6" s="30" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="J6" s="30" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K6" s="30" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="L6" s="30" t="n">
+        <v>45183.04</v>
+      </c>
+      <c r="M6" s="30" t="n">
+        <v>33723.3</v>
+      </c>
+      <c r="N6" s="30" t="n"/>
+      <c r="O6" s="30" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="P6" s="30" t="n">
+        <v>10981.2</v>
+      </c>
+      <c r="Q6" s="30" t="n">
+        <v>5407.99</v>
+      </c>
+      <c r="R6" s="30" t="n"/>
+      <c r="S6" s="30" t="n">
+        <v>16975.84</v>
+      </c>
+      <c r="T6" s="30" t="n">
+        <v>9062.360000000001</v>
+      </c>
+      <c r="U6" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D7" s="29" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I7" s="29" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J7" s="29" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K7" s="29" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L7" s="29" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M7" s="29" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N7" s="29" t="n"/>
-      <c r="O7" s="29" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P7" s="29" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q7" s="29" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R7" s="29" t="n"/>
-      <c r="S7" s="29" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T7" s="29" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U7" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>11935.27</v>
+      </c>
+      <c r="E7" s="31" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G7" s="31" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="H7" s="31" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J7" s="31" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K7" s="31" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L7" s="31" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M7" s="31" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N7" s="31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O7" s="31" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P7" s="31" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q7" s="31" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R7" s="31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S7" s="31" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T7" s="31" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U7" s="31" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:52:03</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="28" t="inlineStr">
-        <is>
-          <t>NIO</t>
-        </is>
-      </c>
-      <c r="B8" s="28" t="inlineStr">
-        <is>
-          <t>NIO Inc.</t>
+      <c r="A8" s="30" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
-        </is>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>11935.27</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="I8" s="28" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J8" s="28" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="K8" s="28" t="n">
-        <v>72540.69</v>
-      </c>
-      <c r="L8" s="28" t="n">
-        <v>65731.56</v>
-      </c>
-      <c r="M8" s="28" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N8" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="28" t="n">
-        <v>-22824.89</v>
-      </c>
-      <c r="P8" s="28" t="n">
-        <v>-22657.69</v>
-      </c>
-      <c r="Q8" s="28" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R8" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="28" t="n">
-        <v>27640.48</v>
-      </c>
-      <c r="T8" s="28" t="n">
-        <v>24106.16</v>
-      </c>
-      <c r="U8" s="28" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:52:03</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D8" s="30" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F8" s="30" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G8" s="30" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I8" s="30" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J8" s="30" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K8" s="30" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L8" s="30" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M8" s="30" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N8" s="30" t="n"/>
+      <c r="O8" s="30" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P8" s="30" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q8" s="30" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R8" s="30" t="n"/>
+      <c r="S8" s="30" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T8" s="30" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U8" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D9" s="29" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I9" s="29" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J9" s="29" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K9" s="29" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L9" s="29" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M9" s="29" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="29" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P9" s="29" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q9" s="29" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R9" s="29" t="n"/>
-      <c r="S9" s="29" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T9" s="29" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U9" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E9" s="31" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G9" s="31" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H9" s="31" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J9" s="31" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K9" s="31" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L9" s="31" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M9" s="31" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N9" s="31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="31" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P9" s="31" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q9" s="31" t="n">
+        <v>132</v>
+      </c>
+      <c r="R9" s="31" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S9" s="31" t="n">
+        <v>188</v>
+      </c>
+      <c r="T9" s="31" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U9" s="31" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B10" s="28" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A10" s="30" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J10" s="28" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K10" s="28" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L10" s="28" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M10" s="28" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N10" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O10" s="28" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P10" s="28" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q10" s="28" t="n">
-        <v>132</v>
-      </c>
-      <c r="R10" s="28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S10" s="28" t="n">
-        <v>188</v>
-      </c>
-      <c r="T10" s="28" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U10" s="28" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D10" s="30" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F10" s="30" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G10" s="30" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I10" s="30" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J10" s="30" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K10" s="30" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L10" s="30" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M10" s="30" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N10" s="30" t="n"/>
+      <c r="O10" s="30" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P10" s="30" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q10" s="30" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R10" s="30" t="n"/>
+      <c r="S10" s="30" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T10" s="30" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U10" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D11" s="29" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F11" s="29" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G11" s="29" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I11" s="29" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J11" s="29" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K11" s="29" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L11" s="29" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M11" s="29" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="29" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P11" s="29" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q11" s="29" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R11" s="29" t="n"/>
-      <c r="S11" s="29" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T11" s="29" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U11" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E11" s="31" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G11" s="31" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H11" s="31" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I11" s="31" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J11" s="31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K11" s="31" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L11" s="31" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M11" s="31" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P11" s="31" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q11" s="31" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R11" s="31" t="n"/>
+      <c r="S11" s="31" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T11" s="31" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U11" s="31" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="28" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B12" s="28" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D12" s="28" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E12" s="28" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F12" s="28" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G12" s="28" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H12" s="28" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I12" s="28" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J12" s="28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K12" s="28" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L12" s="28" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M12" s="28" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N12" s="28" t="n"/>
-      <c r="O12" s="28" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P12" s="28" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q12" s="28" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R12" s="28" t="n"/>
-      <c r="S12" s="28" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T12" s="28" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U12" s="28" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D12" s="30" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F12" s="30" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G12" s="30" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H12" s="30" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I12" s="30" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="30" t="n"/>
+      <c r="L12" s="30" t="n"/>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="30" t="n"/>
+      <c r="P12" s="30" t="n"/>
+      <c r="Q12" s="30" t="n"/>
+      <c r="R12" s="30" t="n"/>
+      <c r="S12" s="30" t="n"/>
+      <c r="T12" s="30" t="n"/>
+      <c r="U12" s="30" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="40.35" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B13" s="29" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D13" s="29" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E13" s="29" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F13" s="29" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G13" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H13" s="29" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I13" s="29" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="29" t="n"/>
-      <c r="L13" s="29" t="n"/>
-      <c r="M13" s="29" t="n"/>
-      <c r="N13" s="29" t="n"/>
-      <c r="O13" s="29" t="n"/>
-      <c r="P13" s="29" t="n"/>
-      <c r="Q13" s="29" t="n"/>
-      <c r="R13" s="29" t="n"/>
-      <c r="S13" s="29" t="n"/>
-      <c r="T13" s="29" t="n"/>
-      <c r="U13" s="29" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="13" ht="40.35" customHeight="1"/>
     <row r="14" ht="40.35" customHeight="1"/>
     <row r="15" ht="40.35" customHeight="1"/>
     <row r="16" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -549,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -660,12 +666,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="30" t="inlineStr">
+      <c r="A2" s="32" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="30" t="inlineStr">
+      <c r="B2" s="32" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -675,66 +681,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="30" t="n">
+      <c r="D2" s="32" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="30" t="n">
+      <c r="E2" s="32" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="30" t="n">
+      <c r="F2" s="32" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="30" t="n">
+      <c r="G2" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="30" t="n">
+      <c r="H2" s="32" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="30" t="n">
+      <c r="I2" s="32" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="30" t="n">
+      <c r="J2" s="32" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="30" t="n">
+      <c r="K2" s="32" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="30" t="n">
+      <c r="L2" s="32" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="30" t="n">
+      <c r="M2" s="32" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="30" t="n"/>
-      <c r="O2" s="30" t="n">
+      <c r="N2" s="32" t="n"/>
+      <c r="O2" s="32" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="30" t="n">
+      <c r="P2" s="32" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="30" t="n">
+      <c r="Q2" s="32" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="30" t="n"/>
-      <c r="S2" s="30" t="n">
+      <c r="R2" s="32" t="n"/>
+      <c r="S2" s="32" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="30" t="n">
+      <c r="T2" s="32" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="30" t="inlineStr">
+      <c r="U2" s="32" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="31" t="inlineStr">
+      <c r="A3" s="33" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="31" t="inlineStr">
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -744,48 +750,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="31" t="n">
+      <c r="D3" s="33" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="31" t="n">
+      <c r="E3" s="33" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="33" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="31" t="n">
+      <c r="G3" s="33" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="31" t="n">
+      <c r="H3" s="33" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="31" t="n">
+      <c r="I3" s="33" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="31" t="n"/>
-      <c r="K3" s="31" t="n"/>
-      <c r="L3" s="31" t="n"/>
-      <c r="M3" s="31" t="n"/>
-      <c r="N3" s="31" t="n"/>
-      <c r="O3" s="31" t="n"/>
-      <c r="P3" s="31" t="n"/>
-      <c r="Q3" s="31" t="n"/>
-      <c r="R3" s="31" t="n"/>
-      <c r="S3" s="31" t="n"/>
-      <c r="T3" s="31" t="n"/>
-      <c r="U3" s="31" t="inlineStr">
+      <c r="J3" s="33" t="n"/>
+      <c r="K3" s="33" t="n"/>
+      <c r="L3" s="33" t="n"/>
+      <c r="M3" s="33" t="n"/>
+      <c r="N3" s="33" t="n"/>
+      <c r="O3" s="33" t="n"/>
+      <c r="P3" s="33" t="n"/>
+      <c r="Q3" s="33" t="n"/>
+      <c r="R3" s="33" t="n"/>
+      <c r="S3" s="33" t="n"/>
+      <c r="T3" s="33" t="n"/>
+      <c r="U3" s="33" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="32" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="32" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -795,66 +801,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="30" t="n">
+      <c r="D4" s="32" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="30" t="n">
+      <c r="E4" s="32" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="30" t="n">
+      <c r="F4" s="32" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="30" t="n">
+      <c r="G4" s="32" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="30" t="n">
+      <c r="H4" s="32" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="30" t="n">
+      <c r="I4" s="32" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="30" t="n">
+      <c r="J4" s="32" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="30" t="n">
+      <c r="K4" s="32" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="30" t="n">
+      <c r="L4" s="32" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="30" t="n">
+      <c r="M4" s="32" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="30" t="n"/>
-      <c r="O4" s="30" t="n">
+      <c r="N4" s="32" t="n"/>
+      <c r="O4" s="32" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="30" t="n">
+      <c r="P4" s="32" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="30" t="n">
+      <c r="Q4" s="32" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="30" t="n"/>
-      <c r="S4" s="30" t="n">
+      <c r="R4" s="32" t="n"/>
+      <c r="S4" s="32" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="30" t="n">
+      <c r="T4" s="32" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="30" t="inlineStr">
+      <c r="U4" s="32" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="33" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -864,66 +870,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="31" t="n">
+      <c r="D5" s="33" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="31" t="n">
+      <c r="E5" s="33" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="33" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="31" t="n">
+      <c r="G5" s="33" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="31" t="n">
+      <c r="H5" s="33" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="31" t="n">
+      <c r="I5" s="33" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="33" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="31" t="n">
+      <c r="K5" s="33" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="31" t="n">
+      <c r="L5" s="33" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="31" t="n">
+      <c r="M5" s="33" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="31" t="n"/>
-      <c r="O5" s="31" t="n">
+      <c r="N5" s="33" t="n"/>
+      <c r="O5" s="33" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="31" t="n">
+      <c r="P5" s="33" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="31" t="n">
+      <c r="Q5" s="33" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="31" t="n"/>
-      <c r="S5" s="31" t="n">
+      <c r="R5" s="33" t="n"/>
+      <c r="S5" s="33" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="31" t="n">
+      <c r="T5" s="33" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="31" t="inlineStr">
+      <c r="U5" s="33" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B6" s="30" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -933,471 +939,395 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="32" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="32" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="32" t="n">
         <v>84.607</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="32" t="n">
         <v>13.75</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="32" t="n">
         <v>96.75</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="32" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J6" s="30" t="n">
+      <c r="J6" s="32" t="n">
         <v>2.53</v>
       </c>
-      <c r="K6" s="30" t="n">
+      <c r="K6" s="32" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L6" s="30" t="n">
+      <c r="L6" s="32" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M6" s="30" t="n">
+      <c r="M6" s="32" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N6" s="30" t="n"/>
-      <c r="O6" s="30" t="n">
+      <c r="N6" s="32" t="n"/>
+      <c r="O6" s="32" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P6" s="30" t="n">
+      <c r="P6" s="32" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q6" s="30" t="n">
+      <c r="Q6" s="32" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R6" s="30" t="n"/>
-      <c r="S6" s="30" t="n">
+      <c r="R6" s="32" t="n"/>
+      <c r="S6" s="32" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T6" s="30" t="n">
+      <c r="T6" s="32" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U6" s="30" t="inlineStr">
+      <c r="U6" s="32" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
-        <is>
-          <t>NIO</t>
-        </is>
-      </c>
-      <c r="B7" s="31" t="inlineStr">
-        <is>
-          <t>NIO Inc.</t>
+      <c r="A7" s="33" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B7" s="33" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
-        </is>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>11935.27</v>
-      </c>
-      <c r="E7" s="31" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="G7" s="31" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="H7" s="31" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="I7" s="31" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J7" s="31" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="K7" s="31" t="n">
-        <v>72540.69</v>
-      </c>
-      <c r="L7" s="31" t="n">
-        <v>65731.56</v>
-      </c>
-      <c r="M7" s="31" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N7" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O7" s="31" t="n">
-        <v>-22824.89</v>
-      </c>
-      <c r="P7" s="31" t="n">
-        <v>-22657.69</v>
-      </c>
-      <c r="Q7" s="31" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R7" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S7" s="31" t="n">
-        <v>27640.48</v>
-      </c>
-      <c r="T7" s="31" t="n">
-        <v>24106.16</v>
-      </c>
-      <c r="U7" s="31" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:52:03</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D7" s="33" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E7" s="33" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F7" s="33" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G7" s="33" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H7" s="33" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I7" s="33" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K7" s="33" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L7" s="33" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M7" s="33" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N7" s="33" t="n"/>
+      <c r="O7" s="33" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P7" s="33" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q7" s="33" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R7" s="33" t="n"/>
+      <c r="S7" s="33" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T7" s="33" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U7" s="33" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A8" s="32" t="inlineStr">
+        <is>
+          <t>SHOP.TO</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="inlineStr">
+        <is>
+          <t>Shopify Inc.</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F8" s="30" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G8" s="30" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I8" s="30" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J8" s="30" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K8" s="30" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L8" s="30" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M8" s="30" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N8" s="30" t="n"/>
-      <c r="O8" s="30" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P8" s="30" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q8" s="30" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R8" s="30" t="n"/>
-      <c r="S8" s="30" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T8" s="30" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U8" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
+        </is>
+      </c>
+      <c r="D8" s="32" t="n">
+        <v>213981.48</v>
+      </c>
+      <c r="E8" s="32" t="n">
+        <v>163.32</v>
+      </c>
+      <c r="F8" s="32" t="n">
+        <v>164.67</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="H8" s="32" t="n">
+        <v>164.76</v>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>156.66</v>
+      </c>
+      <c r="J8" s="32" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>11556</v>
+      </c>
+      <c r="L8" s="32" t="n">
+        <v>11556</v>
+      </c>
+      <c r="M8" s="32" t="n">
+        <v>7060</v>
+      </c>
+      <c r="N8" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="32" t="n">
+        <v>1231</v>
+      </c>
+      <c r="P8" s="32" t="n">
+        <v>1231</v>
+      </c>
+      <c r="Q8" s="32" t="n">
+        <v>132</v>
+      </c>
+      <c r="R8" s="32" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S8" s="32" t="n">
+        <v>188</v>
+      </c>
+      <c r="T8" s="32" t="n">
+        <v>5847</v>
+      </c>
+      <c r="U8" s="32" t="inlineStr">
+        <is>
+          <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="31" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A9" s="33" t="inlineStr">
+        <is>
+          <t>TD.TO</t>
+        </is>
+      </c>
+      <c r="B9" s="33" t="inlineStr">
+        <is>
+          <t>The Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E9" s="31" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F9" s="31" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G9" s="31" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H9" s="31" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I9" s="31" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J9" s="31" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K9" s="31" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L9" s="31" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M9" s="31" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N9" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" s="31" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P9" s="31" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q9" s="31" t="n">
-        <v>132</v>
-      </c>
-      <c r="R9" s="31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S9" s="31" t="n">
-        <v>188</v>
-      </c>
-      <c r="T9" s="31" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U9" s="31" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
+        </is>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>223066.26</v>
+      </c>
+      <c r="E9" s="33" t="n">
+        <v>132.88</v>
+      </c>
+      <c r="F9" s="33" t="n">
+        <v>135.14</v>
+      </c>
+      <c r="G9" s="33" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="H9" s="33" t="n">
+        <v>136.49</v>
+      </c>
+      <c r="I9" s="33" t="n">
+        <v>132.48</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="K9" s="33" t="n">
+        <v>65980</v>
+      </c>
+      <c r="L9" s="33" t="n">
+        <v>61281</v>
+      </c>
+      <c r="M9" s="33" t="n">
+        <v>51524</v>
+      </c>
+      <c r="N9" s="33" t="n"/>
+      <c r="O9" s="33" t="n">
+        <v>21208</v>
+      </c>
+      <c r="P9" s="33" t="n">
+        <v>20538</v>
+      </c>
+      <c r="Q9" s="33" t="n">
+        <v>10634</v>
+      </c>
+      <c r="R9" s="33" t="n"/>
+      <c r="S9" s="33" t="n">
+        <v>528488.99</v>
+      </c>
+      <c r="T9" s="33" t="n">
+        <v>654255</v>
+      </c>
+      <c r="U9" s="33" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:50</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="30" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B10" s="30" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A10" s="32" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B10" s="32" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F10" s="30" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G10" s="30" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I10" s="30" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J10" s="30" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K10" s="30" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L10" s="30" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M10" s="30" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N10" s="30" t="n"/>
-      <c r="O10" s="30" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P10" s="30" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q10" s="30" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R10" s="30" t="n"/>
-      <c r="S10" s="30" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T10" s="30" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U10" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D10" s="32" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E10" s="32" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F10" s="32" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H10" s="32" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J10" s="32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K10" s="32" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L10" s="32" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M10" s="32" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N10" s="32" t="n"/>
+      <c r="O10" s="32" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P10" s="32" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q10" s="32" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R10" s="32" t="n"/>
+      <c r="S10" s="32" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T10" s="32" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U10" s="32" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="31" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A11" s="33" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B11" s="33" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D11" s="31" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G11" s="31" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H11" s="31" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I11" s="31" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J11" s="31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K11" s="31" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L11" s="31" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M11" s="31" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N11" s="31" t="n"/>
-      <c r="O11" s="31" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P11" s="31" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q11" s="31" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R11" s="31" t="n"/>
-      <c r="S11" s="31" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T11" s="31" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U11" s="31" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D11" s="33" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E11" s="33" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F11" s="33" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G11" s="33" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H11" s="33" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I11" s="33" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J11" s="33" t="n"/>
+      <c r="K11" s="33" t="n"/>
+      <c r="L11" s="33" t="n"/>
+      <c r="M11" s="33" t="n"/>
+      <c r="N11" s="33" t="n"/>
+      <c r="O11" s="33" t="n"/>
+      <c r="P11" s="33" t="n"/>
+      <c r="Q11" s="33" t="n"/>
+      <c r="R11" s="33" t="n"/>
+      <c r="S11" s="33" t="n"/>
+      <c r="T11" s="33" t="n"/>
+      <c r="U11" s="33" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="40.35" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F12" s="30" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G12" s="30" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H12" s="30" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="30" t="n"/>
-      <c r="P12" s="30" t="n"/>
-      <c r="Q12" s="30" t="n"/>
-      <c r="R12" s="30" t="n"/>
-      <c r="S12" s="30" t="n"/>
-      <c r="T12" s="30" t="n"/>
-      <c r="U12" s="30" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="12" ht="40.35" customHeight="1"/>
     <row r="13" ht="40.35" customHeight="1"/>
     <row r="14" ht="40.35" customHeight="1"/>
     <row r="15" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -555,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -666,12 +672,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="32" t="inlineStr">
+      <c r="A2" s="34" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="32" t="inlineStr">
+      <c r="B2" s="34" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -681,66 +687,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="32" t="n">
+      <c r="D2" s="34" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="32" t="n">
+      <c r="E2" s="34" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="32" t="n">
+      <c r="F2" s="34" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="32" t="n">
+      <c r="G2" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="32" t="n">
+      <c r="H2" s="34" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="32" t="n">
+      <c r="I2" s="34" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="32" t="n">
+      <c r="J2" s="34" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="32" t="n">
+      <c r="K2" s="34" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="32" t="n">
+      <c r="L2" s="34" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="32" t="n">
+      <c r="M2" s="34" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="32" t="n"/>
-      <c r="O2" s="32" t="n">
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="34" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="32" t="n">
+      <c r="P2" s="34" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="32" t="n">
+      <c r="Q2" s="34" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="32" t="n"/>
-      <c r="S2" s="32" t="n">
+      <c r="R2" s="34" t="n"/>
+      <c r="S2" s="34" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="32" t="n">
+      <c r="T2" s="34" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="32" t="inlineStr">
+      <c r="U2" s="34" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="33" t="inlineStr">
+      <c r="A3" s="35" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="33" t="inlineStr">
+      <c r="B3" s="35" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -750,48 +756,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="33" t="n">
+      <c r="D3" s="35" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="33" t="n">
+      <c r="E3" s="35" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="33" t="n">
+      <c r="F3" s="35" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="33" t="n">
+      <c r="G3" s="35" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="33" t="n">
+      <c r="H3" s="35" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="33" t="n">
+      <c r="I3" s="35" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="33" t="n"/>
-      <c r="K3" s="33" t="n"/>
-      <c r="L3" s="33" t="n"/>
-      <c r="M3" s="33" t="n"/>
-      <c r="N3" s="33" t="n"/>
-      <c r="O3" s="33" t="n"/>
-      <c r="P3" s="33" t="n"/>
-      <c r="Q3" s="33" t="n"/>
-      <c r="R3" s="33" t="n"/>
-      <c r="S3" s="33" t="n"/>
-      <c r="T3" s="33" t="n"/>
-      <c r="U3" s="33" t="inlineStr">
+      <c r="J3" s="35" t="n"/>
+      <c r="K3" s="35" t="n"/>
+      <c r="L3" s="35" t="n"/>
+      <c r="M3" s="35" t="n"/>
+      <c r="N3" s="35" t="n"/>
+      <c r="O3" s="35" t="n"/>
+      <c r="P3" s="35" t="n"/>
+      <c r="Q3" s="35" t="n"/>
+      <c r="R3" s="35" t="n"/>
+      <c r="S3" s="35" t="n"/>
+      <c r="T3" s="35" t="n"/>
+      <c r="U3" s="35" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="32" t="inlineStr">
+      <c r="A4" s="34" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="32" t="inlineStr">
+      <c r="B4" s="34" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -801,66 +807,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" s="34" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="34" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="32" t="n">
+      <c r="F4" s="34" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="32" t="n">
+      <c r="G4" s="34" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="32" t="n">
+      <c r="H4" s="34" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="32" t="n">
+      <c r="I4" s="34" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="32" t="n">
+      <c r="J4" s="34" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="32" t="n">
+      <c r="K4" s="34" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="32" t="n">
+      <c r="L4" s="34" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="32" t="n">
+      <c r="M4" s="34" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="32" t="n"/>
-      <c r="O4" s="32" t="n">
+      <c r="N4" s="34" t="n"/>
+      <c r="O4" s="34" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="32" t="n">
+      <c r="P4" s="34" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="32" t="n">
+      <c r="Q4" s="34" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="32" t="n"/>
-      <c r="S4" s="32" t="n">
+      <c r="R4" s="34" t="n"/>
+      <c r="S4" s="34" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="32" t="n">
+      <c r="T4" s="34" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="32" t="inlineStr">
+      <c r="U4" s="34" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="35" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="35" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -870,66 +876,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="33" t="n">
+      <c r="D5" s="35" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="33" t="n">
+      <c r="E5" s="35" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="33" t="n">
+      <c r="F5" s="35" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="33" t="n">
+      <c r="G5" s="35" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="33" t="n">
+      <c r="H5" s="35" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="33" t="n">
+      <c r="I5" s="35" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="33" t="n">
+      <c r="J5" s="35" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="33" t="n">
+      <c r="K5" s="35" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="33" t="n">
+      <c r="L5" s="35" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="33" t="n">
+      <c r="M5" s="35" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="33" t="n"/>
-      <c r="O5" s="33" t="n">
+      <c r="N5" s="35" t="n"/>
+      <c r="O5" s="35" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="33" t="n">
+      <c r="P5" s="35" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="33" t="n">
+      <c r="Q5" s="35" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="33" t="n"/>
-      <c r="S5" s="33" t="n">
+      <c r="R5" s="35" t="n"/>
+      <c r="S5" s="35" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="33" t="n">
+      <c r="T5" s="35" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="33" t="inlineStr">
+      <c r="U5" s="35" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="32" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B6" s="32" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -939,66 +945,66 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D6" s="32" t="n">
+      <c r="D6" s="34" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E6" s="32" t="n">
+      <c r="E6" s="34" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F6" s="32" t="n">
+      <c r="F6" s="34" t="n">
         <v>84.607</v>
       </c>
-      <c r="G6" s="32" t="n">
+      <c r="G6" s="34" t="n">
         <v>13.75</v>
       </c>
-      <c r="H6" s="32" t="n">
+      <c r="H6" s="34" t="n">
         <v>96.75</v>
       </c>
-      <c r="I6" s="32" t="n">
+      <c r="I6" s="34" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J6" s="32" t="n">
+      <c r="J6" s="34" t="n">
         <v>2.53</v>
       </c>
-      <c r="K6" s="32" t="n">
+      <c r="K6" s="34" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L6" s="32" t="n">
+      <c r="L6" s="34" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M6" s="32" t="n">
+      <c r="M6" s="34" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N6" s="32" t="n"/>
-      <c r="O6" s="32" t="n">
+      <c r="N6" s="34" t="n"/>
+      <c r="O6" s="34" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P6" s="32" t="n">
+      <c r="P6" s="34" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q6" s="32" t="n">
+      <c r="Q6" s="34" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R6" s="32" t="n"/>
-      <c r="S6" s="32" t="n">
+      <c r="R6" s="34" t="n"/>
+      <c r="S6" s="34" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T6" s="32" t="n">
+      <c r="T6" s="34" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U6" s="32" t="inlineStr">
+      <c r="U6" s="34" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -1008,66 +1014,66 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="35" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E7" s="33" t="n">
+      <c r="E7" s="35" t="n">
         <v>177.19</v>
       </c>
-      <c r="F7" s="33" t="n">
+      <c r="F7" s="35" t="n">
         <v>184.89</v>
       </c>
-      <c r="G7" s="33" t="n">
+      <c r="G7" s="35" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="35" t="n">
         <v>182.58</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="35" t="n">
         <v>176.38</v>
       </c>
-      <c r="J7" s="33" t="n">
+      <c r="J7" s="35" t="n">
         <v>4.91</v>
       </c>
-      <c r="K7" s="33" t="n">
+      <c r="K7" s="35" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L7" s="33" t="n">
+      <c r="L7" s="35" t="n">
         <v>215938</v>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="35" t="n">
         <v>60922</v>
       </c>
-      <c r="N7" s="33" t="n"/>
-      <c r="O7" s="33" t="n">
+      <c r="N7" s="35" t="n"/>
+      <c r="O7" s="35" t="n">
         <v>120067</v>
       </c>
-      <c r="P7" s="33" t="n">
+      <c r="P7" s="35" t="n">
         <v>120067</v>
       </c>
-      <c r="Q7" s="33" t="n">
+      <c r="Q7" s="35" t="n">
         <v>29760</v>
       </c>
-      <c r="R7" s="33" t="n"/>
-      <c r="S7" s="33" t="n">
+      <c r="R7" s="35" t="n"/>
+      <c r="S7" s="35" t="n">
         <v>11412</v>
       </c>
-      <c r="T7" s="33" t="n">
+      <c r="T7" s="35" t="n">
         <v>62556</v>
       </c>
-      <c r="U7" s="33" t="inlineStr">
+      <c r="U7" s="35" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>SHOP.TO</t>
         </is>
       </c>
-      <c r="B8" s="32" t="inlineStr">
+      <c r="B8" s="34" t="inlineStr">
         <is>
           <t>Shopify Inc.</t>
         </is>
@@ -1077,256 +1083,188 @@
           <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
         </is>
       </c>
-      <c r="D8" s="32" t="n">
+      <c r="D8" s="34" t="n">
         <v>213981.48</v>
       </c>
-      <c r="E8" s="32" t="n">
+      <c r="E8" s="34" t="n">
         <v>163.32</v>
       </c>
-      <c r="F8" s="32" t="n">
+      <c r="F8" s="34" t="n">
         <v>164.67</v>
       </c>
-      <c r="G8" s="32" t="n">
+      <c r="G8" s="34" t="n">
         <v>-0.82</v>
       </c>
-      <c r="H8" s="32" t="n">
+      <c r="H8" s="34" t="n">
         <v>164.76</v>
       </c>
-      <c r="I8" s="32" t="n">
+      <c r="I8" s="34" t="n">
         <v>156.66</v>
       </c>
-      <c r="J8" s="32" t="n">
+      <c r="J8" s="34" t="n">
         <v>1.28</v>
       </c>
-      <c r="K8" s="32" t="n">
+      <c r="K8" s="34" t="n">
         <v>11556</v>
       </c>
-      <c r="L8" s="32" t="n">
+      <c r="L8" s="34" t="n">
         <v>11556</v>
       </c>
-      <c r="M8" s="32" t="n">
+      <c r="M8" s="34" t="n">
         <v>7060</v>
       </c>
-      <c r="N8" s="32" t="inlineStr">
+      <c r="N8" s="34" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="O8" s="32" t="n">
+      <c r="O8" s="34" t="n">
         <v>1231</v>
       </c>
-      <c r="P8" s="32" t="n">
+      <c r="P8" s="34" t="n">
         <v>1231</v>
       </c>
-      <c r="Q8" s="32" t="n">
+      <c r="Q8" s="34" t="n">
         <v>132</v>
       </c>
-      <c r="R8" s="32" t="inlineStr">
+      <c r="R8" s="34" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="S8" s="32" t="n">
+      <c r="S8" s="34" t="n">
         <v>188</v>
       </c>
-      <c r="T8" s="32" t="n">
+      <c r="T8" s="34" t="n">
         <v>5847</v>
       </c>
-      <c r="U8" s="32" t="inlineStr">
+      <c r="U8" s="34" t="inlineStr">
         <is>
           <t>2026-03-02 17:17:28</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="33" t="inlineStr">
-        <is>
-          <t>TD.TO</t>
-        </is>
-      </c>
-      <c r="B9" s="33" t="inlineStr">
-        <is>
-          <t>The Toronto-Dominion Bank</t>
+      <c r="A9" s="35" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>The Toronto-Dominion Bank, together with its subsidiaries, provides various financial products and services in Canada, the United States, and internationally. It operates through four segments: Canadian Personal and Commercial Banking; U.S. Retail; Wealth Management and Insurance; and Wholesale Banking. The company offers personal deposits, such as chequing, savings, and investment products; financing, investment, cash management, international trade, and banking services to businesses; and financing options to customers at point of sale for automotive and recreational vehicle purchases. It also provides credit cards and payments; real estate secured lending, auto finance, and consumer lending services; point-of-sale payment solutions for large and small businesses; wealth and asset management products, and advice to retail and institutional clients through direct investing, advice-based, and asset management businesses; and property and casualty insurance, as well as life and health insurance products. The company also provides capital markets, and corporate and investment banking products and services, including underwriting and distribution of new debt and equity issues; advice on strategic acquisitions and divestitures; and trading, funding, and investment services to corporations, governments, and institutions. The Toronto-Dominion Bank was founded in 1855 and is headquartered in Toronto, Canada.</t>
-        </is>
-      </c>
-      <c r="D9" s="33" t="n">
-        <v>223066.26</v>
-      </c>
-      <c r="E9" s="33" t="n">
-        <v>132.88</v>
-      </c>
-      <c r="F9" s="33" t="n">
-        <v>135.14</v>
-      </c>
-      <c r="G9" s="33" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="H9" s="33" t="n">
-        <v>136.49</v>
-      </c>
-      <c r="I9" s="33" t="n">
-        <v>132.48</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="K9" s="33" t="n">
-        <v>65980</v>
-      </c>
-      <c r="L9" s="33" t="n">
-        <v>61281</v>
-      </c>
-      <c r="M9" s="33" t="n">
-        <v>51524</v>
-      </c>
-      <c r="N9" s="33" t="n"/>
-      <c r="O9" s="33" t="n">
-        <v>21208</v>
-      </c>
-      <c r="P9" s="33" t="n">
-        <v>20538</v>
-      </c>
-      <c r="Q9" s="33" t="n">
-        <v>10634</v>
-      </c>
-      <c r="R9" s="33" t="n"/>
-      <c r="S9" s="33" t="n">
-        <v>528488.99</v>
-      </c>
-      <c r="T9" s="33" t="n">
-        <v>654255</v>
-      </c>
-      <c r="U9" s="33" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:50</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D9" s="35" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E9" s="35" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F9" s="35" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H9" s="35" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I9" s="35" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J9" s="35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K9" s="35" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L9" s="35" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M9" s="35" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N9" s="35" t="n"/>
+      <c r="O9" s="35" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P9" s="35" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q9" s="35" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R9" s="35" t="n"/>
+      <c r="S9" s="35" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T9" s="35" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U9" s="35" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="32" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A10" s="34" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B10" s="34" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D10" s="32" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E10" s="32" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F10" s="32" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G10" s="32" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H10" s="32" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I10" s="32" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J10" s="32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K10" s="32" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L10" s="32" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M10" s="32" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N10" s="32" t="n"/>
-      <c r="O10" s="32" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P10" s="32" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q10" s="32" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R10" s="32" t="n"/>
-      <c r="S10" s="32" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T10" s="32" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U10" s="32" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G10" s="34" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I10" s="34" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J10" s="34" t="n"/>
+      <c r="K10" s="34" t="n"/>
+      <c r="L10" s="34" t="n"/>
+      <c r="M10" s="34" t="n"/>
+      <c r="N10" s="34" t="n"/>
+      <c r="O10" s="34" t="n"/>
+      <c r="P10" s="34" t="n"/>
+      <c r="Q10" s="34" t="n"/>
+      <c r="R10" s="34" t="n"/>
+      <c r="S10" s="34" t="n"/>
+      <c r="T10" s="34" t="n"/>
+      <c r="U10" s="34" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="40.35" customHeight="1">
-      <c r="A11" s="33" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B11" s="33" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D11" s="33" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E11" s="33" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F11" s="33" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G11" s="33" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H11" s="33" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I11" s="33" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="33" t="n"/>
-      <c r="L11" s="33" t="n"/>
-      <c r="M11" s="33" t="n"/>
-      <c r="N11" s="33" t="n"/>
-      <c r="O11" s="33" t="n"/>
-      <c r="P11" s="33" t="n"/>
-      <c r="Q11" s="33" t="n"/>
-      <c r="R11" s="33" t="n"/>
-      <c r="S11" s="33" t="n"/>
-      <c r="T11" s="33" t="n"/>
-      <c r="U11" s="33" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="11" ht="40.35" customHeight="1"/>
     <row r="12" ht="40.35" customHeight="1"/>
     <row r="13" ht="40.35" customHeight="1"/>
     <row r="14" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -561,7 +567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U10"/>
+  <dimension ref="A1:U9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -672,12 +678,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="34" t="inlineStr">
+      <c r="A2" s="36" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="36" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -687,66 +693,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="34" t="n">
+      <c r="D2" s="36" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="34" t="n">
+      <c r="E2" s="36" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="34" t="n">
+      <c r="F2" s="36" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="34" t="n">
+      <c r="G2" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="34" t="n">
+      <c r="H2" s="36" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="34" t="n">
+      <c r="I2" s="36" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="34" t="n">
+      <c r="J2" s="36" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="34" t="n">
+      <c r="K2" s="36" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="34" t="n">
+      <c r="L2" s="36" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="34" t="n">
+      <c r="M2" s="36" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="34" t="n"/>
-      <c r="O2" s="34" t="n">
+      <c r="N2" s="36" t="n"/>
+      <c r="O2" s="36" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="34" t="n">
+      <c r="P2" s="36" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="34" t="n">
+      <c r="Q2" s="36" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="34" t="n"/>
-      <c r="S2" s="34" t="n">
+      <c r="R2" s="36" t="n"/>
+      <c r="S2" s="36" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="34" t="n">
+      <c r="T2" s="36" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="34" t="inlineStr">
+      <c r="U2" s="36" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="35" t="inlineStr">
+      <c r="A3" s="37" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="35" t="inlineStr">
+      <c r="B3" s="37" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -756,48 +762,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="37" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="35" t="n">
+      <c r="E3" s="37" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="35" t="n">
+      <c r="F3" s="37" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="35" t="n">
+      <c r="G3" s="37" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="35" t="n">
+      <c r="H3" s="37" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="35" t="n">
+      <c r="I3" s="37" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="35" t="n"/>
-      <c r="K3" s="35" t="n"/>
-      <c r="L3" s="35" t="n"/>
-      <c r="M3" s="35" t="n"/>
-      <c r="N3" s="35" t="n"/>
-      <c r="O3" s="35" t="n"/>
-      <c r="P3" s="35" t="n"/>
-      <c r="Q3" s="35" t="n"/>
-      <c r="R3" s="35" t="n"/>
-      <c r="S3" s="35" t="n"/>
-      <c r="T3" s="35" t="n"/>
-      <c r="U3" s="35" t="inlineStr">
+      <c r="J3" s="37" t="n"/>
+      <c r="K3" s="37" t="n"/>
+      <c r="L3" s="37" t="n"/>
+      <c r="M3" s="37" t="n"/>
+      <c r="N3" s="37" t="n"/>
+      <c r="O3" s="37" t="n"/>
+      <c r="P3" s="37" t="n"/>
+      <c r="Q3" s="37" t="n"/>
+      <c r="R3" s="37" t="n"/>
+      <c r="S3" s="37" t="n"/>
+      <c r="T3" s="37" t="n"/>
+      <c r="U3" s="37" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="34" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="34" t="inlineStr">
+      <c r="B4" s="36" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -807,66 +813,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="34" t="n">
+      <c r="D4" s="36" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="34" t="n">
+      <c r="E4" s="36" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="34" t="n">
+      <c r="F4" s="36" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="34" t="n">
+      <c r="G4" s="36" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="34" t="n">
+      <c r="H4" s="36" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="34" t="n">
+      <c r="I4" s="36" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="34" t="n">
+      <c r="J4" s="36" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="34" t="n">
+      <c r="K4" s="36" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="34" t="n">
+      <c r="L4" s="36" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="34" t="n">
+      <c r="M4" s="36" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="34" t="n"/>
-      <c r="O4" s="34" t="n">
+      <c r="N4" s="36" t="n"/>
+      <c r="O4" s="36" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="34" t="n">
+      <c r="P4" s="36" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="34" t="n">
+      <c r="Q4" s="36" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="34" t="n"/>
-      <c r="S4" s="34" t="n">
+      <c r="R4" s="36" t="n"/>
+      <c r="S4" s="36" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="34" t="n">
+      <c r="T4" s="36" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="34" t="inlineStr">
+      <c r="U4" s="36" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -876,66 +882,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n">
+      <c r="D5" s="37" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="35" t="n">
+      <c r="E5" s="37" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="F5" s="37" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="G5" s="37" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="H5" s="37" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="35" t="n">
+      <c r="I5" s="37" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="35" t="n">
+      <c r="J5" s="37" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="35" t="n">
+      <c r="K5" s="37" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="35" t="n">
+      <c r="L5" s="37" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="35" t="n">
+      <c r="M5" s="37" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="35" t="n"/>
-      <c r="O5" s="35" t="n">
+      <c r="N5" s="37" t="n"/>
+      <c r="O5" s="37" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="35" t="n">
+      <c r="P5" s="37" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="35" t="n">
+      <c r="Q5" s="37" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="35" t="n"/>
-      <c r="S5" s="35" t="n">
+      <c r="R5" s="37" t="n"/>
+      <c r="S5" s="37" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="35" t="n">
+      <c r="T5" s="37" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="35" t="inlineStr">
+      <c r="U5" s="37" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="34" t="inlineStr">
+      <c r="A6" s="36" t="inlineStr">
         <is>
           <t>NFLX</t>
         </is>
       </c>
-      <c r="B6" s="34" t="inlineStr">
+      <c r="B6" s="36" t="inlineStr">
         <is>
           <t>Netflix, Inc.</t>
         </is>
@@ -945,66 +951,66 @@
           <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
         </is>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="36" t="n">
         <v>408239.44</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="36" t="n">
         <v>96.23999999999999</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="36" t="n">
         <v>84.607</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="36" t="n">
         <v>13.75</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="36" t="n">
         <v>96.75</v>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="36" t="n">
         <v>90.59999999999999</v>
       </c>
-      <c r="J6" s="34" t="n">
+      <c r="J6" s="36" t="n">
         <v>2.53</v>
       </c>
-      <c r="K6" s="34" t="n">
+      <c r="K6" s="36" t="n">
         <v>45183.04</v>
       </c>
-      <c r="L6" s="34" t="n">
+      <c r="L6" s="36" t="n">
         <v>45183.04</v>
       </c>
-      <c r="M6" s="34" t="n">
+      <c r="M6" s="36" t="n">
         <v>33723.3</v>
       </c>
-      <c r="N6" s="34" t="n"/>
-      <c r="O6" s="34" t="n">
+      <c r="N6" s="36" t="n"/>
+      <c r="O6" s="36" t="n">
         <v>10981.2</v>
       </c>
-      <c r="P6" s="34" t="n">
+      <c r="P6" s="36" t="n">
         <v>10981.2</v>
       </c>
-      <c r="Q6" s="34" t="n">
+      <c r="Q6" s="36" t="n">
         <v>5407.99</v>
       </c>
-      <c r="R6" s="34" t="n"/>
-      <c r="S6" s="34" t="n">
+      <c r="R6" s="36" t="n"/>
+      <c r="S6" s="36" t="n">
         <v>16975.84</v>
       </c>
-      <c r="T6" s="34" t="n">
+      <c r="T6" s="36" t="n">
         <v>9062.360000000001</v>
       </c>
-      <c r="U6" s="34" t="inlineStr">
+      <c r="U6" s="36" t="inlineStr">
         <is>
           <t>2026-03-01 17:05:08</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="35" t="inlineStr">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="37" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -1014,256 +1020,180 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="37" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="37" t="n">
         <v>177.19</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="37" t="n">
         <v>184.89</v>
       </c>
-      <c r="G7" s="35" t="n">
+      <c r="G7" s="37" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H7" s="35" t="n">
+      <c r="H7" s="37" t="n">
         <v>182.58</v>
       </c>
-      <c r="I7" s="35" t="n">
+      <c r="I7" s="37" t="n">
         <v>176.38</v>
       </c>
-      <c r="J7" s="35" t="n">
+      <c r="J7" s="37" t="n">
         <v>4.91</v>
       </c>
-      <c r="K7" s="35" t="n">
+      <c r="K7" s="37" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L7" s="35" t="n">
+      <c r="L7" s="37" t="n">
         <v>215938</v>
       </c>
-      <c r="M7" s="35" t="n">
+      <c r="M7" s="37" t="n">
         <v>60922</v>
       </c>
-      <c r="N7" s="35" t="n"/>
-      <c r="O7" s="35" t="n">
+      <c r="N7" s="37" t="n"/>
+      <c r="O7" s="37" t="n">
         <v>120067</v>
       </c>
-      <c r="P7" s="35" t="n">
+      <c r="P7" s="37" t="n">
         <v>120067</v>
       </c>
-      <c r="Q7" s="35" t="n">
+      <c r="Q7" s="37" t="n">
         <v>29760</v>
       </c>
-      <c r="R7" s="35" t="n"/>
-      <c r="S7" s="35" t="n">
+      <c r="R7" s="37" t="n"/>
+      <c r="S7" s="37" t="n">
         <v>11412</v>
       </c>
-      <c r="T7" s="35" t="n">
+      <c r="T7" s="37" t="n">
         <v>62556</v>
       </c>
-      <c r="U7" s="35" t="inlineStr">
+      <c r="U7" s="37" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="34" t="inlineStr">
-        <is>
-          <t>SHOP.TO</t>
-        </is>
-      </c>
-      <c r="B8" s="34" t="inlineStr">
-        <is>
-          <t>Shopify Inc.</t>
+      <c r="A8" s="36" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B8" s="36" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Shopify Inc., a commerce technology company, provides tools to start, scale, market, and run a business of various sizes in Canada, the United States, Europe, the Middle East, Africa, the Asia Pacific, and Latin America. The Company offers Shopify platform that enables merchants to manage products and inventory, process orders and payments, fulfill and ship orders, build customer relationships, source products, leverage analytics, and reporting and access financing for running their business across all of their sales channels, including web and mobile storefronts, physical retail locations, social media storefronts, and marketplaces. It also provides Shopify Payments, a fully integrated payment processing service that allows merchants to accept and process payment cards online and offline. In addition, the company engages in the sale of themes and apps; shipping labels through Shopify Shipping; point-of-sale hardware; advertising on the Shopify App Store; and Shop Campaigns for buyer acquisitions, as well as registration of domain names. The company was formerly known as Jaded Pixel Technologies Inc. and changed its name to Shopify Inc. in November 2011. Shopify Inc. was incorporated in 2004 and is based in Ottawa, Canada.</t>
-        </is>
-      </c>
-      <c r="D8" s="34" t="n">
-        <v>213981.48</v>
-      </c>
-      <c r="E8" s="34" t="n">
-        <v>163.32</v>
-      </c>
-      <c r="F8" s="34" t="n">
-        <v>164.67</v>
-      </c>
-      <c r="G8" s="34" t="n">
-        <v>-0.82</v>
-      </c>
-      <c r="H8" s="34" t="n">
-        <v>164.76</v>
-      </c>
-      <c r="I8" s="34" t="n">
-        <v>156.66</v>
-      </c>
-      <c r="J8" s="34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="K8" s="34" t="n">
-        <v>11556</v>
-      </c>
-      <c r="L8" s="34" t="n">
-        <v>11556</v>
-      </c>
-      <c r="M8" s="34" t="n">
-        <v>7060</v>
-      </c>
-      <c r="N8" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" s="34" t="n">
-        <v>1231</v>
-      </c>
-      <c r="P8" s="34" t="n">
-        <v>1231</v>
-      </c>
-      <c r="Q8" s="34" t="n">
-        <v>132</v>
-      </c>
-      <c r="R8" s="34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S8" s="34" t="n">
-        <v>188</v>
-      </c>
-      <c r="T8" s="34" t="n">
-        <v>5847</v>
-      </c>
-      <c r="U8" s="34" t="inlineStr">
-        <is>
-          <t>2026-03-02 17:17:28</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D8" s="36" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E8" s="36" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F8" s="36" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G8" s="36" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H8" s="36" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I8" s="36" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J8" s="36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K8" s="36" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L8" s="36" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M8" s="36" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N8" s="36" t="n"/>
+      <c r="O8" s="36" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P8" s="36" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q8" s="36" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R8" s="36" t="n"/>
+      <c r="S8" s="36" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T8" s="36" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U8" s="36" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="35" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B9" s="35" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B9" s="37" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D9" s="35" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F9" s="35" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G9" s="35" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H9" s="35" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I9" s="35" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J9" s="35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K9" s="35" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L9" s="35" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M9" s="35" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N9" s="35" t="n"/>
-      <c r="O9" s="35" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P9" s="35" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q9" s="35" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R9" s="35" t="n"/>
-      <c r="S9" s="35" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T9" s="35" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U9" s="35" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E9" s="37" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F9" s="37" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H9" s="37" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I9" s="37" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J9" s="37" t="n"/>
+      <c r="K9" s="37" t="n"/>
+      <c r="L9" s="37" t="n"/>
+      <c r="M9" s="37" t="n"/>
+      <c r="N9" s="37" t="n"/>
+      <c r="O9" s="37" t="n"/>
+      <c r="P9" s="37" t="n"/>
+      <c r="Q9" s="37" t="n"/>
+      <c r="R9" s="37" t="n"/>
+      <c r="S9" s="37" t="n"/>
+      <c r="T9" s="37" t="n"/>
+      <c r="U9" s="37" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="40.35" customHeight="1">
-      <c r="A10" s="34" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B10" s="34" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E10" s="34" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G10" s="34" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H10" s="34" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I10" s="34" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J10" s="34" t="n"/>
-      <c r="K10" s="34" t="n"/>
-      <c r="L10" s="34" t="n"/>
-      <c r="M10" s="34" t="n"/>
-      <c r="N10" s="34" t="n"/>
-      <c r="O10" s="34" t="n"/>
-      <c r="P10" s="34" t="n"/>
-      <c r="Q10" s="34" t="n"/>
-      <c r="R10" s="34" t="n"/>
-      <c r="S10" s="34" t="n"/>
-      <c r="T10" s="34" t="n"/>
-      <c r="U10" s="34" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="10" ht="40.35" customHeight="1"/>
     <row r="11" ht="40.35" customHeight="1"/>
     <row r="12" ht="40.35" customHeight="1"/>
     <row r="13" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -567,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U9"/>
+  <dimension ref="A1:U8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -678,12 +684,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="36" t="inlineStr">
+      <c r="A2" s="38" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="36" t="inlineStr">
+      <c r="B2" s="38" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -693,66 +699,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="36" t="n">
+      <c r="D2" s="38" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="36" t="n">
+      <c r="E2" s="38" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="36" t="n">
+      <c r="F2" s="38" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="36" t="n">
+      <c r="G2" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="36" t="n">
+      <c r="H2" s="38" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="36" t="n">
+      <c r="I2" s="38" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="36" t="n">
+      <c r="J2" s="38" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="36" t="n">
+      <c r="K2" s="38" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="36" t="n">
+      <c r="L2" s="38" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="36" t="n">
+      <c r="M2" s="38" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="36" t="n"/>
-      <c r="O2" s="36" t="n">
+      <c r="N2" s="38" t="n"/>
+      <c r="O2" s="38" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="36" t="n">
+      <c r="P2" s="38" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="36" t="n">
+      <c r="Q2" s="38" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="36" t="n"/>
-      <c r="S2" s="36" t="n">
+      <c r="R2" s="38" t="n"/>
+      <c r="S2" s="38" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="36" t="n">
+      <c r="T2" s="38" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="36" t="inlineStr">
+      <c r="U2" s="38" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="37" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="B3" s="39" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -762,48 +768,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="37" t="n">
+      <c r="D3" s="39" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="37" t="n">
+      <c r="E3" s="39" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="37" t="n">
+      <c r="F3" s="39" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="37" t="n">
+      <c r="G3" s="39" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="37" t="n">
+      <c r="H3" s="39" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="37" t="n">
+      <c r="I3" s="39" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="37" t="n"/>
-      <c r="K3" s="37" t="n"/>
-      <c r="L3" s="37" t="n"/>
-      <c r="M3" s="37" t="n"/>
-      <c r="N3" s="37" t="n"/>
-      <c r="O3" s="37" t="n"/>
-      <c r="P3" s="37" t="n"/>
-      <c r="Q3" s="37" t="n"/>
-      <c r="R3" s="37" t="n"/>
-      <c r="S3" s="37" t="n"/>
-      <c r="T3" s="37" t="n"/>
-      <c r="U3" s="37" t="inlineStr">
+      <c r="J3" s="39" t="n"/>
+      <c r="K3" s="39" t="n"/>
+      <c r="L3" s="39" t="n"/>
+      <c r="M3" s="39" t="n"/>
+      <c r="N3" s="39" t="n"/>
+      <c r="O3" s="39" t="n"/>
+      <c r="P3" s="39" t="n"/>
+      <c r="Q3" s="39" t="n"/>
+      <c r="R3" s="39" t="n"/>
+      <c r="S3" s="39" t="n"/>
+      <c r="T3" s="39" t="n"/>
+      <c r="U3" s="39" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="38" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="36" t="inlineStr">
+      <c r="B4" s="38" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -813,66 +819,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="36" t="n">
+      <c r="D4" s="38" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="36" t="n">
+      <c r="E4" s="38" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="36" t="n">
+      <c r="F4" s="38" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="36" t="n">
+      <c r="G4" s="38" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="36" t="n">
+      <c r="H4" s="38" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="36" t="n">
+      <c r="I4" s="38" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="36" t="n">
+      <c r="J4" s="38" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="36" t="n">
+      <c r="K4" s="38" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="36" t="n">
+      <c r="L4" s="38" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="36" t="n">
+      <c r="M4" s="38" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="36" t="n"/>
-      <c r="O4" s="36" t="n">
+      <c r="N4" s="38" t="n"/>
+      <c r="O4" s="38" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="36" t="n">
+      <c r="P4" s="38" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="36" t="n">
+      <c r="Q4" s="38" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="36" t="n"/>
-      <c r="S4" s="36" t="n">
+      <c r="R4" s="38" t="n"/>
+      <c r="S4" s="38" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="36" t="n">
+      <c r="T4" s="38" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="36" t="inlineStr">
+      <c r="U4" s="38" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="39" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -882,317 +888,249 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="37" t="n">
+      <c r="D5" s="39" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="37" t="n">
+      <c r="E5" s="39" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="37" t="n">
+      <c r="F5" s="39" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="37" t="n">
+      <c r="G5" s="39" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="37" t="n">
+      <c r="H5" s="39" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="37" t="n">
+      <c r="I5" s="39" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="37" t="n">
+      <c r="J5" s="39" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="37" t="n">
+      <c r="K5" s="39" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="37" t="n">
+      <c r="L5" s="39" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="37" t="n">
+      <c r="M5" s="39" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="37" t="n"/>
-      <c r="O5" s="37" t="n">
+      <c r="N5" s="39" t="n"/>
+      <c r="O5" s="39" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="37" t="n">
+      <c r="P5" s="39" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="37" t="n">
+      <c r="Q5" s="39" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="37" t="n"/>
-      <c r="S5" s="37" t="n">
+      <c r="R5" s="39" t="n"/>
+      <c r="S5" s="39" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="37" t="n">
+      <c r="T5" s="39" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="37" t="inlineStr">
+      <c r="U5" s="39" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="36" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="B6" s="36" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B6" s="38" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Netflix, Inc. provides entertainment services worldwide. The company offers television (TV) series, documentaries, feature films, games, and live programming across various genres and languages. It also provides members the ability to receive streaming content through a host of internet-connected devices, including TVs, digital video players, TV set-top boxes, and mobile devices. Netflix, Inc. was incorporated in 1997 and is headquartered in Los Gatos, California.</t>
-        </is>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>408239.44</v>
-      </c>
-      <c r="E6" s="36" t="n">
-        <v>96.23999999999999</v>
-      </c>
-      <c r="F6" s="36" t="n">
-        <v>84.607</v>
-      </c>
-      <c r="G6" s="36" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="H6" s="36" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="I6" s="36" t="n">
-        <v>90.59999999999999</v>
-      </c>
-      <c r="J6" s="36" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="K6" s="36" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="L6" s="36" t="n">
-        <v>45183.04</v>
-      </c>
-      <c r="M6" s="36" t="n">
-        <v>33723.3</v>
-      </c>
-      <c r="N6" s="36" t="n"/>
-      <c r="O6" s="36" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="P6" s="36" t="n">
-        <v>10981.2</v>
-      </c>
-      <c r="Q6" s="36" t="n">
-        <v>5407.99</v>
-      </c>
-      <c r="R6" s="36" t="n"/>
-      <c r="S6" s="36" t="n">
-        <v>16975.84</v>
-      </c>
-      <c r="T6" s="36" t="n">
-        <v>9062.360000000001</v>
-      </c>
-      <c r="U6" s="36" t="inlineStr">
-        <is>
-          <t>2026-03-01 17:05:08</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E6" s="38" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F6" s="38" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G6" s="38" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H6" s="38" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I6" s="38" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J6" s="38" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K6" s="38" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L6" s="38" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M6" s="38" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N6" s="38" t="n"/>
+      <c r="O6" s="38" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P6" s="38" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q6" s="38" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R6" s="38" t="n"/>
+      <c r="S6" s="38" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T6" s="38" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U6" s="38" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B7" s="37" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
+      <c r="A7" s="39" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E7" s="37" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F7" s="37" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G7" s="37" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H7" s="37" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I7" s="37" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J7" s="37" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K7" s="37" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L7" s="37" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M7" s="37" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N7" s="37" t="n"/>
-      <c r="O7" s="37" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P7" s="37" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q7" s="37" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R7" s="37" t="n"/>
-      <c r="S7" s="37" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T7" s="37" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U7" s="37" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D7" s="39" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E7" s="39" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F7" s="39" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G7" s="39" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H7" s="39" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I7" s="39" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J7" s="39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K7" s="39" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L7" s="39" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M7" s="39" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N7" s="39" t="n"/>
+      <c r="O7" s="39" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P7" s="39" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q7" s="39" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R7" s="39" t="n"/>
+      <c r="S7" s="39" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T7" s="39" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U7" s="39" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
     <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B8" s="36" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>XDIV.TO</t>
+        </is>
+      </c>
+      <c r="B8" s="38" t="inlineStr">
+        <is>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E8" s="36" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F8" s="36" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G8" s="36" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H8" s="36" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I8" s="36" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J8" s="36" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K8" s="36" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L8" s="36" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M8" s="36" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N8" s="36" t="n"/>
-      <c r="O8" s="36" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P8" s="36" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q8" s="36" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R8" s="36" t="n"/>
-      <c r="S8" s="36" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T8" s="36" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U8" s="36" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
+          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
+        </is>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>3940.24</v>
+      </c>
+      <c r="E8" s="38" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F8" s="38" t="n">
+        <v>38.67</v>
+      </c>
+      <c r="G8" s="38" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H8" s="38" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="I8" s="38" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="38" t="n"/>
+      <c r="L8" s="38" t="n"/>
+      <c r="M8" s="38" t="n"/>
+      <c r="N8" s="38" t="n"/>
+      <c r="O8" s="38" t="n"/>
+      <c r="P8" s="38" t="n"/>
+      <c r="Q8" s="38" t="n"/>
+      <c r="R8" s="38" t="n"/>
+      <c r="S8" s="38" t="n"/>
+      <c r="T8" s="38" t="n"/>
+      <c r="U8" s="38" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:59:02</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="40.35" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B9" s="37" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D9" s="37" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E9" s="37" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F9" s="37" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G9" s="37" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H9" s="37" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I9" s="37" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J9" s="37" t="n"/>
-      <c r="K9" s="37" t="n"/>
-      <c r="L9" s="37" t="n"/>
-      <c r="M9" s="37" t="n"/>
-      <c r="N9" s="37" t="n"/>
-      <c r="O9" s="37" t="n"/>
-      <c r="P9" s="37" t="n"/>
-      <c r="Q9" s="37" t="n"/>
-      <c r="R9" s="37" t="n"/>
-      <c r="S9" s="37" t="n"/>
-      <c r="T9" s="37" t="n"/>
-      <c r="U9" s="37" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="9" ht="40.35" customHeight="1"/>
     <row r="10" ht="40.35" customHeight="1"/>
     <row r="11" ht="40.35" customHeight="1"/>
     <row r="12" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -89,7 +89,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -117,6 +117,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -573,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U8"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1" ht="40.35" customHeight="1">
@@ -684,12 +690,12 @@
       </c>
     </row>
     <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="40" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
@@ -699,66 +705,66 @@
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="38" t="n">
+      <c r="D2" s="40" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="38" t="n">
+      <c r="E2" s="40" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="38" t="n">
+      <c r="F2" s="40" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="38" t="n">
+      <c r="G2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="38" t="n">
+      <c r="H2" s="40" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="38" t="n">
+      <c r="I2" s="40" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="38" t="n">
+      <c r="J2" s="40" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="38" t="n">
+      <c r="K2" s="40" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="38" t="n">
+      <c r="L2" s="40" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="38" t="n">
+      <c r="M2" s="40" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="38" t="n"/>
-      <c r="O2" s="38" t="n">
+      <c r="N2" s="40" t="n"/>
+      <c r="O2" s="40" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="38" t="n">
+      <c r="P2" s="40" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="38" t="n">
+      <c r="Q2" s="40" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="38" t="n"/>
-      <c r="S2" s="38" t="n">
+      <c r="R2" s="40" t="n"/>
+      <c r="S2" s="40" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="38" t="n">
+      <c r="T2" s="40" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="38" t="inlineStr">
+      <c r="U2" s="40" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
     <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="39" t="inlineStr">
+      <c r="A3" s="41" t="inlineStr">
         <is>
           <t>BANK.TO</t>
         </is>
       </c>
-      <c r="B3" s="39" t="inlineStr">
+      <c r="B3" s="41" t="inlineStr">
         <is>
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
         </is>
@@ -768,48 +774,48 @@
           <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
         </is>
       </c>
-      <c r="D3" s="39" t="n">
+      <c r="D3" s="41" t="n">
         <v>882.9299999999999</v>
       </c>
-      <c r="E3" s="39" t="n">
+      <c r="E3" s="41" t="n">
         <v>9.77</v>
       </c>
-      <c r="F3" s="39" t="n">
+      <c r="F3" s="41" t="n">
         <v>9.91</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G3" s="41" t="n">
         <v>-1.41</v>
       </c>
-      <c r="H3" s="39" t="n">
+      <c r="H3" s="41" t="n">
         <v>9.91</v>
       </c>
-      <c r="I3" s="39" t="n">
+      <c r="I3" s="41" t="n">
         <v>9.74</v>
       </c>
-      <c r="J3" s="39" t="n"/>
-      <c r="K3" s="39" t="n"/>
-      <c r="L3" s="39" t="n"/>
-      <c r="M3" s="39" t="n"/>
-      <c r="N3" s="39" t="n"/>
-      <c r="O3" s="39" t="n"/>
-      <c r="P3" s="39" t="n"/>
-      <c r="Q3" s="39" t="n"/>
-      <c r="R3" s="39" t="n"/>
-      <c r="S3" s="39" t="n"/>
-      <c r="T3" s="39" t="n"/>
-      <c r="U3" s="39" t="inlineStr">
+      <c r="J3" s="41" t="n"/>
+      <c r="K3" s="41" t="n"/>
+      <c r="L3" s="41" t="n"/>
+      <c r="M3" s="41" t="n"/>
+      <c r="N3" s="41" t="n"/>
+      <c r="O3" s="41" t="n"/>
+      <c r="P3" s="41" t="n"/>
+      <c r="Q3" s="41" t="n"/>
+      <c r="R3" s="41" t="n"/>
+      <c r="S3" s="41" t="n"/>
+      <c r="T3" s="41" t="n"/>
+      <c r="U3" s="41" t="inlineStr">
         <is>
           <t>2026-03-01 15:59:09</t>
         </is>
       </c>
     </row>
     <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="38" t="inlineStr">
+      <c r="A4" s="40" t="inlineStr">
         <is>
           <t>GOOGL</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="40" t="inlineStr">
         <is>
           <t>Alphabet Inc.</t>
         </is>
@@ -819,66 +825,66 @@
           <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
-      <c r="D4" s="38" t="n">
+      <c r="D4" s="40" t="n">
         <v>3771360.87</v>
       </c>
-      <c r="E4" s="38" t="n">
+      <c r="E4" s="40" t="n">
         <v>311.76</v>
       </c>
-      <c r="F4" s="38" t="n">
+      <c r="F4" s="40" t="n">
         <v>307.38</v>
       </c>
-      <c r="G4" s="38" t="n">
+      <c r="G4" s="40" t="n">
         <v>1.42</v>
       </c>
-      <c r="H4" s="38" t="n">
+      <c r="H4" s="40" t="n">
         <v>312.37</v>
       </c>
-      <c r="I4" s="38" t="n">
+      <c r="I4" s="40" t="n">
         <v>303.8</v>
       </c>
-      <c r="J4" s="38" t="n">
+      <c r="J4" s="40" t="n">
         <v>10.82</v>
       </c>
-      <c r="K4" s="38" t="n">
+      <c r="K4" s="40" t="n">
         <v>402836</v>
       </c>
-      <c r="L4" s="38" t="n">
+      <c r="L4" s="40" t="n">
         <v>402836</v>
       </c>
-      <c r="M4" s="38" t="n">
+      <c r="M4" s="40" t="n">
         <v>307394</v>
       </c>
-      <c r="N4" s="38" t="n"/>
-      <c r="O4" s="38" t="n">
+      <c r="N4" s="40" t="n"/>
+      <c r="O4" s="40" t="n">
         <v>132170</v>
       </c>
-      <c r="P4" s="38" t="n">
+      <c r="P4" s="40" t="n">
         <v>132170</v>
       </c>
-      <c r="Q4" s="38" t="n">
+      <c r="Q4" s="40" t="n">
         <v>73795</v>
       </c>
-      <c r="R4" s="38" t="n"/>
-      <c r="S4" s="38" t="n">
+      <c r="R4" s="40" t="n"/>
+      <c r="S4" s="40" t="n">
         <v>66996</v>
       </c>
-      <c r="T4" s="38" t="n">
+      <c r="T4" s="40" t="n">
         <v>126843</v>
       </c>
-      <c r="U4" s="38" t="inlineStr">
+      <c r="U4" s="40" t="inlineStr">
         <is>
           <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
     <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="39" t="inlineStr">
+      <c r="A5" s="41" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B5" s="39" t="inlineStr">
+      <c r="B5" s="41" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
@@ -888,66 +894,66 @@
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D5" s="39" t="n">
+      <c r="D5" s="41" t="n">
         <v>2918992.05</v>
       </c>
-      <c r="E5" s="39" t="n">
+      <c r="E5" s="41" t="n">
         <v>392.74</v>
       </c>
-      <c r="F5" s="39" t="n">
+      <c r="F5" s="41" t="n">
         <v>401.72</v>
       </c>
-      <c r="G5" s="39" t="n">
+      <c r="G5" s="41" t="n">
         <v>-2.24</v>
       </c>
-      <c r="H5" s="39" t="n">
+      <c r="H5" s="41" t="n">
         <v>396.8</v>
       </c>
-      <c r="I5" s="39" t="n">
+      <c r="I5" s="41" t="n">
         <v>390</v>
       </c>
-      <c r="J5" s="39" t="n">
+      <c r="J5" s="41" t="n">
         <v>15.98</v>
       </c>
-      <c r="K5" s="39" t="n">
+      <c r="K5" s="41" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L5" s="39" t="n">
+      <c r="L5" s="41" t="n">
         <v>281724</v>
       </c>
-      <c r="M5" s="39" t="n">
+      <c r="M5" s="41" t="n">
         <v>211915</v>
       </c>
-      <c r="N5" s="39" t="n"/>
-      <c r="O5" s="39" t="n">
+      <c r="N5" s="41" t="n"/>
+      <c r="O5" s="41" t="n">
         <v>119262</v>
       </c>
-      <c r="P5" s="39" t="n">
+      <c r="P5" s="41" t="n">
         <v>101832</v>
       </c>
-      <c r="Q5" s="39" t="n">
+      <c r="Q5" s="41" t="n">
         <v>72361</v>
       </c>
-      <c r="R5" s="39" t="n"/>
-      <c r="S5" s="39" t="n">
+      <c r="R5" s="41" t="n"/>
+      <c r="S5" s="41" t="n">
         <v>123278</v>
       </c>
-      <c r="T5" s="39" t="n">
+      <c r="T5" s="41" t="n">
         <v>89462</v>
       </c>
-      <c r="U5" s="39" t="inlineStr">
+      <c r="U5" s="41" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
     <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="38" t="inlineStr">
+      <c r="A6" s="40" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B6" s="38" t="inlineStr">
+      <c r="B6" s="40" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
@@ -957,66 +963,66 @@
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="40" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E6" s="38" t="n">
+      <c r="E6" s="40" t="n">
         <v>177.19</v>
       </c>
-      <c r="F6" s="38" t="n">
+      <c r="F6" s="40" t="n">
         <v>184.89</v>
       </c>
-      <c r="G6" s="38" t="n">
+      <c r="G6" s="40" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H6" s="38" t="n">
+      <c r="H6" s="40" t="n">
         <v>182.58</v>
       </c>
-      <c r="I6" s="38" t="n">
+      <c r="I6" s="40" t="n">
         <v>176.38</v>
       </c>
-      <c r="J6" s="38" t="n">
+      <c r="J6" s="40" t="n">
         <v>4.91</v>
       </c>
-      <c r="K6" s="38" t="n">
+      <c r="K6" s="40" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L6" s="38" t="n">
+      <c r="L6" s="40" t="n">
         <v>215938</v>
       </c>
-      <c r="M6" s="38" t="n">
+      <c r="M6" s="40" t="n">
         <v>60922</v>
       </c>
-      <c r="N6" s="38" t="n"/>
-      <c r="O6" s="38" t="n">
+      <c r="N6" s="40" t="n"/>
+      <c r="O6" s="40" t="n">
         <v>120067</v>
       </c>
-      <c r="P6" s="38" t="n">
+      <c r="P6" s="40" t="n">
         <v>120067</v>
       </c>
-      <c r="Q6" s="38" t="n">
+      <c r="Q6" s="40" t="n">
         <v>29760</v>
       </c>
-      <c r="R6" s="38" t="n"/>
-      <c r="S6" s="38" t="n">
+      <c r="R6" s="40" t="n"/>
+      <c r="S6" s="40" t="n">
         <v>11412</v>
       </c>
-      <c r="T6" s="38" t="n">
+      <c r="T6" s="40" t="n">
         <v>62556</v>
       </c>
-      <c r="U6" s="38" t="inlineStr">
+      <c r="U6" s="40" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="39" t="inlineStr">
+      <c r="A7" s="41" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B7" s="39" t="inlineStr">
+      <c r="B7" s="41" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
@@ -1026,110 +1032,60 @@
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D7" s="39" t="n">
+      <c r="D7" s="41" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E7" s="39" t="n">
+      <c r="E7" s="41" t="n">
         <v>402.51</v>
       </c>
-      <c r="F7" s="39" t="n">
+      <c r="F7" s="41" t="n">
         <v>408.58</v>
       </c>
-      <c r="G7" s="39" t="n">
+      <c r="G7" s="41" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H7" s="39" t="n">
+      <c r="H7" s="41" t="n">
         <v>407.11</v>
       </c>
-      <c r="I7" s="39" t="n">
+      <c r="I7" s="41" t="n">
         <v>398.12</v>
       </c>
-      <c r="J7" s="39" t="n">
+      <c r="J7" s="41" t="n">
         <v>1.09</v>
       </c>
-      <c r="K7" s="39" t="n">
+      <c r="K7" s="41" t="n">
         <v>94827</v>
       </c>
-      <c r="L7" s="39" t="n">
+      <c r="L7" s="41" t="n">
         <v>94827</v>
       </c>
-      <c r="M7" s="39" t="n">
+      <c r="M7" s="41" t="n">
         <v>96773</v>
       </c>
-      <c r="N7" s="39" t="n"/>
-      <c r="O7" s="39" t="n">
+      <c r="N7" s="41" t="n"/>
+      <c r="O7" s="41" t="n">
         <v>3794</v>
       </c>
-      <c r="P7" s="39" t="n">
+      <c r="P7" s="41" t="n">
         <v>3794</v>
       </c>
-      <c r="Q7" s="39" t="n">
+      <c r="Q7" s="41" t="n">
         <v>14999</v>
       </c>
-      <c r="R7" s="39" t="n"/>
-      <c r="S7" s="39" t="n">
+      <c r="R7" s="41" t="n"/>
+      <c r="S7" s="41" t="n">
         <v>14719</v>
       </c>
-      <c r="T7" s="39" t="n">
+      <c r="T7" s="41" t="n">
         <v>44059</v>
       </c>
-      <c r="U7" s="39" t="inlineStr">
+      <c r="U7" s="41" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="40.35" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
-        <is>
-          <t>XDIV.TO</t>
-        </is>
-      </c>
-      <c r="B8" s="38" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="inlineStr">
-        <is>
-          <t>iShares Core MSCI Canadian Quality Dividend Index ETF is an ETF. Fund family: BlackRock Asset Management Canada Ltd.</t>
-        </is>
-      </c>
-      <c r="D8" s="38" t="n">
-        <v>3940.24</v>
-      </c>
-      <c r="E8" s="38" t="n">
-        <v>38.7</v>
-      </c>
-      <c r="F8" s="38" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="G8" s="38" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="H8" s="38" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="I8" s="38" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="J8" s="38" t="n"/>
-      <c r="K8" s="38" t="n"/>
-      <c r="L8" s="38" t="n"/>
-      <c r="M8" s="38" t="n"/>
-      <c r="N8" s="38" t="n"/>
-      <c r="O8" s="38" t="n"/>
-      <c r="P8" s="38" t="n"/>
-      <c r="Q8" s="38" t="n"/>
-      <c r="R8" s="38" t="n"/>
-      <c r="S8" s="38" t="n"/>
-      <c r="T8" s="38" t="n"/>
-      <c r="U8" s="38" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:02</t>
-        </is>
-      </c>
-    </row>
+    <row r="8" ht="40.35" customHeight="1"/>
     <row r="9" ht="40.35" customHeight="1"/>
     <row r="10" ht="40.35" customHeight="1"/>
     <row r="11" ht="40.35" customHeight="1"/>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -25,41 +26,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -71,152 +46,23 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -579,10 +425,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:U6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="40.35" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Stock Ticker</t>
@@ -689,413 +535,351 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="40.35" customHeight="1">
-      <c r="A2" s="40" t="inlineStr">
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>AMZN</t>
         </is>
       </c>
-      <c r="B2" s="40" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Amazon.com, Inc.</t>
         </is>
       </c>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Amazon.com, Inc. engages in the retail sale of consumer products, advertising, and subscriptions service through online and physical stores in North America and internationally. The company operates through three segments: North America, International, and Amazon Web Services (AWS). It also manufactures and sells electronic devices, including Kindle, fire tablets, fire TVs, echo, ring, blink, and eero; and develops and produces media content. In addition, the company offers programs that enable sellers to sell their products in its stores; and programs that allow authors, independent publishers, musicians, filmmakers, Twitch streamers, skill and app developers, and others to publish and sell content. Further, it provides compute, storage, Artificial intelligence, database, analytics, machine learning, and other services, as well as advertising services through programs, such as sponsored ads, display, and video advertising. Additionally, the company offers Amazon Prime, a membership program. The company's products offered through its stores include merchandise and content purchased for resale and products offered by third-party sellers. It serves consumers, sellers, developers, enterprises, content creators, advertisers, and employees. The company was incorporated in 1994 and is headquartered in Seattle, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="40" t="n">
+      <c r="D2" t="n">
         <v>2254333.28</v>
       </c>
-      <c r="E2" s="40" t="n">
+      <c r="E2" t="n">
         <v>210</v>
       </c>
-      <c r="F2" s="40" t="n">
+      <c r="F2" t="n">
         <v>207.92</v>
       </c>
-      <c r="G2" s="40" t="n">
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="40" t="n">
+      <c r="H2" t="n">
         <v>210.33</v>
       </c>
-      <c r="I2" s="40" t="n">
+      <c r="I2" t="n">
         <v>205.2</v>
       </c>
-      <c r="J2" s="40" t="n">
+      <c r="J2" t="n">
         <v>7.16</v>
       </c>
-      <c r="K2" s="40" t="n">
+      <c r="K2" t="n">
         <v>716923.99</v>
       </c>
-      <c r="L2" s="40" t="n">
+      <c r="L2" t="n">
         <v>716924</v>
       </c>
-      <c r="M2" s="40" t="n">
+      <c r="M2" t="n">
         <v>574785</v>
       </c>
-      <c r="N2" s="40" t="n"/>
-      <c r="O2" s="40" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>77670</v>
       </c>
-      <c r="P2" s="40" t="n">
+      <c r="P2" t="n">
         <v>77670</v>
       </c>
-      <c r="Q2" s="40" t="n">
+      <c r="Q2" t="n">
         <v>30425</v>
       </c>
-      <c r="R2" s="40" t="n"/>
-      <c r="S2" s="40" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>178547</v>
       </c>
-      <c r="T2" s="40" t="n">
+      <c r="T2" t="n">
         <v>123029</v>
       </c>
-      <c r="U2" s="40" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>2026-03-01 18:39:12</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="40.35" customHeight="1">
-      <c r="A3" s="41" t="inlineStr">
-        <is>
-          <t>BANK.TO</t>
-        </is>
-      </c>
-      <c r="B3" s="41" t="inlineStr">
-        <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr">
-        <is>
-          <t>Evolve Canadian Banks and Lifecos Enhanced Yield Index Fund is an ETF. Fund family: Evolve Funds Group Inc.</t>
-        </is>
-      </c>
-      <c r="D3" s="41" t="n">
-        <v>882.9299999999999</v>
-      </c>
-      <c r="E3" s="41" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="F3" s="41" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="G3" s="41" t="n">
-        <v>-1.41</v>
-      </c>
-      <c r="H3" s="41" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="I3" s="41" t="n">
-        <v>9.74</v>
-      </c>
-      <c r="J3" s="41" t="n"/>
-      <c r="K3" s="41" t="n"/>
-      <c r="L3" s="41" t="n"/>
-      <c r="M3" s="41" t="n"/>
-      <c r="N3" s="41" t="n"/>
-      <c r="O3" s="41" t="n"/>
-      <c r="P3" s="41" t="n"/>
-      <c r="Q3" s="41" t="n"/>
-      <c r="R3" s="41" t="n"/>
-      <c r="S3" s="41" t="n"/>
-      <c r="T3" s="41" t="n"/>
-      <c r="U3" s="41" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:59:09</t>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Alphabet Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>3771360.87</v>
+      </c>
+      <c r="E3" t="n">
+        <v>311.76</v>
+      </c>
+      <c r="F3" t="n">
+        <v>307.38</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H3" t="n">
+        <v>312.37</v>
+      </c>
+      <c r="I3" t="n">
+        <v>303.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>10.82</v>
+      </c>
+      <c r="K3" t="n">
+        <v>402836</v>
+      </c>
+      <c r="L3" t="n">
+        <v>402836</v>
+      </c>
+      <c r="M3" t="n">
+        <v>307394</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>132170</v>
+      </c>
+      <c r="P3" t="n">
+        <v>132170</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>73795</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>66996</v>
+      </c>
+      <c r="T3" t="n">
+        <v>126843</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:39:06</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="40.35" customHeight="1">
-      <c r="A4" s="40" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="B4" s="40" t="inlineStr">
-        <is>
-          <t>Alphabet Inc.</t>
-        </is>
-      </c>
-      <c r="C4" s="7" t="inlineStr">
-        <is>
-          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
-        </is>
-      </c>
-      <c r="D4" s="40" t="n">
-        <v>3771360.87</v>
-      </c>
-      <c r="E4" s="40" t="n">
-        <v>311.76</v>
-      </c>
-      <c r="F4" s="40" t="n">
-        <v>307.38</v>
-      </c>
-      <c r="G4" s="40" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="H4" s="40" t="n">
-        <v>312.37</v>
-      </c>
-      <c r="I4" s="40" t="n">
-        <v>303.8</v>
-      </c>
-      <c r="J4" s="40" t="n">
-        <v>10.82</v>
-      </c>
-      <c r="K4" s="40" t="n">
-        <v>402836</v>
-      </c>
-      <c r="L4" s="40" t="n">
-        <v>402836</v>
-      </c>
-      <c r="M4" s="40" t="n">
-        <v>307394</v>
-      </c>
-      <c r="N4" s="40" t="n"/>
-      <c r="O4" s="40" t="n">
-        <v>132170</v>
-      </c>
-      <c r="P4" s="40" t="n">
-        <v>132170</v>
-      </c>
-      <c r="Q4" s="40" t="n">
-        <v>73795</v>
-      </c>
-      <c r="R4" s="40" t="n"/>
-      <c r="S4" s="40" t="n">
-        <v>66996</v>
-      </c>
-      <c r="T4" s="40" t="n">
-        <v>126843</v>
-      </c>
-      <c r="U4" s="40" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:39:06</t>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2918992.05</v>
+      </c>
+      <c r="E4" t="n">
+        <v>392.74</v>
+      </c>
+      <c r="F4" t="n">
+        <v>401.72</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-2.24</v>
+      </c>
+      <c r="H4" t="n">
+        <v>396.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>390</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K4" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L4" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M4" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P4" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T4" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:58</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="40.35" customHeight="1">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>MSFT</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="n">
-        <v>2918992.05</v>
-      </c>
-      <c r="E5" s="41" t="n">
-        <v>392.74</v>
-      </c>
-      <c r="F5" s="41" t="n">
-        <v>401.72</v>
-      </c>
-      <c r="G5" s="41" t="n">
-        <v>-2.24</v>
-      </c>
-      <c r="H5" s="41" t="n">
-        <v>396.8</v>
-      </c>
-      <c r="I5" s="41" t="n">
-        <v>390</v>
-      </c>
-      <c r="J5" s="41" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="K5" s="41" t="n">
-        <v>305453.01</v>
-      </c>
-      <c r="L5" s="41" t="n">
-        <v>281724</v>
-      </c>
-      <c r="M5" s="41" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N5" s="41" t="n"/>
-      <c r="O5" s="41" t="n">
-        <v>119262</v>
-      </c>
-      <c r="P5" s="41" t="n">
-        <v>101832</v>
-      </c>
-      <c r="Q5" s="41" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R5" s="41" t="n"/>
-      <c r="S5" s="41" t="n">
-        <v>123278</v>
-      </c>
-      <c r="T5" s="41" t="n">
-        <v>89462</v>
-      </c>
-      <c r="U5" s="41" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:58</t>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E5" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F5" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K5" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L5" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M5" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P5" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T5" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="40.35" customHeight="1">
-      <c r="A6" s="40" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B6" s="40" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D6" s="40" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E6" s="40" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F6" s="40" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G6" s="40" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H6" s="40" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I6" s="40" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J6" s="40" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K6" s="40" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L6" s="40" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M6" s="40" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N6" s="40" t="n"/>
-      <c r="O6" s="40" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P6" s="40" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q6" s="40" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R6" s="40" t="n"/>
-      <c r="S6" s="40" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T6" s="40" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U6" s="40" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E6" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F6" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H6" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I6" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K6" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L6" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M6" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>14719</v>
+      </c>
+      <c r="T6" t="n">
+        <v>44059</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="40.35" customHeight="1">
-      <c r="A7" s="41" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B7" s="41" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D7" s="41" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E7" s="41" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F7" s="41" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G7" s="41" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H7" s="41" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I7" s="41" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J7" s="41" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K7" s="41" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L7" s="41" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M7" s="41" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N7" s="41" t="n"/>
-      <c r="O7" s="41" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P7" s="41" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q7" s="41" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R7" s="41" t="n"/>
-      <c r="S7" s="41" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T7" s="41" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U7" s="41" t="inlineStr">
-        <is>
-          <t>2026-03-01 16:52:00</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40.35" customHeight="1"/>
-    <row r="9" ht="40.35" customHeight="1"/>
-    <row r="10" ht="40.35" customHeight="1"/>
-    <row r="11" ht="40.35" customHeight="1"/>
-    <row r="12" ht="40.35" customHeight="1"/>
-    <row r="13" ht="40.35" customHeight="1"/>
-    <row r="14" ht="40.35" customHeight="1"/>
-    <row r="15" ht="40.35" customHeight="1"/>
-    <row r="16" ht="40.35" customHeight="1"/>
-    <row r="17" ht="40.35" customHeight="1"/>
-    <row r="18" ht="40.35" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U6"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,136 +745,213 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>NIO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>NIO Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>4306603.08</v>
+        <v>11935.27</v>
       </c>
       <c r="E5" t="n">
-        <v>177.19</v>
+        <v>4.72</v>
       </c>
       <c r="F5" t="n">
-        <v>184.89</v>
+        <v>4.87</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.16</v>
+        <v>-3.08</v>
       </c>
       <c r="H5" t="n">
-        <v>182.58</v>
+        <v>4.79</v>
       </c>
       <c r="I5" t="n">
-        <v>176.38</v>
+        <v>4.64</v>
       </c>
       <c r="J5" t="n">
-        <v>4.91</v>
+        <v>-1.68</v>
       </c>
       <c r="K5" t="n">
-        <v>215938.01</v>
+        <v>72540.69</v>
       </c>
       <c r="L5" t="n">
-        <v>215938</v>
+        <v>65731.56</v>
       </c>
       <c r="M5" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>49268.56</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O5" t="n">
-        <v>120067</v>
+        <v>-22824.89</v>
       </c>
       <c r="P5" t="n">
-        <v>120067</v>
+        <v>-22657.69</v>
       </c>
       <c r="Q5" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>-14559.44</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="S5" t="n">
-        <v>11412</v>
+        <v>27640.48</v>
       </c>
       <c r="T5" t="n">
-        <v>62556</v>
+        <v>24106.16</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-02 23:11:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1510391.41</v>
+        <v>4306603.08</v>
       </c>
       <c r="E6" t="n">
-        <v>402.51</v>
+        <v>177.19</v>
       </c>
       <c r="F6" t="n">
-        <v>408.58</v>
+        <v>184.89</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.49</v>
+        <v>-4.16</v>
       </c>
       <c r="H6" t="n">
-        <v>407.11</v>
+        <v>182.58</v>
       </c>
       <c r="I6" t="n">
-        <v>398.12</v>
+        <v>176.38</v>
       </c>
       <c r="J6" t="n">
-        <v>1.09</v>
+        <v>4.91</v>
       </c>
       <c r="K6" t="n">
-        <v>94827</v>
+        <v>215938.01</v>
       </c>
       <c r="L6" t="n">
-        <v>94827</v>
+        <v>215938</v>
       </c>
       <c r="M6" t="n">
-        <v>96773</v>
+        <v>60922</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="P6" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="Q6" t="n">
-        <v>14999</v>
+        <v>29760</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T6" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E7" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F7" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H7" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I7" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K7" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L7" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M7" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P7" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="n">
         <v>14719</v>
       </c>
-      <c r="T6" t="n">
+      <c r="T7" t="n">
         <v>44059</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,213 +745,136 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NIO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIO Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11935.27</v>
+        <v>4306603.08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.72</v>
+        <v>177.19</v>
       </c>
       <c r="F5" t="n">
-        <v>4.87</v>
+        <v>184.89</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.08</v>
+        <v>-4.16</v>
       </c>
       <c r="H5" t="n">
-        <v>4.79</v>
+        <v>182.58</v>
       </c>
       <c r="I5" t="n">
-        <v>4.64</v>
+        <v>176.38</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.68</v>
+        <v>4.91</v>
       </c>
       <c r="K5" t="n">
-        <v>72540.69</v>
+        <v>215938.01</v>
       </c>
       <c r="L5" t="n">
-        <v>65731.56</v>
+        <v>215938</v>
       </c>
       <c r="M5" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>60922</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>-22824.89</v>
+        <v>120067</v>
       </c>
       <c r="P5" t="n">
-        <v>-22657.69</v>
+        <v>120067</v>
       </c>
       <c r="Q5" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>29760</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>27640.48</v>
+        <v>11412</v>
       </c>
       <c r="T5" t="n">
-        <v>24106.16</v>
+        <v>62556</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>2026-03-02 23:11:49</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4306603.08</v>
+        <v>1510391.41</v>
       </c>
       <c r="E6" t="n">
-        <v>177.19</v>
+        <v>402.51</v>
       </c>
       <c r="F6" t="n">
-        <v>184.89</v>
+        <v>408.58</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.16</v>
+        <v>-1.49</v>
       </c>
       <c r="H6" t="n">
-        <v>182.58</v>
+        <v>407.11</v>
       </c>
       <c r="I6" t="n">
-        <v>176.38</v>
+        <v>398.12</v>
       </c>
       <c r="J6" t="n">
-        <v>4.91</v>
+        <v>1.09</v>
       </c>
       <c r="K6" t="n">
-        <v>215938.01</v>
+        <v>94827</v>
       </c>
       <c r="L6" t="n">
-        <v>215938</v>
+        <v>94827</v>
       </c>
       <c r="M6" t="n">
-        <v>60922</v>
+        <v>96773</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="P6" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="Q6" t="n">
-        <v>29760</v>
+        <v>14999</v>
       </c>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>11412</v>
+        <v>14719</v>
       </c>
       <c r="T6" t="n">
-        <v>62556</v>
+        <v>44059</v>
       </c>
       <c r="U6" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E7" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F7" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H7" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I7" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K7" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L7" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M7" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P7" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T7" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U7" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -1,150 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StockSync\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83B56D38-3862-4B1B-BB4B-23A9716D7596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-109" windowWidth="19286" windowHeight="10219" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
-  <si>
-    <t>Stock Ticker</t>
-  </si>
-  <si>
-    <t>Company Name</t>
-  </si>
-  <si>
-    <t>Company Description</t>
-  </si>
-  <si>
-    <t>Mkt Cap/Net Assets (M)</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Prev Close</t>
-  </si>
-  <si>
-    <t>Change %</t>
-  </si>
-  <si>
-    <t>Day High</t>
-  </si>
-  <si>
-    <t>Day Low</t>
-  </si>
-  <si>
-    <t>EPS (TTM)</t>
-  </si>
-  <si>
-    <t>Revenue TTM (M)</t>
-  </si>
-  <si>
-    <t>Revenue 1Y (M)</t>
-  </si>
-  <si>
-    <t>Revenue 3Y (M)</t>
-  </si>
-  <si>
-    <t>Revenue 5Y (M)</t>
-  </si>
-  <si>
-    <t>Net Income TTM (M)</t>
-  </si>
-  <si>
-    <t>Net Income 1Y (M)</t>
-  </si>
-  <si>
-    <t>Net Income 3Y (M)</t>
-  </si>
-  <si>
-    <t>Net Income 5Y (M)</t>
-  </si>
-  <si>
-    <t>Total Debt (M)</t>
-  </si>
-  <si>
-    <t>Cash (M)</t>
-  </si>
-  <si>
-    <t>Last Updated</t>
-  </si>
-  <si>
-    <t>NVDA</t>
-  </si>
-  <si>
-    <t>NVIDIA Corporation</t>
-  </si>
-  <si>
-    <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-  </si>
-  <si>
-    <t>2026-03-01 15:58:54</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>Tesla, Inc.</t>
-  </si>
-  <si>
-    <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-  </si>
-  <si>
-    <t>2026-03-01 16:52:00</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -156,55 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -492,208 +420,336 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Stock Ticker</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Company Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Company Description</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Mkt Cap/Net Assets (M)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Prev Close</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Change %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Day High</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Day Low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EPS (TTM)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue TTM (M)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue 1Y (M)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue 3Y (M)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue 5Y (M)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Net Income TTM (M)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Net Income 1Y (M)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Net Income 3Y (M)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Net Income 5Y (M)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Total Debt (M)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Cash (M)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Last Updated</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="2">
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>11935.27</v>
+      </c>
+      <c r="E2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K2" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L2" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M2" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P2" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T2" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-03-02 23:32:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E3" t="n">
         <v>177.19</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F3" t="n">
         <v>184.89</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G3" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H3" t="n">
         <v>182.58</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I3" t="n">
         <v>176.38</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J3" t="n">
         <v>4.91</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K3" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L3" t="n">
         <v>215938</v>
       </c>
-      <c r="M2" s="2">
+      <c r="M3" t="n">
         <v>60922</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>120067</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P3" t="n">
         <v>120067</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="Q3" t="n">
         <v>29760</v>
       </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>11412</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T3" t="n">
         <v>62556</v>
       </c>
-      <c r="U2" s="2" t="s">
-        <v>24</v>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="4">
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E4" t="n">
         <v>402.51</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F4" t="n">
         <v>408.58</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G4" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H4" t="n">
         <v>407.11</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I4" t="n">
         <v>398.12</v>
       </c>
-      <c r="J3" s="4">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="K3" s="4">
+      <c r="J4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K4" t="n">
         <v>94827</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L4" t="n">
         <v>94827</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M4" t="n">
         <v>96773</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>3794</v>
       </c>
-      <c r="P3" s="4">
+      <c r="P4" t="n">
         <v>3794</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="Q4" t="n">
         <v>14999</v>
       </c>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
         <v>14719</v>
       </c>
-      <c r="T3" s="4">
+      <c r="T4" t="n">
         <v>44059</v>
       </c>
-      <c r="U3" s="4" t="s">
-        <v>28</v>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 16:52:00</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="5" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="8" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="10" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="12" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="14" spans="1:21" ht="40.35" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,213 +538,136 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NIO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NIO Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11935.27</v>
+        <v>4306603.08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.72</v>
+        <v>177.19</v>
       </c>
       <c r="F2" t="n">
-        <v>4.87</v>
+        <v>184.89</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.08</v>
+        <v>-4.16</v>
       </c>
       <c r="H2" t="n">
-        <v>4.79</v>
+        <v>182.58</v>
       </c>
       <c r="I2" t="n">
-        <v>4.64</v>
+        <v>176.38</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.68</v>
+        <v>4.91</v>
       </c>
       <c r="K2" t="n">
-        <v>72540.69</v>
+        <v>215938.01</v>
       </c>
       <c r="L2" t="n">
-        <v>65731.56</v>
+        <v>215938</v>
       </c>
       <c r="M2" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>60922</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>-22824.89</v>
+        <v>120067</v>
       </c>
       <c r="P2" t="n">
-        <v>-22657.69</v>
+        <v>120067</v>
       </c>
       <c r="Q2" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>29760</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>27640.48</v>
+        <v>11412</v>
       </c>
       <c r="T2" t="n">
-        <v>24106.16</v>
+        <v>62556</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-02 23:32:38</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4306603.08</v>
+        <v>1510391.41</v>
       </c>
       <c r="E3" t="n">
-        <v>177.19</v>
+        <v>402.51</v>
       </c>
       <c r="F3" t="n">
-        <v>184.89</v>
+        <v>408.58</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.16</v>
+        <v>-1.49</v>
       </c>
       <c r="H3" t="n">
-        <v>182.58</v>
+        <v>407.11</v>
       </c>
       <c r="I3" t="n">
-        <v>176.38</v>
+        <v>398.12</v>
       </c>
       <c r="J3" t="n">
-        <v>4.91</v>
+        <v>1.09</v>
       </c>
       <c r="K3" t="n">
-        <v>215938.01</v>
+        <v>94827</v>
       </c>
       <c r="L3" t="n">
-        <v>215938</v>
+        <v>94827</v>
       </c>
       <c r="M3" t="n">
-        <v>60922</v>
+        <v>96773</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="P3" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="Q3" t="n">
-        <v>29760</v>
+        <v>14999</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>11412</v>
+        <v>14719</v>
       </c>
       <c r="T3" t="n">
-        <v>62556</v>
+        <v>44059</v>
       </c>
       <c r="U3" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E4" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F4" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G4" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H4" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I4" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K4" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L4" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M4" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P4" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T4" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U4" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,12 +29,24 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +67,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,138 +560,215 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E2" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F2" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H2" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I2" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K2" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L2" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M2" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P2" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T2" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>11935.27</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>-3.08</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>4.79</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-02 18:43:08</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" s="2" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" s="2" t="n">
         <v>402.51</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" s="2" t="n">
         <v>408.58</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" s="2" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" s="2" t="n">
         <v>407.11</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" s="2" t="n">
         <v>398.12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" s="2" t="n">
         <v>1.09</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" s="2" t="n">
         <v>96773</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>14999</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n">
         <v>14719</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" s="2" t="n">
         <v>44059</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,24 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,22 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,215 +536,138 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>NIO</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>NIO Inc.</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>11935.27</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.87</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>-3.08</v>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>72540.69</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>65731.56</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>-22824.89</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>-22657.69</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>27640.48</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>24106.16</v>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-02 18:43:08</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E2" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F2" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H2" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I2" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J2" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K2" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L2" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M2" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P2" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T2" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D3" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E3" t="n">
         <v>402.51</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F3" t="n">
         <v>408.58</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G3" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H3" t="n">
         <v>407.11</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I3" t="n">
         <v>398.12</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J3" t="n">
         <v>1.09</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K3" t="n">
         <v>94827</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L3" t="n">
         <v>94827</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M3" t="n">
         <v>96773</v>
       </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>3794</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P3" t="n">
         <v>3794</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q3" t="n">
         <v>14999</v>
       </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T3" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,12 +29,24 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +67,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,138 +560,215 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E2" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F2" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H2" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I2" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K2" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L2" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M2" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P2" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T2" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3002160.38</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>403.93</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>406.7</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>392.68</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J3" s="4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P3" s="4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" s="2" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" s="2" t="n">
         <v>402.51</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" s="2" t="n">
         <v>408.58</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" s="2" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H4" s="2" t="n">
         <v>407.11</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I4" s="2" t="n">
         <v>398.12</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J4" s="2" t="n">
         <v>1.09</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M4" s="2" t="n">
         <v>96773</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q4" s="2" t="n">
         <v>14999</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n">
         <v>14719</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T4" s="2" t="n">
         <v>44059</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,24 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,22 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,215 +536,284 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>3002160.38</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>403.93</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="n">
         <v>398.55</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" t="n">
         <v>1.35</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" t="n">
         <v>406.7</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>392.68</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>15.98</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>281724</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>211915</v>
       </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>119262</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>101832</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>72361</v>
       </c>
-      <c r="R2" s="2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" s="2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>123278</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>89462</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11606.55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K3" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-03-03 21:29:38</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L4" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" t="n">
         <v>402.51</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" t="n">
         <v>408.58</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G5" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H5" t="n">
         <v>407.11</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I5" t="n">
         <v>398.12</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J5" t="n">
         <v>1.09</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K5" t="n">
         <v>94827</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L5" t="n">
         <v>94827</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M5" t="n">
         <v>96773</v>
       </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>3794</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P5" t="n">
         <v>3794</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q5" t="n">
         <v>14999</v>
       </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T5" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,12 +29,24 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -55,10 +67,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -536,284 +560,207 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NIO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NIO Inc.</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>11606.55</v>
-      </c>
-      <c r="E2" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="F2" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="G2" t="n">
-        <v>-2.75</v>
-      </c>
-      <c r="H2" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="J2" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="K2" t="n">
-        <v>72540.69</v>
-      </c>
-      <c r="L2" t="n">
-        <v>65731.56</v>
-      </c>
-      <c r="M2" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>-22824.89</v>
-      </c>
-      <c r="P2" t="n">
-        <v>-22657.69</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="n">
-        <v>27640.48</v>
-      </c>
-      <c r="T2" t="n">
-        <v>24106.16</v>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>2026-03-03 21:29:38</t>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>3002160.38</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>403.93</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>398.55</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>406.7</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>392.68</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>305453.01</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>281724</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>211915</v>
+      </c>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n">
+        <v>119262</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>101832</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>72361</v>
+      </c>
+      <c r="R2" s="2" t="n"/>
+      <c r="S2" s="2" t="n">
+        <v>123278</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>89462</v>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>NVDA</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>NVIDIA Corporation</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="4" t="n">
         <v>4306603.08</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="4" t="n">
         <v>177.19</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="4" t="n">
         <v>184.89</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="4" t="n">
         <v>-4.16</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="4" t="n">
         <v>182.58</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="4" t="n">
         <v>176.38</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="4" t="n">
         <v>4.91</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="4" t="n">
         <v>215938.01</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="4" t="n">
         <v>215938</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="4" t="n">
         <v>60922</v>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="n">
+      <c r="N3" s="4" t="n"/>
+      <c r="O3" s="4" t="n">
         <v>120067</v>
       </c>
-      <c r="P3" t="n">
+      <c r="P3" s="4" t="n">
         <v>120067</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="Q3" s="4" t="n">
         <v>29760</v>
       </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="n">
+      <c r="R3" s="4" t="n"/>
+      <c r="S3" s="4" t="n">
         <v>11412</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="4" t="n">
         <v>62556</v>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" s="4" t="inlineStr">
         <is>
           <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SoFi Technologies, Inc.</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>23732.66</v>
-      </c>
-      <c r="E4" t="n">
-        <v>18.61</v>
-      </c>
-      <c r="F4" t="n">
-        <v>18.39</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H4" t="n">
-        <v>19.04</v>
-      </c>
-      <c r="I4" t="n">
-        <v>17.69</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3583.03</v>
-      </c>
-      <c r="L4" t="n">
-        <v>3613.35</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2108.22</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="P4" t="n">
-        <v>481.32</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>-300.74</v>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1939.17</v>
-      </c>
-      <c r="T4" t="n">
-        <v>5001.41</v>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-03-03 21:34:25</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D4" s="2" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E4" s="2" t="n">
         <v>402.51</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F4" s="2" t="n">
         <v>408.58</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G4" s="2" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H4" s="2" t="n">
         <v>407.11</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I4" s="2" t="n">
         <v>398.12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J4" s="2" t="n">
         <v>1.09</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L4" s="2" t="n">
         <v>94827</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M4" s="2" t="n">
         <v>96773</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P4" s="2" t="n">
         <v>3794</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q4" s="2" t="n">
         <v>14999</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="n">
         <v>14719</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T4" s="2" t="n">
         <v>44059</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,282 +538,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NIO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NIO Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3002160.38</v>
+        <v>11606.55</v>
       </c>
       <c r="E2" t="n">
-        <v>403.93</v>
+        <v>4.59</v>
       </c>
       <c r="F2" t="n">
-        <v>398.55</v>
+        <v>4.72</v>
       </c>
       <c r="G2" t="n">
-        <v>1.35</v>
+        <v>-2.75</v>
       </c>
       <c r="H2" t="n">
-        <v>406.7</v>
+        <v>4.59</v>
       </c>
       <c r="I2" t="n">
-        <v>392.68</v>
+        <v>4.41</v>
       </c>
       <c r="J2" t="n">
-        <v>15.98</v>
+        <v>-1.68</v>
       </c>
       <c r="K2" t="n">
-        <v>305453.01</v>
+        <v>72540.69</v>
       </c>
       <c r="L2" t="n">
-        <v>281724</v>
+        <v>65731.56</v>
       </c>
       <c r="M2" t="n">
-        <v>211915</v>
+        <v>49268.56</v>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>119262</v>
+        <v>-22824.89</v>
       </c>
       <c r="P2" t="n">
-        <v>101832</v>
+        <v>-22657.69</v>
       </c>
       <c r="Q2" t="n">
-        <v>72361</v>
+        <v>-14559.44</v>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>123278</v>
+        <v>27640.48</v>
       </c>
       <c r="T2" t="n">
-        <v>89462</v>
+        <v>24106.16</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-03 16:28:44</t>
+          <t>2026-03-03 21:29:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIO Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11606.55</v>
+        <v>4306603.08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.59</v>
+        <v>177.19</v>
       </c>
       <c r="F3" t="n">
-        <v>4.72</v>
+        <v>184.89</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.75</v>
+        <v>-4.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.59</v>
+        <v>182.58</v>
       </c>
       <c r="I3" t="n">
-        <v>4.41</v>
+        <v>176.38</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.68</v>
+        <v>4.91</v>
       </c>
       <c r="K3" t="n">
-        <v>72540.69</v>
+        <v>215938.01</v>
       </c>
       <c r="L3" t="n">
-        <v>65731.56</v>
+        <v>215938</v>
       </c>
       <c r="M3" t="n">
-        <v>49268.56</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>60922</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-22824.89</v>
+        <v>120067</v>
       </c>
       <c r="P3" t="n">
-        <v>-22657.69</v>
+        <v>120067</v>
       </c>
       <c r="Q3" t="n">
-        <v>-14559.44</v>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>29760</v>
+      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>27640.48</v>
+        <v>11412</v>
       </c>
       <c r="T3" t="n">
-        <v>24106.16</v>
+        <v>62556</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-03 21:29:38</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4306603.08</v>
+        <v>1510391.41</v>
       </c>
       <c r="E4" t="n">
-        <v>177.19</v>
+        <v>402.51</v>
       </c>
       <c r="F4" t="n">
-        <v>184.89</v>
+        <v>408.58</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.16</v>
+        <v>-1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>182.58</v>
+        <v>407.11</v>
       </c>
       <c r="I4" t="n">
-        <v>176.38</v>
+        <v>398.12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.91</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>215938.01</v>
+        <v>94827</v>
       </c>
       <c r="L4" t="n">
-        <v>215938</v>
+        <v>94827</v>
       </c>
       <c r="M4" t="n">
-        <v>60922</v>
+        <v>96773</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="P4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="Q4" t="n">
-        <v>29760</v>
+        <v>14999</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>11412</v>
+        <v>14719</v>
       </c>
       <c r="T4" t="n">
-        <v>62556</v>
+        <v>44059</v>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H5" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M5" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T5" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -676,67 +676,144 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>SoFi Technologies, Inc. provides various financial services in the United States, Latin America, Canada, and Hong Kong. The company operates through three segments: Lending, Technology Platform, and Financial Services. It offers lending and financial services and products that allows its members to borrow, save, spend, invest, and protect money; and personal loans, student loans, home loans, and related services. The company also operates Galileo, a technology platform that offers services to financial and non-financial institution; and Technisys, a cloud-native digital and core banking platform that provides software licenses and associated services, including implementation and maintenance. In addition, it provides SoFi Money offers checking and savings accounts, and cash management products; SoFi Invest, a mobile-first investment platform that offers access to trading and advisory solutions, such as investing and robo-advisory; and SoFI Crypto, a new digital asset trading platform. Further, the company offers SoFi Credit Card that provides cash back rewards on every purchase; Sofi Relay, a personal finance management product that allows to track all of their financial accounts comprising credit score and spending behaviors; SoFi Protect which offers insurance product; SoFi Travel, an application that manages travel search and booking experience; SoFi At Work provides financial benefits to employees, including student loan payments made on their employees' behalf; Lantern Credit, a financial services marketplace platform for seeking alternative products and provide product comparisons; and other lending as a service that offers pre-qualified borrower referrals and offers loans to third-party partner. The company was founded in 2011 and is based in San Francisco, California.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>23732.66</v>
+      </c>
+      <c r="E4" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="F4" t="n">
+        <v>18.39</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="I4" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3583.03</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3613.35</v>
+      </c>
+      <c r="M4" t="n">
+        <v>2108.22</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="P4" t="n">
+        <v>481.32</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-300.74</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>1939.17</v>
+      </c>
+      <c r="T4" t="n">
+        <v>5001.41</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-03 21:34:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D5" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E5" t="n">
         <v>402.51</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>408.58</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G5" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H5" t="n">
         <v>407.11</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I5" t="n">
         <v>398.12</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J5" t="n">
         <v>1.09</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K5" t="n">
         <v>94827</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L5" t="n">
         <v>94827</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M5" t="n">
         <v>96773</v>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>3794</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P5" t="n">
         <v>3794</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="Q5" t="n">
         <v>14999</v>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -29,24 +29,12 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
-        <bgColor rgb="00D9E1F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -67,22 +55,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -449,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -560,207 +536,284 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Microsoft Corporation</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" t="n">
         <v>3002160.38</v>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" t="n">
         <v>403.93</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="F2" t="n">
         <v>398.55</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="G2" t="n">
         <v>1.35</v>
       </c>
-      <c r="H2" s="2" t="n">
+      <c r="H2" t="n">
         <v>406.7</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" t="n">
         <v>392.68</v>
       </c>
-      <c r="J2" s="2" t="n">
+      <c r="J2" t="n">
         <v>15.98</v>
       </c>
-      <c r="K2" s="2" t="n">
+      <c r="K2" t="n">
         <v>305453.01</v>
       </c>
-      <c r="L2" s="2" t="n">
+      <c r="L2" t="n">
         <v>281724</v>
       </c>
-      <c r="M2" s="2" t="n">
+      <c r="M2" t="n">
         <v>211915</v>
       </c>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="n">
         <v>119262</v>
       </c>
-      <c r="P2" s="2" t="n">
+      <c r="P2" t="n">
         <v>101832</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" t="n">
         <v>72361</v>
       </c>
-      <c r="R2" s="2" t="n"/>
-      <c r="S2" s="2" t="n">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="n">
         <v>123278</v>
       </c>
-      <c r="T2" s="2" t="n">
+      <c r="T2" t="n">
         <v>89462</v>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
-        <v>4306603.08</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>177.19</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>184.89</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>-4.16</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>182.58</v>
-      </c>
-      <c r="I3" s="4" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>4.91</v>
-      </c>
-      <c r="K3" s="4" t="n">
-        <v>215938.01</v>
-      </c>
-      <c r="L3" s="4" t="n">
-        <v>215938</v>
-      </c>
-      <c r="M3" s="4" t="n">
-        <v>60922</v>
-      </c>
-      <c r="N3" s="4" t="n"/>
-      <c r="O3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>120067</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>29760</v>
-      </c>
-      <c r="R3" s="4" t="n"/>
-      <c r="S3" s="4" t="n">
-        <v>11412</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>62556</v>
-      </c>
-      <c r="U3" s="4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NIO</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>NIO Inc.</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>11606.55</v>
+      </c>
+      <c r="E3" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-1.68</v>
+      </c>
+      <c r="K3" t="n">
+        <v>72540.69</v>
+      </c>
+      <c r="L3" t="n">
+        <v>65731.56</v>
+      </c>
+      <c r="M3" t="n">
+        <v>49268.56</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O3" t="n">
+        <v>-22824.89</v>
+      </c>
+      <c r="P3" t="n">
+        <v>-22657.69</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-14559.44</v>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>27640.48</v>
+      </c>
+      <c r="T3" t="n">
+        <v>24106.16</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>2026-03-03 21:39:04</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4306603.08</v>
+      </c>
+      <c r="E4" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="F4" t="n">
+        <v>184.89</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-4.16</v>
+      </c>
+      <c r="H4" t="n">
+        <v>182.58</v>
+      </c>
+      <c r="I4" t="n">
+        <v>176.38</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>215938.01</v>
+      </c>
+      <c r="L4" t="n">
+        <v>215938</v>
+      </c>
+      <c r="M4" t="n">
+        <v>60922</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="P4" t="n">
+        <v>120067</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>29760</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D5" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="E5" t="n">
         <v>402.51</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="F5" t="n">
         <v>408.58</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="G5" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H4" s="2" t="n">
+      <c r="H5" t="n">
         <v>407.11</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I5" t="n">
         <v>398.12</v>
       </c>
-      <c r="J4" s="2" t="n">
+      <c r="J5" t="n">
         <v>1.09</v>
       </c>
-      <c r="K4" s="2" t="n">
+      <c r="K5" t="n">
         <v>94827</v>
       </c>
-      <c r="L4" s="2" t="n">
+      <c r="L5" t="n">
         <v>94827</v>
       </c>
-      <c r="M4" s="2" t="n">
+      <c r="M5" t="n">
         <v>96773</v>
       </c>
-      <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="n">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>3794</v>
       </c>
-      <c r="P4" s="2" t="n">
+      <c r="P5" t="n">
         <v>3794</v>
       </c>
-      <c r="Q4" s="2" t="n">
+      <c r="Q5" t="n">
         <v>14999</v>
       </c>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="n">
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" s="2" t="n">
+      <c r="T5" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -650,11 +650,7 @@
       <c r="M3" t="n">
         <v>49268.56</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
         <v>-22824.89</v>
       </c>
@@ -664,11 +660,7 @@
       <c r="Q3" t="n">
         <v>-14559.44</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
         <v>27640.48</v>
       </c>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -607,205 +607,136 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NIO</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NIO Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIO Inc. designs, develops, manufactures, and sells smart electric vehicles in China, Europe, and internationally. It offers five and six-seater electric SUVs, as well as smart electric sedans. The company also offers power solutions, including Power Home, a home charging solution; Power Swap, a battery-swapping service; Power Charger and Destination Charger; Power Mobile, a mobile charging service through charging vans; Power Map, an application that provides access to a network of public chargers and their real-time information; and One Click for power valet service. In addition, it provides repair, maintenance, and bodywork services through its service centers and authorized third-party service centers; statutory and third-party liability insurance, and vehicle damage insurance through third-party insurers; repair and maintenance; courtesy vehicle; data packages; and auto financing and financial leasing services. Further, the company is involved in the provision of energy and service packages to its users; design and technology development activities; manufacture of electric powertrains, battery packs, and components; and sales and after-sales management activities. The company was formerly known as NextEV Inc. and changed its name to NIO Inc. in July 2017. NIO Inc. was incorporated in 2014 and is based in Shanghai, China.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11606.55</v>
+        <v>4306603.08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.59</v>
+        <v>177.19</v>
       </c>
       <c r="F3" t="n">
-        <v>4.72</v>
+        <v>184.89</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.75</v>
+        <v>-4.16</v>
       </c>
       <c r="H3" t="n">
-        <v>4.59</v>
+        <v>182.58</v>
       </c>
       <c r="I3" t="n">
-        <v>4.41</v>
+        <v>176.38</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.68</v>
+        <v>4.91</v>
       </c>
       <c r="K3" t="n">
-        <v>72540.69</v>
+        <v>215938.01</v>
       </c>
       <c r="L3" t="n">
-        <v>65731.56</v>
+        <v>215938</v>
       </c>
       <c r="M3" t="n">
-        <v>49268.56</v>
+        <v>60922</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>-22824.89</v>
+        <v>120067</v>
       </c>
       <c r="P3" t="n">
-        <v>-22657.69</v>
+        <v>120067</v>
       </c>
       <c r="Q3" t="n">
-        <v>-14559.44</v>
+        <v>29760</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>27640.48</v>
+        <v>11412</v>
       </c>
       <c r="T3" t="n">
-        <v>24106.16</v>
+        <v>62556</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-03 21:39:04</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4306603.08</v>
+        <v>1510391.41</v>
       </c>
       <c r="E4" t="n">
-        <v>177.19</v>
+        <v>402.51</v>
       </c>
       <c r="F4" t="n">
-        <v>184.89</v>
+        <v>408.58</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.16</v>
+        <v>-1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>182.58</v>
+        <v>407.11</v>
       </c>
       <c r="I4" t="n">
-        <v>176.38</v>
+        <v>398.12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.91</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>215938.01</v>
+        <v>94827</v>
       </c>
       <c r="L4" t="n">
-        <v>215938</v>
+        <v>94827</v>
       </c>
       <c r="M4" t="n">
-        <v>60922</v>
+        <v>96773</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="P4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="Q4" t="n">
-        <v>29760</v>
+        <v>14999</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>11412</v>
+        <v>14719</v>
       </c>
       <c r="T4" t="n">
-        <v>62556</v>
+        <v>44059</v>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H5" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M5" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T5" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,205 +538,282 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Robinhood Markets, Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3002160.38</v>
+        <v>68486.46000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>403.93</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>398.55</v>
+        <v>78.78</v>
       </c>
       <c r="G2" t="n">
-        <v>1.35</v>
+        <v>-3.44</v>
       </c>
       <c r="H2" t="n">
-        <v>406.7</v>
+        <v>77.3999</v>
       </c>
       <c r="I2" t="n">
-        <v>392.68</v>
+        <v>72.25</v>
       </c>
       <c r="J2" t="n">
-        <v>15.98</v>
+        <v>2.05</v>
       </c>
       <c r="K2" t="n">
-        <v>305453.01</v>
+        <v>4473</v>
       </c>
       <c r="L2" t="n">
-        <v>281724</v>
+        <v>4473</v>
       </c>
       <c r="M2" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>1865</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O2" t="n">
-        <v>119262</v>
+        <v>1883</v>
       </c>
       <c r="P2" t="n">
-        <v>101832</v>
+        <v>1883</v>
       </c>
       <c r="Q2" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-541</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>123278</v>
+        <v>12449</v>
       </c>
       <c r="T2" t="n">
-        <v>89462</v>
+        <v>12646</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-03 16:28:44</t>
+          <t>2026-03-03 21:43:11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4306603.08</v>
+        <v>3002160.38</v>
       </c>
       <c r="E3" t="n">
-        <v>177.19</v>
+        <v>403.93</v>
       </c>
       <c r="F3" t="n">
-        <v>184.89</v>
+        <v>398.55</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.16</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>182.58</v>
+        <v>406.7</v>
       </c>
       <c r="I3" t="n">
-        <v>176.38</v>
+        <v>392.68</v>
       </c>
       <c r="J3" t="n">
-        <v>4.91</v>
+        <v>15.98</v>
       </c>
       <c r="K3" t="n">
-        <v>215938.01</v>
+        <v>305453.01</v>
       </c>
       <c r="L3" t="n">
-        <v>215938</v>
+        <v>281724</v>
       </c>
       <c r="M3" t="n">
-        <v>60922</v>
+        <v>211915</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>120067</v>
+        <v>119262</v>
       </c>
       <c r="P3" t="n">
-        <v>120067</v>
+        <v>101832</v>
       </c>
       <c r="Q3" t="n">
-        <v>29760</v>
+        <v>72361</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>11412</v>
+        <v>123278</v>
       </c>
       <c r="T3" t="n">
-        <v>62556</v>
+        <v>89462</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1510391.41</v>
+        <v>4306603.08</v>
       </c>
       <c r="E4" t="n">
-        <v>402.51</v>
+        <v>177.19</v>
       </c>
       <c r="F4" t="n">
-        <v>408.58</v>
+        <v>184.89</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.49</v>
+        <v>-4.16</v>
       </c>
       <c r="H4" t="n">
-        <v>407.11</v>
+        <v>182.58</v>
       </c>
       <c r="I4" t="n">
-        <v>398.12</v>
+        <v>176.38</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>4.91</v>
       </c>
       <c r="K4" t="n">
-        <v>94827</v>
+        <v>215938.01</v>
       </c>
       <c r="L4" t="n">
-        <v>94827</v>
+        <v>215938</v>
       </c>
       <c r="M4" t="n">
-        <v>96773</v>
+        <v>60922</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="P4" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="Q4" t="n">
-        <v>14999</v>
+        <v>29760</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F5" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H5" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M5" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,282 +538,205 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc.</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Robinhood Markets, Inc. operates financial services platform in the United States. The company's platform allows users to invest in stocks, exchange-traded funds (ETFs), and American depository receipts. It offers fractional trading, recurring investments, access to investing on margin, fully-paid securities lending, cash sweep, instant withdrawals, retirement program, around-the-clock trading, joint investing accounts, event contracts, future contract services, and short selling. The company also provides various learning and education solutions comprise Snacks, an accessible digest of business news stories for a new generation of investors; Learn, which is an online collection of guides, feature tutorials, and financial dictionary; Newsfeeds that offer access to free, premium news from sites from various sites, such as Barron's, Reuters, and Dow Jones. In addition, the company offers In-App Education, a resource that covers investing fundamentals, including why people invest, a stock market overview, and tips on how to define investing goals, as well as allows customers to understand the basics of investing before their first trade; and Crypto Learn and Earn, an educational module available to various crypto customers through Robinhood Learn to teach customers the basics related to cryptocurrency. Further, it provides Robinhood credit cards, cash card and spending accounts, and wallets. Robinhood Markets, Inc. was incorporated in 2013 and is headquartered in Menlo Park, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>68486.46000000001</v>
+        <v>3002160.38</v>
       </c>
       <c r="E2" t="n">
-        <v>76.06999999999999</v>
+        <v>403.93</v>
       </c>
       <c r="F2" t="n">
-        <v>78.78</v>
+        <v>398.55</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.44</v>
+        <v>1.35</v>
       </c>
       <c r="H2" t="n">
-        <v>77.3999</v>
+        <v>406.7</v>
       </c>
       <c r="I2" t="n">
-        <v>72.25</v>
+        <v>392.68</v>
       </c>
       <c r="J2" t="n">
-        <v>2.05</v>
+        <v>15.98</v>
       </c>
       <c r="K2" t="n">
-        <v>4473</v>
+        <v>305453.01</v>
       </c>
       <c r="L2" t="n">
-        <v>4473</v>
+        <v>281724</v>
       </c>
       <c r="M2" t="n">
-        <v>1865</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>211915</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>1883</v>
+        <v>119262</v>
       </c>
       <c r="P2" t="n">
-        <v>1883</v>
+        <v>101832</v>
       </c>
       <c r="Q2" t="n">
-        <v>-541</v>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+        <v>72361</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>12449</v>
+        <v>123278</v>
       </c>
       <c r="T2" t="n">
-        <v>12646</v>
+        <v>89462</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-03 21:43:11</t>
+          <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3002160.38</v>
+        <v>4306603.08</v>
       </c>
       <c r="E3" t="n">
-        <v>403.93</v>
+        <v>177.19</v>
       </c>
       <c r="F3" t="n">
-        <v>398.55</v>
+        <v>184.89</v>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>-4.16</v>
       </c>
       <c r="H3" t="n">
-        <v>406.7</v>
+        <v>182.58</v>
       </c>
       <c r="I3" t="n">
-        <v>392.68</v>
+        <v>176.38</v>
       </c>
       <c r="J3" t="n">
-        <v>15.98</v>
+        <v>4.91</v>
       </c>
       <c r="K3" t="n">
-        <v>305453.01</v>
+        <v>215938.01</v>
       </c>
       <c r="L3" t="n">
-        <v>281724</v>
+        <v>215938</v>
       </c>
       <c r="M3" t="n">
-        <v>211915</v>
+        <v>60922</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>119262</v>
+        <v>120067</v>
       </c>
       <c r="P3" t="n">
-        <v>101832</v>
+        <v>120067</v>
       </c>
       <c r="Q3" t="n">
-        <v>72361</v>
+        <v>29760</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>123278</v>
+        <v>11412</v>
       </c>
       <c r="T3" t="n">
-        <v>89462</v>
+        <v>62556</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-03 16:28:44</t>
+          <t>2026-03-01 15:58:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>TSLA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Tesla, Inc.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4306603.08</v>
+        <v>1510391.41</v>
       </c>
       <c r="E4" t="n">
-        <v>177.19</v>
+        <v>402.51</v>
       </c>
       <c r="F4" t="n">
-        <v>184.89</v>
+        <v>408.58</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.16</v>
+        <v>-1.49</v>
       </c>
       <c r="H4" t="n">
-        <v>182.58</v>
+        <v>407.11</v>
       </c>
       <c r="I4" t="n">
-        <v>176.38</v>
+        <v>398.12</v>
       </c>
       <c r="J4" t="n">
-        <v>4.91</v>
+        <v>1.09</v>
       </c>
       <c r="K4" t="n">
-        <v>215938.01</v>
+        <v>94827</v>
       </c>
       <c r="L4" t="n">
-        <v>215938</v>
+        <v>94827</v>
       </c>
       <c r="M4" t="n">
-        <v>60922</v>
+        <v>96773</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="P4" t="n">
-        <v>120067</v>
+        <v>3794</v>
       </c>
       <c r="Q4" t="n">
-        <v>29760</v>
+        <v>14999</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>11412</v>
+        <v>14719</v>
       </c>
       <c r="T4" t="n">
-        <v>62556</v>
+        <v>44059</v>
       </c>
       <c r="U4" t="inlineStr">
-        <is>
-          <t>2026-03-01 15:58:54</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>1510391.41</v>
-      </c>
-      <c r="E5" t="n">
-        <v>402.51</v>
-      </c>
-      <c r="F5" t="n">
-        <v>408.58</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="H5" t="n">
-        <v>407.11</v>
-      </c>
-      <c r="I5" t="n">
-        <v>398.12</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="L5" t="n">
-        <v>94827</v>
-      </c>
-      <c r="M5" t="n">
-        <v>96773</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3794</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>14999</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
-        <v>14719</v>
-      </c>
-      <c r="T5" t="n">
-        <v>44059</v>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:U5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,205 +538,282 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation</t>
+          <t>Alphabet Inc.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
+          <t>Alphabet Inc. offers various products and platforms in the United States, Europe, the Middle East, Africa, the Asia-Pacific, Canada, and Latin America. It operates through Google Services, Google Cloud, and Other Bets segments. The Google Services segment provides products and services, including ads, Android, Chrome, devices, Gmail, Google Drive, Google Maps, Google Photos, Google Play, Search, and YouTube. It is also involved in the sale of apps and in-app purchases and digital content in Google Play and YouTube; and devices, as well as the provision of YouTube consumer subscription services, such as YouTube TV, YouTube Music and Premium, NFL Sunday Ticket, and Google One. The Google Cloud segment offers consumption-based fees and subscriptions for AI solutions, including AI infrastructure, Vertex AI platform, and Gemini enterprise. It also provides cybersecurity, and data and analytics services; Google Workspace that include cloud-based communication and collaboration tools for enterprises, such as Calendar, Gmail, Docs, Drive, and Meet; and other enterprise services. The Other Bets segment sells transportation and internet services. Alphabet Inc. was incorporated in 1998 and is headquartered in Mountain View, California.</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3002160.38</v>
+        <v>3672407.28</v>
       </c>
       <c r="E2" t="n">
-        <v>403.93</v>
+        <v>303.58</v>
       </c>
       <c r="F2" t="n">
-        <v>398.55</v>
+        <v>306.52</v>
       </c>
       <c r="G2" t="n">
-        <v>1.35</v>
+        <v>-0.96</v>
       </c>
       <c r="H2" t="n">
-        <v>406.7</v>
+        <v>303.94</v>
       </c>
       <c r="I2" t="n">
-        <v>392.68</v>
+        <v>296.71</v>
       </c>
       <c r="J2" t="n">
-        <v>15.98</v>
+        <v>10.82</v>
       </c>
       <c r="K2" t="n">
-        <v>305453.01</v>
+        <v>402836</v>
       </c>
       <c r="L2" t="n">
-        <v>281724</v>
+        <v>402836</v>
       </c>
       <c r="M2" t="n">
-        <v>211915</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>307394</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="O2" t="n">
-        <v>119262</v>
+        <v>132170</v>
       </c>
       <c r="P2" t="n">
-        <v>101832</v>
+        <v>132170</v>
       </c>
       <c r="Q2" t="n">
-        <v>72361</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>73795</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="S2" t="n">
-        <v>123278</v>
+        <v>66996</v>
       </c>
       <c r="T2" t="n">
-        <v>89462</v>
+        <v>126843</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>2026-03-03 16:28:44</t>
+          <t>2026-03-03 21:45:13</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation</t>
+          <t>Microsoft Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
+          <t>Microsoft Corporation develops and supports software, services, devices, and solutions worldwide. The Productivity and Business Processes segment offers Microsoft 365 commercial, enterprise mobility + security, windows commercial, power BI, exchange, sharepoint, Microsoft teams, security and compliance, and copilot; Microsoft 365 commercial products, such as Windows commercial on-premises and office licensed services; Microsoft 365 consumer products and cloud services, including Microsoft 365 consumer subscriptions, office licensed on-premises, and other consumer services; LinkedIn; dynamics products and cloud services, such as dynamics 365, cloud-based applications, and on-premises ERP and CRM applications. Its Intelligent Cloud segment provides Server products and cloud services comprising Azure and other cloud services, GitHub, Nuance Healthcare, virtual desktop offerings, and other cloud services; server products, including SQL and windows server, visual studio and system center related client access licenses, and other on-premises offerings; enterprise and partner services, such as enterprise support and nuance professional services, industry solutions, Microsoft partner network, and learning experience. The Personal Computing segment provides windows and devices, such as Windows OEM licensing and devices and surface and PC accessories; gaming services and solutions, such as Xbox hardware, content, and services, first- and third-party content Xbox game pass, subscriptions, and cloud gaming, advertising, and other cloud services; search and news advertising services that includes Bing and Copilot, Microsoft News and Edge, and third-party affiliates. It sells its products through OEMs, distributors, and resellers; and online and retail stores. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>4306603.08</v>
+        <v>3002160.38</v>
       </c>
       <c r="E3" t="n">
-        <v>177.19</v>
+        <v>403.93</v>
       </c>
       <c r="F3" t="n">
-        <v>184.89</v>
+        <v>398.55</v>
       </c>
       <c r="G3" t="n">
-        <v>-4.16</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="n">
-        <v>182.58</v>
+        <v>406.7</v>
       </c>
       <c r="I3" t="n">
-        <v>176.38</v>
+        <v>392.68</v>
       </c>
       <c r="J3" t="n">
-        <v>4.91</v>
+        <v>15.98</v>
       </c>
       <c r="K3" t="n">
-        <v>215938.01</v>
+        <v>305453.01</v>
       </c>
       <c r="L3" t="n">
-        <v>215938</v>
+        <v>281724</v>
       </c>
       <c r="M3" t="n">
-        <v>60922</v>
+        <v>211915</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>120067</v>
+        <v>119262</v>
       </c>
       <c r="P3" t="n">
-        <v>120067</v>
+        <v>101832</v>
       </c>
       <c r="Q3" t="n">
-        <v>29760</v>
+        <v>72361</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>11412</v>
+        <v>123278</v>
       </c>
       <c r="T3" t="n">
-        <v>62556</v>
+        <v>89462</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>2026-03-01 15:58:54</t>
+          <t>2026-03-03 16:28:44</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tesla, Inc.</t>
+          <t>NVIDIA Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+          <t>NVIDIA Corporation, a computing infrastructure company, provides graphics and compute and networking solutions in the United States, Taiwan, China, Hong Kong, and internationally. It operates through Compute &amp; Networking and Graphics segments. The Compute &amp; Networking segment includes its Data Center accelerated computing and networking platforms and artificial intelligence solutions and software and automotive platforms and autonomous and electric vehicle solutions, including software. The Graphics segment offers GeForce GPUs for gaming and PCs; Quadro/NVIDIA RTX GPUs for enterprise workstation graphics; GeForce NOW cloud gaming service; and NVIDIA vGPU software for graphics- virtual desktops and workstations. It also develops standalone software solutions, including NVIDIA AI Enterprise, NVIDIA Omniverse, NVIDIA DRIVE, and other software products. The company's products are used in gaming, professional visualization, data center, and automotive markets. It sells its products to original equipment manufacturers, original device manufacturers, system integrators and distributors, independent software vendors, cloud service providers, add-in board manufacturers, distributors, automotive manufacturers and tier-1 automotive suppliers, and other ecosystem participants. NVIDIA Corporation was incorporated in 1993 and is headquartered in Santa Clara, California.</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1510391.41</v>
+        <v>4306603.08</v>
       </c>
       <c r="E4" t="n">
-        <v>402.51</v>
+        <v>177.19</v>
       </c>
       <c r="F4" t="n">
-        <v>408.58</v>
+        <v>184.89</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.49</v>
+        <v>-4.16</v>
       </c>
       <c r="H4" t="n">
-        <v>407.11</v>
+        <v>182.58</v>
       </c>
       <c r="I4" t="n">
-        <v>398.12</v>
+        <v>176.38</v>
       </c>
       <c r="J4" t="n">
-        <v>1.09</v>
+        <v>4.91</v>
       </c>
       <c r="K4" t="n">
-        <v>94827</v>
+        <v>215938.01</v>
       </c>
       <c r="L4" t="n">
-        <v>94827</v>
+        <v>215938</v>
       </c>
       <c r="M4" t="n">
-        <v>96773</v>
+        <v>60922</v>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="P4" t="n">
-        <v>3794</v>
+        <v>120067</v>
       </c>
       <c r="Q4" t="n">
-        <v>14999</v>
+        <v>29760</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
+        <v>11412</v>
+      </c>
+      <c r="T4" t="n">
+        <v>62556</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2026-03-01 15:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1510391.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>402.51</v>
+      </c>
+      <c r="F5" t="n">
+        <v>408.58</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="H5" t="n">
+        <v>407.11</v>
+      </c>
+      <c r="I5" t="n">
+        <v>398.12</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="L5" t="n">
+        <v>94827</v>
+      </c>
+      <c r="M5" t="n">
+        <v>96773</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
+        <v>3794</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3794</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>14999</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="n">
         <v>14719</v>
       </c>
-      <c r="T4" t="n">
+      <c r="T5" t="n">
         <v>44059</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U5"/>
+  <dimension ref="A1:U6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -581,11 +581,7 @@
       <c r="M2" t="n">
         <v>307394</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
         <v>132170</v>
       </c>
@@ -595,11 +591,7 @@
       <c r="Q2" t="n">
         <v>73795</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
         <v>66996</v>
       </c>
@@ -753,67 +745,144 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc. builds and deploys software platforms for the intelligence community to assist in counterterrorism investigations and operations in the United States, the United Kingdom, and internationally. It provides Palantir Gotham integrates with other platforms for defense offerings which enables users to see, understand, and act in the modern battlespace; operations centers to the tactical edge; integrating data from domains and sensors in near real-time; and situational awareness and accelerating operational decision-making, as well as facilitates the hand-off between analysts and operational users, helping operators plan and execute real-world responses to threats that have been identified within the platform. The company also offers Palantir Foundry, a platform that transforms the ways organizations operate by creating a central operating system for their data; and allows individual users to integrate and analyze the data they need in one place. In addition, it provides Palantir Apollo, a software that delivers software and updates across the business, as well as enables customers to deploy their software virtually in any environment; and Palantir Artificial Intelligence Platform that provides unified access to open-source, self-hosted, and commercial large language models (LLMs) that can transform structured and unstructured data into LLM-understandable objects and can turn organizations' actions and processes into tools for humans and LLM-driven agents. The company was incorporated in 2003 and is headquartered in Aventura, Florida.</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>352102.48</v>
+      </c>
+      <c r="E5" t="n">
+        <v>147.22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>145.133</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="H5" t="n">
+        <v>147.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>138.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4475.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2225.01</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1625.03</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>209.82</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>229.34</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7177.04</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>2026-03-03 21:45:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Tesla, Inc.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Tesla, Inc. designs, develops, manufactures, leases, and sells electric vehicles, and energy generation and storage systems in the United States, China, and internationally. The company operates in two segments, Automotive; and Energy Generation and Storage. The company offers electric vehicles, as well as sells automotive regulatory credits; and non-warranty maintenance services and collision, automotive insurance services, as well as part sales and retail merchandise sale. It also provides sedans and sport utility vehicles through direct and used vehicle sales, a network of Tesla Superchargers, and in-app upgrades; purchase financing and leasing services; services for electric vehicles through its company-owned service locations and Tesla mobile service technicians; and vehicle limited warranties and extended service plans. In addition, the company engages in the design, manufacture, installation, sale, and leasing of solar energy generation and energy storage products, and related services to residential, commercial, and industrial customers and utilities through its website, stores, and galleries, as well as through a network of channel partners. Further, it provides services and repairs to its energy product customers, including under warranty and extended service plans; and various financing options to its residential customers; lithium-ion battery energy storage products, such as Powerwall and Megapack; energy generation products, including solar panels and solar roof; self-driving development and artificial intelligence software, vehicle control and infotainment software, and battery and powertrain. The company was formerly known as Tesla Motors, Inc. and changed its name to Tesla, Inc. in February 2017. Tesla, Inc. was incorporated in 2003 and is headquartered in Austin, Texas.</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D6" t="n">
         <v>1510391.41</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E6" t="n">
         <v>402.51</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>408.58</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G6" t="n">
         <v>-1.49</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H6" t="n">
         <v>407.11</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I6" t="n">
         <v>398.12</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J6" t="n">
         <v>1.09</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K6" t="n">
         <v>94827</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L6" t="n">
         <v>94827</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M6" t="n">
         <v>96773</v>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="n">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>3794</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P6" t="n">
         <v>3794</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q6" t="n">
         <v>14999</v>
       </c>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="n">
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="n">
         <v>14719</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T6" t="n">
         <v>44059</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>2026-03-01 16:52:00</t>
         </is>

--- a/stocks.xlsx
+++ b/stocks.xlsx
@@ -788,11 +788,7 @@
       <c r="M5" t="n">
         <v>2225.01</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
         <v>1625.03</v>
       </c>
@@ -802,11 +798,7 @@
       <c r="Q5" t="n">
         <v>209.82</v>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
         <v>229.34</v>
       </c>
